--- a/Results/Phase 2/Hydrogen/hydrogen ionising radiation results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen ionising radiation results.xlsx
@@ -886,7 +886,7 @@
         <v>0.0319567636359015</v>
       </c>
       <c r="N5" t="n">
-        <v>1.690083873104201</v>
+        <v>0.03195676363590191</v>
       </c>
       <c r="O5" t="n">
         <v>0.03195676363590191</v>
@@ -974,7 +974,7 @@
         <v>43.91099732222107</v>
       </c>
       <c r="N6" t="n">
-        <v>1.690083873104201</v>
+        <v>11.57413313234396</v>
       </c>
       <c r="O6" t="n">
         <v>11.57413331633711</v>
@@ -1062,7 +1062,7 @@
         <v>0.0527795486415709</v>
       </c>
       <c r="N7" t="n">
-        <v>1.690083873104201</v>
+        <v>0.0527795486415709</v>
       </c>
       <c r="O7" t="n">
         <v>0.05277868513124487</v>
@@ -1150,7 +1150,7 @@
         <v>0.09788884719354389</v>
       </c>
       <c r="N8" t="n">
-        <v>1.690083873104201</v>
+        <v>0.07579677198205165</v>
       </c>
       <c r="O8" t="n">
         <v>0.0818678660477571</v>
@@ -1238,7 +1238,7 @@
         <v>0.19621519605051</v>
       </c>
       <c r="N9" t="n">
-        <v>1.690083873104201</v>
+        <v>0.19621519605051</v>
       </c>
       <c r="O9" t="n">
         <v>0.2085409980230425</v>
@@ -1922,7 +1922,7 @@
         <v>0.01904000474839085</v>
       </c>
       <c r="N5" t="n">
-        <v>2.518621175655716</v>
+        <v>0.01904000474839081</v>
       </c>
       <c r="O5" t="n">
         <v>0.01904000474839081</v>
@@ -2010,7 +2010,7 @@
         <v>10.07327722724162</v>
       </c>
       <c r="N6" t="n">
-        <v>2.518621175655716</v>
+        <v>10.07336692780404</v>
       </c>
       <c r="O6" t="n">
         <v>38.27031195064526</v>
@@ -2098,7 +2098,7 @@
         <v>0.03415553945448917</v>
       </c>
       <c r="N7" t="n">
-        <v>2.518621175655716</v>
+        <v>0.03415553945448917</v>
       </c>
       <c r="O7" t="n">
         <v>0.03415517624651015</v>
@@ -2183,10 +2183,10 @@
         <v>0.07215522950234546</v>
       </c>
       <c r="M8" t="n">
-        <v>0.07215522950243121</v>
+        <v>0.07215522950243122</v>
       </c>
       <c r="N8" t="n">
-        <v>2.518621175655716</v>
+        <v>0.05429937895859584</v>
       </c>
       <c r="O8" t="n">
         <v>0.05920632171323282</v>
@@ -2274,7 +2274,7 @@
         <v>0.1176499001337205</v>
       </c>
       <c r="N9" t="n">
-        <v>2.518621175655716</v>
+        <v>0.1176499001337205</v>
       </c>
       <c r="O9" t="n">
         <v>0.1251727250538676</v>
@@ -2958,7 +2958,7 @@
         <v>0.0321465532426107</v>
       </c>
       <c r="N5" t="n">
-        <v>1.190567840093185</v>
+        <v>0.03214655324261069</v>
       </c>
       <c r="O5" t="n">
         <v>0.03214655324261069</v>
@@ -3046,7 +3046,7 @@
         <v>41.09071131655933</v>
       </c>
       <c r="N6" t="n">
-        <v>1.190567840093185</v>
+        <v>10.83303561117608</v>
       </c>
       <c r="O6" t="n">
         <v>10.83308762478382</v>
@@ -3134,7 +3134,7 @@
         <v>0.05104466452312441</v>
       </c>
       <c r="N7" t="n">
-        <v>1.190567840093185</v>
+        <v>0.05104466452312441</v>
       </c>
       <c r="O7" t="n">
         <v>0.05104377821437014</v>
@@ -3222,7 +3222,7 @@
         <v>0.09067485091213791</v>
       </c>
       <c r="N8" t="n">
-        <v>1.190567840093185</v>
+        <v>0.07108805829329902</v>
       </c>
       <c r="O8" t="n">
         <v>0.07647067895287558</v>
@@ -3310,7 +3310,7 @@
         <v>0.1675196610758571</v>
       </c>
       <c r="N9" t="n">
-        <v>1.190567840093185</v>
+        <v>0.1675196610758571</v>
       </c>
       <c r="O9" t="n">
         <v>0.1777059769582757</v>
@@ -3694,34 +3694,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6139131954078559</v>
+        <v>0.6139131954078555</v>
       </c>
       <c r="C2" t="n">
         <v>0.6150305269156652</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6141048205510169</v>
+        <v>0.6141048205510165</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04458525885673926</v>
+        <v>0.04458525885673922</v>
       </c>
       <c r="F2" t="n">
         <v>0.6287359130599492</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6158839443661773</v>
+        <v>0.6158839443661775</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6222762765088626</v>
+        <v>0.622276276508863</v>
       </c>
       <c r="I2" t="n">
         <v>0.615781583188228</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6205717994891203</v>
+        <v>0.6205717994891208</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6139974290123014</v>
+        <v>0.6139974290123016</v>
       </c>
       <c r="L2" t="n">
         <v>0.6133704357534878</v>
@@ -3730,49 +3730,49 @@
         <v>0.6176126459210581</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6166128689888211</v>
+        <v>0.6166128689888208</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6485050823805831</v>
+        <v>0.6485050823805828</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6297154763149291</v>
+        <v>0.629715476314929</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6317087891732651</v>
+        <v>0.6317087891732653</v>
       </c>
       <c r="R2" t="n">
         <v>0.6199337828083236</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6135495564386005</v>
+        <v>0.6135495564386</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6293424784115148</v>
+        <v>0.6293424784115147</v>
       </c>
       <c r="U2" t="n">
         <v>0.621778001497759</v>
       </c>
       <c r="V2" t="n">
-        <v>1.099174784330459</v>
+        <v>1.09917478433046</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6350334960119575</v>
+        <v>0.6350334960119571</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6142412985856616</v>
+        <v>0.6142412985856621</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6329126846044211</v>
+        <v>0.6329126846044214</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.6233371534839086</v>
+        <v>0.6233371534839088</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.6165766892623874</v>
+        <v>0.6165766892623875</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.6148135026153312</v>
+        <v>0.6148135026153313</v>
       </c>
     </row>
     <row r="3">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6226704638604479</v>
+        <v>0.6226704638604476</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6226704638604479</v>
+        <v>0.6226704638604476</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6226704638604479</v>
+        <v>0.6226704638604476</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0314631960823025</v>
+        <v>0.03146319608230242</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6226704638604479</v>
+        <v>0.6226704638604476</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6226704638604479</v>
+        <v>0.6226704638604476</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6226704638604479</v>
+        <v>0.6226704638604476</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6226704638604479</v>
+        <v>0.6226704638604476</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6229960071253038</v>
+        <v>0.6229960071253037</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6226704638604479</v>
+        <v>0.6226704638604476</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6226704638604479</v>
+        <v>0.6226704638604476</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6226704638604479</v>
+        <v>0.6226704638604476</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6226704638604479</v>
+        <v>0.6226704638604476</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6226704638604479</v>
+        <v>0.6226704638604476</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6226704638604479</v>
+        <v>0.6226704638604476</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6226704638604479</v>
+        <v>0.6226704638604476</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6226704638604479</v>
+        <v>0.6226704638604476</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6226704638604479</v>
+        <v>0.6226704638604476</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6226704638604479</v>
+        <v>0.6226704638604476</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6226704638604479</v>
+        <v>0.6226704638604476</v>
       </c>
       <c r="V3" t="n">
         <v>1.103010467218555</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6226704638604479</v>
+        <v>0.6226704638604476</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6226704638604479</v>
+        <v>0.6226704638604476</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.6226704638604479</v>
+        <v>0.6226704638604476</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.6226704638604479</v>
+        <v>0.6226704638604476</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.6226704638604479</v>
+        <v>0.6226704638604476</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.6226704638604479</v>
+        <v>0.6226704638604476</v>
       </c>
     </row>
     <row r="4">
@@ -3870,85 +3870,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2290085433646346</v>
+        <v>0.2290085433646379</v>
       </c>
       <c r="C4" t="n">
-        <v>0.514545562519217</v>
+        <v>0.514545562519216</v>
       </c>
       <c r="D4" t="n">
-        <v>0.300412605215255</v>
+        <v>0.300412605215253</v>
       </c>
       <c r="E4" t="n">
-        <v>3.421039034676848</v>
+        <v>3.421039034676847</v>
       </c>
       <c r="F4" t="n">
-        <v>4.102795586709949</v>
+        <v>4.102795586709941</v>
       </c>
       <c r="G4" t="n">
-        <v>0.691709705118232</v>
+        <v>0.6917097051182323</v>
       </c>
       <c r="H4" t="n">
         <v>2.571790917072606</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7521449869066051</v>
+        <v>0.7521449869066028</v>
       </c>
       <c r="J4" t="n">
         <v>1.761528782217699</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2535523161397025</v>
+        <v>0.2535523161397015</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1032772940590725</v>
+        <v>0.1032772940590698</v>
       </c>
       <c r="M4" t="n">
-        <v>1.240592638436753</v>
+        <v>1.240592638436749</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9431983735994485</v>
+        <v>0.9431983735994494</v>
       </c>
       <c r="O4" t="n">
-        <v>7.952925581011524</v>
+        <v>7.952925581011533</v>
       </c>
       <c r="P4" t="n">
-        <v>3.948447423021966</v>
+        <v>3.948447423021959</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.731161956349387</v>
+        <v>4.731161956349383</v>
       </c>
       <c r="R4" t="n">
         <v>1.891125419689492</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1437178695645847</v>
+        <v>0.143717869564586</v>
       </c>
       <c r="T4" t="n">
-        <v>4.345580171063602</v>
+        <v>4.345580171063604</v>
       </c>
       <c r="U4" t="n">
-        <v>2.144055793899971</v>
+        <v>2.144055793899994</v>
       </c>
       <c r="V4" t="n">
-        <v>2.996072061761161</v>
+        <v>2.996072061761169</v>
       </c>
       <c r="W4" t="n">
-        <v>5.600272391225815</v>
+        <v>5.600272391225813</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3321606322732821</v>
+        <v>0.3321606322732898</v>
       </c>
       <c r="Y4" t="n">
         <v>5.008890293894743</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.329033274973267</v>
+        <v>2.329033274973265</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.9179143603802352</v>
+        <v>0.9179143603802353</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.5155480056349016</v>
+        <v>0.5155480056349009</v>
       </c>
     </row>
     <row r="5">
@@ -3958,85 +3958,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02592040748245085</v>
+        <v>0.02592040748245037</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02592040748245114</v>
+        <v>0.02592040748245019</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02592040748245114</v>
+        <v>0.02592040748245019</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02592040748245114</v>
+        <v>0.02592040748245019</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02592040748245089</v>
+        <v>0.02592040748245033</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02592040748245114</v>
+        <v>0.02592040748245019</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02592040748245114</v>
+        <v>0.02592040748245019</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02592040748245114</v>
+        <v>0.02592040748245019</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0265318268398547</v>
+        <v>0.02653182683985406</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02592040748245114</v>
+        <v>0.02592040748245019</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02592040748245113</v>
+        <v>0.02592040748245024</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02592040748245114</v>
+        <v>0.02592040748245019</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9431983735994485</v>
+        <v>0.02592040748245033</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02592040748245089</v>
+        <v>0.02592040748245033</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02592040748245089</v>
+        <v>0.02592040748245033</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02592040748245089</v>
+        <v>0.02592040748245033</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02592040748245114</v>
+        <v>0.02592040748245019</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02592040748245114</v>
+        <v>0.02592040748245019</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02592040748245114</v>
+        <v>0.02592040748245019</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02724077363725304</v>
+        <v>0.02724077363725249</v>
       </c>
       <c r="V5" t="n">
         <v>0.02997767516400533</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02592040748245089</v>
+        <v>0.02592040748245033</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02592040748245085</v>
+        <v>0.02592040748245037</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.02724077363725304</v>
+        <v>0.02724077363725249</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.02592040748245114</v>
+        <v>0.02592040748245019</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02592040748245114</v>
+        <v>0.02592040748245019</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.02592040748245089</v>
+        <v>0.02592040748245033</v>
       </c>
     </row>
     <row r="6">
@@ -4046,82 +4046,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38.27690310049663</v>
+        <v>38.27690310049665</v>
       </c>
       <c r="C6" t="n">
-        <v>10.08711244501035</v>
+        <v>10.08711244501033</v>
       </c>
       <c r="D6" t="n">
-        <v>38.27690310049662</v>
+        <v>38.27690310049664</v>
       </c>
       <c r="E6" t="n">
-        <v>38.27690310049662</v>
+        <v>38.27690310049664</v>
       </c>
       <c r="F6" t="n">
-        <v>10.08711244501035</v>
+        <v>10.08711244501033</v>
       </c>
       <c r="G6" t="n">
-        <v>10.08711244501035</v>
+        <v>10.08711244501033</v>
       </c>
       <c r="H6" t="n">
-        <v>10.08711244501035</v>
+        <v>10.08711244501033</v>
       </c>
       <c r="I6" t="n">
-        <v>10.08711244501035</v>
+        <v>10.08711244501033</v>
       </c>
       <c r="J6" t="n">
-        <v>38.27751451985399</v>
+        <v>38.27751451985403</v>
       </c>
       <c r="K6" t="n">
-        <v>38.27690310049662</v>
+        <v>38.27690310049664</v>
       </c>
       <c r="L6" t="n">
-        <v>38.27690310049663</v>
+        <v>38.27690310049665</v>
       </c>
       <c r="M6" t="n">
-        <v>10.08711244501035</v>
+        <v>10.08711244501033</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9431983735994485</v>
+        <v>10.08681322568853</v>
       </c>
       <c r="O6" t="n">
-        <v>38.27931049170001</v>
+        <v>38.27931049169997</v>
       </c>
       <c r="P6" t="n">
-        <v>38.27929415702709</v>
+        <v>38.27929415702705</v>
       </c>
       <c r="Q6" t="n">
-        <v>38.27690310049662</v>
+        <v>38.27690310049664</v>
       </c>
       <c r="R6" t="n">
-        <v>10.08711244501035</v>
+        <v>10.08711244501033</v>
       </c>
       <c r="S6" t="n">
-        <v>38.27690310049662</v>
+        <v>38.27690310049664</v>
       </c>
       <c r="T6" t="n">
-        <v>10.08711244501035</v>
+        <v>10.08711244501033</v>
       </c>
       <c r="U6" t="n">
-        <v>10.08711244501035</v>
+        <v>10.08711244501033</v>
       </c>
       <c r="V6" t="n">
-        <v>38.28096036817822</v>
+        <v>38.28096036817821</v>
       </c>
       <c r="W6" t="n">
-        <v>38.27930886435541</v>
+        <v>38.27930886435539</v>
       </c>
       <c r="X6" t="n">
-        <v>10.08711244501035</v>
+        <v>10.08711244501033</v>
       </c>
       <c r="Y6" t="n">
-        <v>10.52773642173313</v>
+        <v>10.52773642173314</v>
       </c>
       <c r="Z6" t="n">
-        <v>38.27690310049662</v>
+        <v>38.27690310049664</v>
       </c>
       <c r="AA6" t="n">
-        <v>38.27690310049662</v>
+        <v>38.27690310049664</v>
       </c>
       <c r="AB6" t="n">
         <v>10.08615946235336</v>
@@ -4134,85 +4134,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04036833821406778</v>
+        <v>0.04036833821406761</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04036833821406769</v>
+        <v>0.04036833821406757</v>
       </c>
       <c r="D7" t="n">
-        <v>0.04036833821406769</v>
+        <v>0.04036833821406757</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04036833821406769</v>
+        <v>0.04036833821406757</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04036833821406769</v>
+        <v>0.04036833821406757</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04036833821406769</v>
+        <v>0.04036833821406757</v>
       </c>
       <c r="H7" t="n">
-        <v>0.04036833821406769</v>
+        <v>0.04036833821406757</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04036833821406769</v>
+        <v>0.04036833821406757</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04097975757147235</v>
+        <v>0.0409797575714715</v>
       </c>
       <c r="K7" t="n">
-        <v>0.04036833821406769</v>
+        <v>0.04036833821406757</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04036833821406778</v>
+        <v>0.04036833821406761</v>
       </c>
       <c r="M7" t="n">
-        <v>0.04036833821406769</v>
+        <v>0.04036833821406757</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9431983735994485</v>
+        <v>0.04036833821406757</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04036768624572794</v>
+        <v>0.04036768624572735</v>
       </c>
       <c r="P7" t="n">
-        <v>0.04036768624572794</v>
+        <v>0.04036768624572735</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.04036833821406769</v>
+        <v>0.04036833821406757</v>
       </c>
       <c r="R7" t="n">
-        <v>0.04036833821406769</v>
+        <v>0.04036833821406757</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04036833821406769</v>
+        <v>0.04036833821406757</v>
       </c>
       <c r="T7" t="n">
-        <v>0.04036833821406769</v>
+        <v>0.04036833821406757</v>
       </c>
       <c r="U7" t="n">
-        <v>0.04038363224321253</v>
+        <v>0.04038363224321211</v>
       </c>
       <c r="V7" t="n">
-        <v>0.04442560589562274</v>
+        <v>0.04442560589562275</v>
       </c>
       <c r="W7" t="n">
-        <v>0.04036833821406769</v>
+        <v>0.04036833821406757</v>
       </c>
       <c r="X7" t="n">
-        <v>0.04036833821406778</v>
+        <v>0.04036833821406761</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.04036833821406769</v>
+        <v>0.04036833821406757</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.04036833821406769</v>
+        <v>0.04036833821406757</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.04036833821406769</v>
+        <v>0.04036833821406757</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.04036833821406769</v>
+        <v>0.04036833821406757</v>
       </c>
     </row>
     <row r="8">
@@ -4222,85 +4222,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.05186491565937254</v>
+        <v>0.05186491565937241</v>
       </c>
       <c r="C8" t="n">
-        <v>0.07166501452779689</v>
+        <v>0.07166501452779583</v>
       </c>
       <c r="D8" t="n">
-        <v>0.07166501452779689</v>
+        <v>0.07166501452779583</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06112204595326844</v>
+        <v>0.06112204595326773</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05494953965064118</v>
+        <v>0.05494953965064074</v>
       </c>
       <c r="G8" t="n">
-        <v>0.075770694011308</v>
+        <v>0.07577069401130748</v>
       </c>
       <c r="H8" t="n">
-        <v>0.07166501452779689</v>
+        <v>0.07166501452779583</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07166501452779689</v>
+        <v>0.07166501452779583</v>
       </c>
       <c r="J8" t="n">
-        <v>0.07227643388520009</v>
+        <v>0.07227643388519991</v>
       </c>
       <c r="K8" t="n">
-        <v>0.07166501452779689</v>
+        <v>0.07166501452779583</v>
       </c>
       <c r="L8" t="n">
-        <v>0.071665014527797</v>
+        <v>0.07166501452779582</v>
       </c>
       <c r="M8" t="n">
-        <v>0.07166501452782695</v>
+        <v>0.07166501452782642</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9431983735994485</v>
+        <v>0.05631662541199917</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06053449599216183</v>
+        <v>0.06053449599216081</v>
       </c>
       <c r="P8" t="n">
-        <v>0.05950059399665847</v>
+        <v>0.05950059399665747</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.04797374432522963</v>
+        <v>0.04797374432522912</v>
       </c>
       <c r="R8" t="n">
-        <v>0.07166501452779689</v>
+        <v>0.07166501452779583</v>
       </c>
       <c r="S8" t="n">
-        <v>0.07166501452779689</v>
+        <v>0.07166501452779583</v>
       </c>
       <c r="T8" t="n">
-        <v>0.07166501452779689</v>
+        <v>0.07166501452779583</v>
       </c>
       <c r="U8" t="n">
-        <v>0.06201320827632613</v>
+        <v>0.06201320827632588</v>
       </c>
       <c r="V8" t="n">
-        <v>0.07032424686402369</v>
+        <v>0.07032424686402371</v>
       </c>
       <c r="W8" t="n">
-        <v>0.07166890578213389</v>
+        <v>0.07166890578213342</v>
       </c>
       <c r="X8" t="n">
-        <v>0.04978846270999893</v>
+        <v>0.04978846270999857</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0913729426706158</v>
+        <v>0.09137294267061551</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.05149711866028205</v>
+        <v>0.05149711866028207</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.07166501452779689</v>
+        <v>0.07166501452779583</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.09234787342306358</v>
+        <v>0.09234787342306268</v>
       </c>
     </row>
     <row r="9">
@@ -4310,85 +4310,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1008331767477557</v>
+        <v>0.1008331767477546</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1229936262506969</v>
+        <v>0.1229936262506962</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1229936262506969</v>
+        <v>0.1229936262506962</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1178791119437498</v>
+        <v>0.1178791119437493</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07190769608864288</v>
+        <v>0.07190769608864223</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1229936614136697</v>
+        <v>0.122993661413669</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1229936262506969</v>
+        <v>0.1229936262506962</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1229936262506969</v>
+        <v>0.1229936262506962</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1236050456081006</v>
+        <v>0.1236050456081003</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1229936262506969</v>
+        <v>0.1229936262506962</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1229936262506969</v>
+        <v>0.1229936262506962</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1229936262506969</v>
+        <v>0.1229936262506962</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9431983735994485</v>
+        <v>0.1229936262506962</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1303376170152799</v>
+        <v>0.1303376170152792</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1319348013575712</v>
+        <v>0.1319348013575709</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1229936614136697</v>
+        <v>0.122993661413669</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1229936262506969</v>
+        <v>0.1229936262506962</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1229936262506969</v>
+        <v>0.1229936262506962</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1229936262506969</v>
+        <v>0.1229936262506962</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1229936262506969</v>
+        <v>0.1229936262506962</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1526236187106025</v>
+        <v>0.1526236187106026</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1229936262506969</v>
+        <v>0.1229936262506962</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1229936262506969</v>
+        <v>0.1229936262506962</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.1229936262506969</v>
+        <v>0.1229936262506962</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.1096328597473089</v>
+        <v>0.1096328597473081</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.1229936262506969</v>
+        <v>0.1229936262506962</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.1229936262506969</v>
+        <v>0.1229936262506962</v>
       </c>
     </row>
     <row r="10">
@@ -4398,16 +4398,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6176183535645517</v>
+        <v>0.6176183535645513</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6111381675983886</v>
+        <v>0.6111381675983889</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6165738921204925</v>
+        <v>0.616573892120493</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.04819880298861643</v>
+        <v>-0.04819880298861658</v>
       </c>
       <c r="F10" t="n">
         <v>0.5313198115129683</v>
@@ -4416,16 +4416,16 @@
         <v>0.6059033591016967</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5690732968100923</v>
+        <v>0.5690732968100927</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6067820198988554</v>
+        <v>0.6067820198988547</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5805353070573164</v>
+        <v>0.5805353070573163</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6171951753335123</v>
+        <v>0.6171951753335126</v>
       </c>
       <c r="L10" t="n">
         <v>0.6208588332713245</v>
@@ -4434,46 +4434,46 @@
         <v>0.5961278464626097</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6017949289267043</v>
+        <v>0.6017949289267046</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4115956203251657</v>
+        <v>0.4115956203251659</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5234118546961142</v>
+        <v>0.5234118546961143</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.5131788084773165</v>
+        <v>0.5131788084773166</v>
       </c>
       <c r="R10" t="n">
         <v>0.5825891609395997</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6197906568583809</v>
+        <v>0.619790656858381</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5273793785705718</v>
+        <v>0.5273793785705708</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5711032172836464</v>
+        <v>0.5711032172836469</v>
       </c>
       <c r="V10" t="n">
         <v>1.024170475905395</v>
       </c>
       <c r="W10" t="n">
-        <v>0.4930070311750319</v>
+        <v>0.4930070311750321</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6157678213854226</v>
+        <v>0.6157678213854224</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5057131966957945</v>
+        <v>0.5057131966957941</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.5616213075561522</v>
+        <v>0.5616213075561521</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.6019555040285592</v>
+        <v>0.6019555040285588</v>
       </c>
       <c r="AB10" t="n">
         <v>0.61242510365643</v>
@@ -4486,85 +4486,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6116144691231027</v>
+        <v>0.6116144691231029</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6097832953651811</v>
+        <v>0.6097832953651812</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6113308609807167</v>
+        <v>0.611330860980717</v>
       </c>
       <c r="E11" t="n">
-        <v>0.008338795411743122</v>
+        <v>0.008338795411743056</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5871710751245895</v>
+        <v>0.5871710751245907</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6082548582673537</v>
+        <v>0.608254858267354</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5978893946969144</v>
+        <v>0.5978893946969145</v>
       </c>
       <c r="I11" t="n">
         <v>0.6085522905522374</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6012520456439631</v>
+        <v>0.6012520456439632</v>
       </c>
       <c r="K11" t="n">
-        <v>0.611506155283837</v>
+        <v>0.6115061552838369</v>
       </c>
       <c r="L11" t="n">
         <v>0.6125461380621123</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6055356704187391</v>
+        <v>0.6055356704187385</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6071144340675853</v>
+        <v>0.6071144340675857</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5524653559164149</v>
+        <v>0.5524653559164153</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5845524928267385</v>
+        <v>0.5845524928267383</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.5818897370447383</v>
+        <v>0.5818897370447381</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6016966622478044</v>
+        <v>0.6016966622478043</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6122392350752601</v>
+        <v>0.6122392350752599</v>
       </c>
       <c r="T11" t="n">
         <v>0.5859847309299503</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5983147399702503</v>
+        <v>0.5983147399702501</v>
       </c>
       <c r="V11" t="n">
         <v>1.063302337034826</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5760362209272516</v>
+        <v>0.5760362209272513</v>
       </c>
       <c r="X11" t="n">
-        <v>0.6111005742621091</v>
+        <v>0.6111005742621095</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.579696755323809</v>
+        <v>0.5796967553238092</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.5955595928133366</v>
+        <v>0.5955595928133371</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.6071513165242175</v>
+        <v>0.6071513165242181</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.6101518310724776</v>
+        <v>0.6101518310724773</v>
       </c>
     </row>
   </sheetData>
@@ -4730,85 +4730,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6072734707937222</v>
+        <v>0.6072734707937227</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6073967099973062</v>
+        <v>0.6073967099973065</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6097197867435885</v>
+        <v>0.6097197867435896</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02893577687835906</v>
+        <v>0.02893577687835909</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6286297781684114</v>
+        <v>0.6286297781684125</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6091745379062555</v>
+        <v>0.6091745379062571</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6148911154108476</v>
+        <v>0.6148911154108478</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6175542645752677</v>
+        <v>0.6175542645752686</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6128364515282411</v>
+        <v>0.612836451528242</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6150359594881868</v>
+        <v>0.6150359594881878</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6139657198463361</v>
+        <v>0.6139657198463363</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6160078760023565</v>
+        <v>0.6160078760023574</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6088027765826303</v>
+        <v>0.608802776582631</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6315609731139266</v>
+        <v>0.6315609731139272</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6184319629366964</v>
+        <v>0.6184319629366973</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6282312757335149</v>
+        <v>0.6282312757335151</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6154559746487759</v>
+        <v>0.615455974648776</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6134987474801036</v>
+        <v>0.6134987474801056</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6242030225071079</v>
+        <v>0.6242030225071097</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6102020805832375</v>
+        <v>0.6102020805832384</v>
       </c>
       <c r="V2" t="n">
         <v>1.07902351386043</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6225165332380673</v>
+        <v>0.6225165332380679</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6093584009270003</v>
+        <v>0.6093584009270013</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6110956378232719</v>
+        <v>0.6110956378232725</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.6091497500696093</v>
+        <v>0.6091497500696101</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.6097921741063587</v>
+        <v>0.6097921741063591</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.6074093073916417</v>
+        <v>0.607409307391643</v>
       </c>
     </row>
     <row r="3">
@@ -4818,85 +4818,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6155009164550038</v>
+        <v>0.6155009164550057</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6155009164550038</v>
+        <v>0.6155009164550057</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6155009164550038</v>
+        <v>0.6155009164550057</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0248728545300819</v>
+        <v>0.02487285453008205</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6155009164550038</v>
+        <v>0.6155009164550057</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6155009164550038</v>
+        <v>0.6155009164550057</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6155009164550038</v>
+        <v>0.6155009164550057</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6155009164550038</v>
+        <v>0.6155009164550057</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6154637104971813</v>
+        <v>0.6154637104971825</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6155009164550038</v>
+        <v>0.6155009164550057</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6155009164550038</v>
+        <v>0.6155009164550057</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6155009164550038</v>
+        <v>0.6155009164550057</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6155009164550038</v>
+        <v>0.6155009164550057</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6155009164550038</v>
+        <v>0.6155009164550057</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6155009164550038</v>
+        <v>0.6155009164550057</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6155009164550038</v>
+        <v>0.6155009164550057</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6155009164550038</v>
+        <v>0.6155009164550057</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6155009164550038</v>
+        <v>0.6155009164550057</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6155009164550038</v>
+        <v>0.6155009164550057</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6155009164550038</v>
+        <v>0.6155009164550057</v>
       </c>
       <c r="V3" t="n">
-        <v>1.091997435066519</v>
+        <v>1.091997435066518</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6155009164550038</v>
+        <v>0.6155009164550057</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6155009164550038</v>
+        <v>0.6155009164550057</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.6155009164550038</v>
+        <v>0.6155009164550057</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.6155009164550038</v>
+        <v>0.6155009164550057</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.6155009164550038</v>
+        <v>0.6155009164550057</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.6155009164550038</v>
+        <v>0.6155009164550057</v>
       </c>
     </row>
     <row r="4">
@@ -4906,85 +4906,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3209240444825594</v>
+        <v>0.320924044482562</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3721260972899307</v>
+        <v>0.3721260972899308</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9638139947146969</v>
+        <v>0.9638139947146934</v>
       </c>
       <c r="E4" t="n">
-        <v>1.046302645188631</v>
+        <v>1.046302645188633</v>
       </c>
       <c r="F4" t="n">
-        <v>5.859307011424292</v>
+        <v>5.859307011424291</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7495353114246501</v>
+        <v>0.7495353114246518</v>
       </c>
       <c r="H4" t="n">
         <v>2.494201730570359</v>
       </c>
       <c r="I4" t="n">
-        <v>3.0529467932986</v>
+        <v>3.052946793298602</v>
       </c>
       <c r="J4" t="n">
-        <v>1.711933049846844</v>
+        <v>1.711933049846841</v>
       </c>
       <c r="K4" t="n">
-        <v>2.132980982803451</v>
+        <v>2.132980982803459</v>
       </c>
       <c r="L4" t="n">
-        <v>1.940042735320843</v>
+        <v>1.940042735320838</v>
       </c>
       <c r="M4" t="n">
         <v>2.579546982262471</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7543655786914194</v>
+        <v>0.7543655786914163</v>
       </c>
       <c r="O4" t="n">
-        <v>5.757952145492964</v>
+        <v>5.757952145492967</v>
       </c>
       <c r="P4" t="n">
-        <v>2.847048646605185</v>
+        <v>2.847048646605179</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.484323893963902</v>
+        <v>5.4843238939639</v>
       </c>
       <c r="R4" t="n">
-        <v>2.595387256870603</v>
+        <v>2.595387256870611</v>
       </c>
       <c r="S4" t="n">
-        <v>1.779907064986803</v>
+        <v>1.779907064986799</v>
       </c>
       <c r="T4" t="n">
-        <v>4.864753075744252</v>
+        <v>4.864753075744265</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01183393650977</v>
+        <v>1.011833936509771</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9158066116376822</v>
+        <v>0.9158066116376801</v>
       </c>
       <c r="W4" t="n">
-        <v>4.225957864500335</v>
+        <v>4.225957864500322</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8704982774137102</v>
+        <v>0.8704982774137094</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.334526208606015</v>
+        <v>1.334526208606012</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.6953220882970521</v>
+        <v>0.6953220882970537</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.9959056184409159</v>
+        <v>0.9959056184409192</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.4174277730304076</v>
+        <v>0.4174277730304086</v>
       </c>
     </row>
     <row r="5">
@@ -4994,85 +4994,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01616434546619042</v>
+        <v>0.01616434546619156</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0161643454661903</v>
+        <v>0.01616434546619182</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0161643454661903</v>
+        <v>0.01616434546619182</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0161643454661903</v>
+        <v>0.01616434546619182</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01616434546619017</v>
+        <v>0.01616434546619086</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0161643454661903</v>
+        <v>0.01616434546619182</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0161643454661903</v>
+        <v>0.01616434546619182</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0161643454661903</v>
+        <v>0.01616434546619182</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01670187189129365</v>
+        <v>0.01670187189129437</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0161643454661903</v>
+        <v>0.01616434546619182</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01616434546619043</v>
+        <v>0.01616434546619188</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0161643454661903</v>
+        <v>0.01616434546619182</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7543655786914194</v>
+        <v>0.01616434546619086</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01616434546619017</v>
+        <v>0.01616434546619086</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01616434546619017</v>
+        <v>0.01616434546619086</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01616434546619017</v>
+        <v>0.01616434546619086</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0161643454661903</v>
+        <v>0.01616434546619182</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0161643454661903</v>
+        <v>0.01616434546619182</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0161643454661903</v>
+        <v>0.01616434546619182</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01511735814950438</v>
+        <v>0.01511735814950561</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01974937080556673</v>
+        <v>0.01974937080556672</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01616434546619017</v>
+        <v>0.01616434546619086</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01616434546619042</v>
+        <v>0.01616434546619084</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01511735814950438</v>
+        <v>0.01511735814950561</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0161643454661903</v>
+        <v>0.01616434546619182</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0161643454661903</v>
+        <v>0.01616434546619182</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01616434546619017</v>
+        <v>0.01616434546619086</v>
       </c>
     </row>
     <row r="6">
@@ -5088,10 +5088,10 @@
         <v>10.07008697083318</v>
       </c>
       <c r="D6" t="n">
-        <v>38.25701044128687</v>
+        <v>38.25701044128691</v>
       </c>
       <c r="E6" t="n">
-        <v>38.25701044128687</v>
+        <v>38.25701044128691</v>
       </c>
       <c r="F6" t="n">
         <v>10.07008697083318</v>
@@ -5100,16 +5100,16 @@
         <v>10.07008697083318</v>
       </c>
       <c r="H6" t="n">
-        <v>38.25701044128687</v>
+        <v>38.25701044128691</v>
       </c>
       <c r="I6" t="n">
         <v>10.07008697083318</v>
       </c>
       <c r="J6" t="n">
-        <v>38.25754796771201</v>
+        <v>38.25754796771199</v>
       </c>
       <c r="K6" t="n">
-        <v>38.25701044128687</v>
+        <v>38.25701044128691</v>
       </c>
       <c r="L6" t="n">
         <v>10.07008697083318</v>
@@ -5118,49 +5118,49 @@
         <v>10.07008697083318</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7543655786914194</v>
+        <v>10.07009598753208</v>
       </c>
       <c r="O6" t="n">
         <v>10.07014290909392</v>
       </c>
       <c r="P6" t="n">
-        <v>38.25943435641783</v>
+        <v>38.25943435641785</v>
       </c>
       <c r="Q6" t="n">
-        <v>38.25701044128687</v>
+        <v>38.25701044128691</v>
       </c>
       <c r="R6" t="n">
-        <v>38.25701044128687</v>
+        <v>38.25701044128691</v>
       </c>
       <c r="S6" t="n">
         <v>10.07008697083318</v>
       </c>
       <c r="T6" t="n">
-        <v>38.25701044128687</v>
+        <v>38.25701044128691</v>
       </c>
       <c r="U6" t="n">
-        <v>38.25701044128687</v>
+        <v>38.25701044128691</v>
       </c>
       <c r="V6" t="n">
-        <v>10.07367199617256</v>
+        <v>10.07367199617255</v>
       </c>
       <c r="W6" t="n">
-        <v>10.58255280922414</v>
+        <v>10.58255280922412</v>
       </c>
       <c r="X6" t="n">
         <v>10.07008697083318</v>
       </c>
       <c r="Y6" t="n">
-        <v>10.51036741485855</v>
+        <v>10.51036741485854</v>
       </c>
       <c r="Z6" t="n">
         <v>10.07008697083318</v>
       </c>
       <c r="AA6" t="n">
-        <v>38.25701044128687</v>
+        <v>38.25701044128691</v>
       </c>
       <c r="AB6" t="n">
-        <v>10.06987142208493</v>
+        <v>10.06987142208494</v>
       </c>
     </row>
     <row r="7">
@@ -5170,85 +5170,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02734576235536054</v>
+        <v>0.02734576235536189</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02734576235536031</v>
+        <v>0.02734576235536182</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02734576235536031</v>
+        <v>0.02734576235536182</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02734576235536031</v>
+        <v>0.02734576235536182</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02734576235536031</v>
+        <v>0.02734576235536182</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02734576235536031</v>
+        <v>0.02734576235536182</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02734576235536031</v>
+        <v>0.02734576235536182</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02734576235536031</v>
+        <v>0.02734576235536182</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02788328878046373</v>
+        <v>0.02788328878046437</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02734576235536031</v>
+        <v>0.02734576235536182</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02734576235536055</v>
+        <v>0.02734576235536189</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02734576235536031</v>
+        <v>0.02734576235536182</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7543655786914194</v>
+        <v>0.02734576235536182</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02734545138979983</v>
+        <v>0.02734545138980094</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02734545138979983</v>
+        <v>0.02734545138980094</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.02734576235536031</v>
+        <v>0.02734576235536182</v>
       </c>
       <c r="R7" t="n">
-        <v>0.02734576235536031</v>
+        <v>0.02734576235536182</v>
       </c>
       <c r="S7" t="n">
-        <v>0.02734576235536031</v>
+        <v>0.02734576235536182</v>
       </c>
       <c r="T7" t="n">
-        <v>0.02734576235536031</v>
+        <v>0.02734576235536182</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02711581887717615</v>
+        <v>0.0271158188771766</v>
       </c>
       <c r="V7" t="n">
-        <v>0.03093078769473679</v>
+        <v>0.03093078769473668</v>
       </c>
       <c r="W7" t="n">
-        <v>0.02734576235536031</v>
+        <v>0.02734576235536182</v>
       </c>
       <c r="X7" t="n">
-        <v>0.02734576235536055</v>
+        <v>0.02734576235536189</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.02734576235536031</v>
+        <v>0.02734576235536182</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.02734576235536031</v>
+        <v>0.02734576235536182</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.02734576235536031</v>
+        <v>0.02734576235536182</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.02734576235536031</v>
+        <v>0.02734576235536182</v>
       </c>
     </row>
     <row r="8">
@@ -5258,85 +5258,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03796104621691292</v>
+        <v>0.03796104621691344</v>
       </c>
       <c r="C8" t="n">
-        <v>0.054719270719971</v>
+        <v>0.05471927071997217</v>
       </c>
       <c r="D8" t="n">
-        <v>0.054719270719971</v>
+        <v>0.05471927071997217</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04579601051439569</v>
+        <v>0.04579601051439666</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04057178173373022</v>
+        <v>0.04057178173373088</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0581941977382057</v>
+        <v>0.05819419773820667</v>
       </c>
       <c r="H8" t="n">
-        <v>0.054719270719971</v>
+        <v>0.05471927071997217</v>
       </c>
       <c r="I8" t="n">
-        <v>0.054719270719971</v>
+        <v>0.05471927071997217</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05525679714507459</v>
+        <v>0.05525679714507484</v>
       </c>
       <c r="K8" t="n">
-        <v>0.054719270719971</v>
+        <v>0.05471927071997217</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05471927071997113</v>
+        <v>0.05471927071997223</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05471927072003844</v>
+        <v>0.05471927072003944</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7543655786914194</v>
+        <v>0.04172884313298845</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04529872541347627</v>
+        <v>0.04529872541347755</v>
       </c>
       <c r="P8" t="n">
-        <v>0.04442366100754895</v>
+        <v>0.04442366100755026</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.03466767262175593</v>
+        <v>0.03466767262175707</v>
       </c>
       <c r="R8" t="n">
-        <v>0.054719270719971</v>
+        <v>0.05471927071997217</v>
       </c>
       <c r="S8" t="n">
-        <v>0.054719270719971</v>
+        <v>0.05471927071997217</v>
       </c>
       <c r="T8" t="n">
-        <v>0.054719270719971</v>
+        <v>0.05471927071997217</v>
       </c>
       <c r="U8" t="n">
         <v>0.04636184543262838</v>
       </c>
       <c r="V8" t="n">
-        <v>0.05352773641597871</v>
+        <v>0.05352773641597872</v>
       </c>
       <c r="W8" t="n">
-        <v>0.05472256416330463</v>
+        <v>0.0547225641633054</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0362035971793646</v>
+        <v>0.03620359717936596</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.07107715486305544</v>
+        <v>0.07107715486305648</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03764975359546334</v>
+        <v>0.03764975359546475</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.054719270719971</v>
+        <v>0.05471927071997217</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.07222463748742654</v>
+        <v>0.07222463748742723</v>
       </c>
     </row>
     <row r="9">
@@ -5346,85 +5346,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0672831736332843</v>
+        <v>0.06728317363328498</v>
       </c>
       <c r="C9" t="n">
-        <v>0.08268643138082665</v>
+        <v>0.08268643138082793</v>
       </c>
       <c r="D9" t="n">
-        <v>0.08268643138082665</v>
+        <v>0.08268643138082793</v>
       </c>
       <c r="E9" t="n">
-        <v>0.07913142407182211</v>
+        <v>0.0791314240718238</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04717771535459784</v>
+        <v>0.04717771535459932</v>
       </c>
       <c r="G9" t="n">
-        <v>0.08268643365640371</v>
+        <v>0.08268643365640402</v>
       </c>
       <c r="H9" t="n">
-        <v>0.08268643138082665</v>
+        <v>0.08268643138082793</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08268643138082665</v>
+        <v>0.08268643138082793</v>
       </c>
       <c r="J9" t="n">
-        <v>0.08322395780593035</v>
+        <v>0.08322395780593064</v>
       </c>
       <c r="K9" t="n">
-        <v>0.08268643138082665</v>
+        <v>0.08268643138082793</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08268643138082672</v>
+        <v>0.0826864313808279</v>
       </c>
       <c r="M9" t="n">
-        <v>0.08268643138082665</v>
+        <v>0.08268643138082793</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7543655786914194</v>
+        <v>0.08268643138082793</v>
       </c>
       <c r="O9" t="n">
-        <v>0.08779105385921995</v>
+        <v>0.08779105385922131</v>
       </c>
       <c r="P9" t="n">
-        <v>0.08890122117279931</v>
+        <v>0.08890122117279968</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.08268643365640371</v>
+        <v>0.08268643365640402</v>
       </c>
       <c r="R9" t="n">
-        <v>0.08268643138082665</v>
+        <v>0.08268643138082793</v>
       </c>
       <c r="S9" t="n">
-        <v>0.08268643138082665</v>
+        <v>0.08268643138082793</v>
       </c>
       <c r="T9" t="n">
-        <v>0.08268643138082665</v>
+        <v>0.08268643138082793</v>
       </c>
       <c r="U9" t="n">
-        <v>0.08268643138082665</v>
+        <v>0.08268643138082793</v>
       </c>
       <c r="V9" t="n">
         <v>0.1040464495056218</v>
       </c>
       <c r="W9" t="n">
-        <v>0.08268643138082665</v>
+        <v>0.08268643138082793</v>
       </c>
       <c r="X9" t="n">
-        <v>0.08268643138082672</v>
+        <v>0.0826864313808279</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.08268643138082665</v>
+        <v>0.08268643138082793</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.07339963757378733</v>
+        <v>0.07339963757378812</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.08268643138082665</v>
+        <v>0.08268643138082793</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.08268643138082665</v>
+        <v>0.08268643138082793</v>
       </c>
     </row>
     <row r="10">
@@ -5434,85 +5434,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6076685137659618</v>
+        <v>0.607668513765963</v>
       </c>
       <c r="C10" t="n">
-        <v>0.607057653105974</v>
+        <v>0.6070576531059754</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5934599493361226</v>
+        <v>0.5934599493361248</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0009268441098603876</v>
+        <v>-0.0009268441098597832</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4833421888338434</v>
+        <v>0.4833421888338446</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5963693834430892</v>
+        <v>0.5963693834430894</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5635217053302801</v>
+        <v>0.5635217053302811</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5476964300805711</v>
+        <v>0.5476964300805713</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5747374170547184</v>
+        <v>0.5747374170547198</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5622448893536227</v>
+        <v>0.562244889353624</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5681542308930448</v>
+        <v>0.5681542308930464</v>
       </c>
       <c r="M10" t="n">
-        <v>0.556850728445287</v>
+        <v>0.5568507284452888</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5987607990273465</v>
+        <v>0.5987607990273472</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4630120764802509</v>
+        <v>0.4630120764802517</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5411378724192721</v>
+        <v>0.5411378724192729</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4846946758152784</v>
+        <v>0.4846946758152795</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5600793286259048</v>
+        <v>0.560079328625905</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5707718214813281</v>
+        <v>0.5707718214813295</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5086918042312882</v>
+        <v>0.5086918042312886</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5903791956063644</v>
+        <v>0.590379195606365</v>
       </c>
       <c r="V10" t="n">
         <v>1.0680582965966</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5177665579353735</v>
+        <v>0.5177665579353747</v>
       </c>
       <c r="X10" t="n">
-        <v>0.5955575975898282</v>
+        <v>0.5955575975898287</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5852213902211963</v>
+        <v>0.5852213902211975</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.5965272561756207</v>
+        <v>0.5965272561756219</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.5928838142997561</v>
+        <v>0.5928838142997566</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.606995596326075</v>
+        <v>0.6069955963260758</v>
       </c>
     </row>
     <row r="11">
@@ -5522,85 +5522,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6037097026098206</v>
+        <v>0.6037097026098215</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6035549982664135</v>
+        <v>0.6035549982664142</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5996910764641034</v>
+        <v>0.5996910764641042</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01719683177842399</v>
+        <v>0.01719683177842435</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5684971359359081</v>
+        <v>0.5684971359359094</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6004696294172568</v>
+        <v>0.6004696294172576</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5912404087011807</v>
+        <v>0.5912404087011812</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5867030071948243</v>
+        <v>0.5867030071948242</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5943058582249243</v>
+        <v>0.5943058582249254</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5908042974401706</v>
+        <v>0.5908042974401712</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5924228270307108</v>
+        <v>0.5924228270307117</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5893218535508757</v>
+        <v>0.5893218535508764</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6011859698054577</v>
+        <v>0.6011859698054582</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5621780649723144</v>
+        <v>0.562178064972316</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5845965409194785</v>
+        <v>0.5845965409194787</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.5687140193876853</v>
+        <v>0.568714019387686</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5902389755684144</v>
+        <v>0.590238975568415</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5931468667239141</v>
+        <v>0.5931468667239153</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5756045360648736</v>
+        <v>0.5756045360648747</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5987716175389317</v>
+        <v>0.598771617538932</v>
       </c>
       <c r="V11" t="n">
-        <v>1.068131129567109</v>
+        <v>1.068131129567111</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5780470886507151</v>
+        <v>0.5780470886507155</v>
       </c>
       <c r="X11" t="n">
-        <v>0.6002841272877593</v>
+        <v>0.6002841272877605</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.5973183568917645</v>
+        <v>0.5973183568917654</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.6005166741770231</v>
+        <v>0.6005166741770235</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.5995013205492932</v>
+        <v>0.5995013205492939</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.6035393596281324</v>
+        <v>0.6035393596281339</v>
       </c>
     </row>
   </sheetData>
@@ -6066,7 +6066,7 @@
         <v>0.03529560009074039</v>
       </c>
       <c r="N5" t="n">
-        <v>4.124552008383038</v>
+        <v>0.03529560009074061</v>
       </c>
       <c r="O5" t="n">
         <v>0.03529560009074061</v>
@@ -6154,7 +6154,7 @@
         <v>41.10419794592597</v>
       </c>
       <c r="N6" t="n">
-        <v>4.124552008383038</v>
+        <v>10.83974883676957</v>
       </c>
       <c r="O6" t="n">
         <v>41.1072883799874</v>
@@ -6242,7 +6242,7 @@
         <v>0.05972988556488508</v>
       </c>
       <c r="N7" t="n">
-        <v>4.124552008383038</v>
+        <v>0.05972988556488508</v>
       </c>
       <c r="O7" t="n">
         <v>0.05972911149624499</v>
@@ -6330,7 +6330,7 @@
         <v>0.1129635024998531</v>
       </c>
       <c r="N8" t="n">
-        <v>4.124552008383038</v>
+        <v>0.08716220664020008</v>
       </c>
       <c r="O8" t="n">
         <v>0.09425262675129882</v>
@@ -6418,7 +6418,7 @@
         <v>0.2136541640041341</v>
       </c>
       <c r="N9" t="n">
-        <v>4.124552008383038</v>
+        <v>0.2136541640041341</v>
       </c>
       <c r="O9" t="n">
         <v>0.2270338946946261</v>
@@ -6808,7 +6808,7 @@
         <v>0.6165122044295556</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6153407796162815</v>
+        <v>0.6153407796162814</v>
       </c>
       <c r="E2" t="n">
         <v>0.03902585650695659</v>
@@ -6817,31 +6817,31 @@
         <v>0.6298294345790045</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6248297930358983</v>
+        <v>0.6248297930358981</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6175534671672295</v>
+        <v>0.6175534671672294</v>
       </c>
       <c r="I2" t="n">
         <v>0.6165165277292337</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6270428674156496</v>
+        <v>0.6270428674156499</v>
       </c>
       <c r="K2" t="n">
         <v>0.6158759975796966</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6152553038653301</v>
+        <v>0.61525530386533</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6332124583279224</v>
+        <v>0.6332124583279222</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6271963346972477</v>
+        <v>0.6271963346972476</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6707000382419552</v>
+        <v>0.670700038241955</v>
       </c>
       <c r="P2" t="n">
         <v>0.6500805022850058</v>
@@ -6856,7 +6856,7 @@
         <v>0.6159673420400612</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6323266499932202</v>
+        <v>0.6323266499932203</v>
       </c>
       <c r="U2" t="n">
         <v>0.6301703552335441</v>
@@ -6871,13 +6871,13 @@
         <v>0.6315193219475264</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6391994799280916</v>
+        <v>0.6391994799280918</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.6218148832581948</v>
+        <v>0.6218148832581949</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.6176547743371652</v>
+        <v>0.6176547743371651</v>
       </c>
       <c r="AB2" t="n">
         <v>0.6320417428837847</v>
@@ -6890,85 +6890,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6242610785249174</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6242610785249174</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6242610785249174</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="E3" t="n">
         <v>0.03030757540724199</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6242610785249174</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6242610785249174</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6242610785249174</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6242610785249174</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="J3" t="n">
         <v>0.6244226532489505</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6242610785249174</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6242610785249174</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6242610785249174</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6242610785249174</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6242610785249174</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6242610785249174</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6242610785249174</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6242610785249174</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6242610785249174</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6242610785249174</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6242610785249174</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="V3" t="n">
         <v>1.103687899720697</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6242610785249174</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6242610785249174</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.6242610785249174</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.6242610785249174</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.6242610785249174</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.6242610785249174</v>
+        <v>0.6242610785249173</v>
       </c>
     </row>
     <row r="4">
@@ -6981,7 +6981,7 @@
         <v>0.09914276234670488</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4912099720263997</v>
+        <v>0.4912099720263996</v>
       </c>
       <c r="D4" t="n">
         <v>0.2073354258649341</v>
@@ -7005,13 +7005,13 @@
         <v>2.780419812118907</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3252650280762219</v>
+        <v>0.325265028076222</v>
       </c>
       <c r="L4" t="n">
         <v>0.17436187583225</v>
       </c>
       <c r="M4" t="n">
-        <v>4.137859763199257</v>
+        <v>4.137859763199259</v>
       </c>
       <c r="N4" t="n">
         <v>3.087696440115822</v>
@@ -7066,7 +7066,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02680054036059761</v>
+        <v>0.0268005403605976</v>
       </c>
       <c r="C5" t="n">
         <v>0.0268005403605976</v>
@@ -7102,7 +7102,7 @@
         <v>0.0268005403605976</v>
       </c>
       <c r="N5" t="n">
-        <v>3.087696440115822</v>
+        <v>0.02680054036059717</v>
       </c>
       <c r="O5" t="n">
         <v>0.02680054036059717</v>
@@ -7154,7 +7154,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38.28187905185669</v>
+        <v>38.28187905185671</v>
       </c>
       <c r="C6" t="n">
         <v>10.08691841125872</v>
@@ -7166,31 +7166,31 @@
         <v>10.08691841125872</v>
       </c>
       <c r="F6" t="n">
-        <v>38.28187905185669</v>
+        <v>38.28187905185671</v>
       </c>
       <c r="G6" t="n">
-        <v>38.28187905185669</v>
+        <v>38.28187905185671</v>
       </c>
       <c r="H6" t="n">
-        <v>38.28187905185669</v>
+        <v>38.28187905185671</v>
       </c>
       <c r="I6" t="n">
-        <v>38.28187905185669</v>
+        <v>38.28187905185671</v>
       </c>
       <c r="J6" t="n">
         <v>38.28245717957703</v>
       </c>
       <c r="K6" t="n">
-        <v>38.28187905185669</v>
+        <v>38.28187905185671</v>
       </c>
       <c r="L6" t="n">
         <v>10.08691841125872</v>
       </c>
       <c r="M6" t="n">
-        <v>38.28187905185669</v>
+        <v>38.28187905185671</v>
       </c>
       <c r="N6" t="n">
-        <v>3.087696440115822</v>
+        <v>10.08704278484853</v>
       </c>
       <c r="O6" t="n">
         <v>38.28478021781243</v>
@@ -7199,13 +7199,13 @@
         <v>9.505806793573507</v>
       </c>
       <c r="Q6" t="n">
-        <v>38.28187905185669</v>
+        <v>38.28187905185671</v>
       </c>
       <c r="R6" t="n">
         <v>10.08691841125872</v>
       </c>
       <c r="S6" t="n">
-        <v>38.28187905185669</v>
+        <v>38.28187905185671</v>
       </c>
       <c r="T6" t="n">
         <v>10.08691841125872</v>
@@ -7220,7 +7220,7 @@
         <v>10.59999491777172</v>
       </c>
       <c r="X6" t="n">
-        <v>38.28187905185669</v>
+        <v>38.28187905185671</v>
       </c>
       <c r="Y6" t="n">
         <v>10.52782809446125</v>
@@ -7229,7 +7229,7 @@
         <v>10.08691841125872</v>
       </c>
       <c r="AA6" t="n">
-        <v>38.28187905185669</v>
+        <v>38.28187905185671</v>
       </c>
       <c r="AB6" t="n">
         <v>10.08764511302372</v>
@@ -7242,43 +7242,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04412020698237619</v>
+        <v>0.0441202069823762</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04412020698237619</v>
+        <v>0.0441202069823762</v>
       </c>
       <c r="D7" t="n">
-        <v>0.04412020698237619</v>
+        <v>0.0441202069823762</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04412020698237619</v>
+        <v>0.0441202069823762</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04412020698237619</v>
+        <v>0.0441202069823762</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04412020698237619</v>
+        <v>0.0441202069823762</v>
       </c>
       <c r="H7" t="n">
-        <v>0.04412020698237619</v>
+        <v>0.0441202069823762</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04412020698237619</v>
+        <v>0.0441202069823762</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04469833470277818</v>
+        <v>0.04469833470277817</v>
       </c>
       <c r="K7" t="n">
-        <v>0.04412020698237619</v>
+        <v>0.0441202069823762</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04412020698237619</v>
+        <v>0.0441202069823762</v>
       </c>
       <c r="M7" t="n">
-        <v>0.04412020698237619</v>
+        <v>0.0441202069823762</v>
       </c>
       <c r="N7" t="n">
-        <v>3.087696440115822</v>
+        <v>0.0441202069823762</v>
       </c>
       <c r="O7" t="n">
         <v>0.04411961547761301</v>
@@ -7287,16 +7287,16 @@
         <v>0.04411961547761301</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.04412020698237619</v>
+        <v>0.0441202069823762</v>
       </c>
       <c r="R7" t="n">
-        <v>0.04412020698237619</v>
+        <v>0.0441202069823762</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04412020698237619</v>
+        <v>0.0441202069823762</v>
       </c>
       <c r="T7" t="n">
-        <v>0.04412020698237619</v>
+        <v>0.0441202069823762</v>
       </c>
       <c r="U7" t="n">
         <v>0.04403196392190632</v>
@@ -7305,22 +7305,22 @@
         <v>0.0479648586511565</v>
       </c>
       <c r="W7" t="n">
-        <v>0.04412020698237619</v>
+        <v>0.0441202069823762</v>
       </c>
       <c r="X7" t="n">
-        <v>0.04412020698237619</v>
+        <v>0.0441202069823762</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.04412020698237619</v>
+        <v>0.0441202069823762</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.04412020698237619</v>
+        <v>0.0441202069823762</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.04412020698237619</v>
+        <v>0.0441202069823762</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.04412020698237619</v>
+        <v>0.0441202069823762</v>
       </c>
     </row>
     <row r="8">
@@ -7330,7 +7330,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.05873873656429766</v>
+        <v>0.05873873656429765</v>
       </c>
       <c r="C8" t="n">
         <v>0.08290647494121249</v>
@@ -7366,7 +7366,7 @@
         <v>0.08290647494121837</v>
       </c>
       <c r="N8" t="n">
-        <v>3.087696440115822</v>
+        <v>0.06417243451744861</v>
       </c>
       <c r="O8" t="n">
         <v>0.06932071147679042</v>
@@ -7387,13 +7387,13 @@
         <v>0.08290647494121249</v>
       </c>
       <c r="U8" t="n">
-        <v>0.07104259658231378</v>
+        <v>0.07104259658231377</v>
       </c>
       <c r="V8" t="n">
         <v>0.08007079691020559</v>
       </c>
       <c r="W8" t="n">
-        <v>0.08291122456684426</v>
+        <v>0.08291122456684424</v>
       </c>
       <c r="X8" t="n">
         <v>0.05620424560630946</v>
@@ -7454,7 +7454,7 @@
         <v>0.1445564523732746</v>
       </c>
       <c r="N9" t="n">
-        <v>3.087696440115822</v>
+        <v>0.1445564523732746</v>
       </c>
       <c r="O9" t="n">
         <v>0.1534484906209455</v>
@@ -7512,7 +7512,7 @@
         <v>0.61330849307332</v>
       </c>
       <c r="D10" t="n">
-        <v>0.620182851947756</v>
+        <v>0.6201828519477559</v>
       </c>
       <c r="E10" t="n">
         <v>-0.02313590818508258</v>
@@ -7521,7 +7521,7 @@
         <v>0.5357491944139207</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5637007517980497</v>
+        <v>0.5637007517980496</v>
       </c>
       <c r="H10" t="n">
         <v>0.6073369607800398</v>
@@ -7530,10 +7530,10 @@
         <v>0.6133164204619049</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5521040307690702</v>
+        <v>0.5521040307690703</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6170375517601056</v>
+        <v>0.6170375517601058</v>
       </c>
       <c r="L10" t="n">
         <v>0.620650239908667</v>
@@ -7542,7 +7542,7 @@
         <v>0.5159117247447117</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5504274599348997</v>
+        <v>0.5504274599348998</v>
       </c>
       <c r="O10" t="n">
         <v>0.2904138745522095</v>
@@ -7551,10 +7551,10 @@
         <v>0.4130291460120593</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.5588994590340716</v>
+        <v>0.5588994590340717</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6185362497102467</v>
+        <v>0.6185362497102468</v>
       </c>
       <c r="S10" t="n">
         <v>0.6164156542224719</v>
@@ -7563,25 +7563,25 @@
         <v>0.5207533501500081</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5323832107974932</v>
+        <v>0.5323832107974934</v>
       </c>
       <c r="V10" t="n">
         <v>1.026510018336417</v>
       </c>
       <c r="W10" t="n">
-        <v>0.482430225147207</v>
+        <v>0.4824302251472068</v>
       </c>
       <c r="X10" t="n">
-        <v>0.5253214152926736</v>
+        <v>0.5253214152926737</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4795724016398812</v>
+        <v>0.4795724016398814</v>
       </c>
       <c r="Z10" t="n">
         <v>0.5816505493741486</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.6065091216863642</v>
+        <v>0.6065091216863643</v>
       </c>
       <c r="AB10" t="n">
         <v>0.5223797218598426</v>
@@ -7594,19 +7594,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6141456220238005</v>
+        <v>0.6141456220238006</v>
       </c>
       <c r="C11" t="n">
         <v>0.61152874314526</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6134851735271361</v>
+        <v>0.6134851735271362</v>
       </c>
       <c r="E11" t="n">
         <v>0.01470890115817224</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5895562452378625</v>
+        <v>0.5895562452378628</v>
       </c>
       <c r="G11" t="n">
         <v>0.597274651380863</v>
@@ -7621,37 +7621,37 @@
         <v>0.5941376637215284</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6125892698816935</v>
+        <v>0.6125892698816936</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6136123607878758</v>
+        <v>0.613612360787876</v>
       </c>
       <c r="M11" t="n">
         <v>0.5839131570690256</v>
       </c>
       <c r="N11" t="n">
-        <v>0.593601802945008</v>
+        <v>0.5936018029450081</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5187984965264598</v>
+        <v>0.5187984965264597</v>
       </c>
       <c r="P11" t="n">
-        <v>0.553969299835427</v>
+        <v>0.5539692998354268</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.5960348932549578</v>
+        <v>0.596034893254958</v>
       </c>
       <c r="R11" t="n">
         <v>0.6130209478650911</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6123976489805643</v>
+        <v>0.612397648980564</v>
       </c>
       <c r="T11" t="n">
         <v>0.5852303037230778</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5883656326201747</v>
+        <v>0.5883656326201746</v>
       </c>
       <c r="V11" t="n">
         <v>1.064452523059287</v>
@@ -7660,19 +7660,19 @@
         <v>0.5741421191784718</v>
       </c>
       <c r="X11" t="n">
-        <v>0.5865014598748574</v>
+        <v>0.5865014598748572</v>
       </c>
       <c r="Y11" t="n">
         <v>0.5733656708499451</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.6024269567028964</v>
+        <v>0.6024269567028966</v>
       </c>
       <c r="AA11" t="n">
         <v>0.6095775774034944</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.5856854009245565</v>
+        <v>0.5856854009245566</v>
       </c>
     </row>
   </sheetData>
@@ -8138,7 +8138,7 @@
         <v>0.01847836328865656</v>
       </c>
       <c r="N5" t="n">
-        <v>1.720196596302732</v>
+        <v>0.0184783632886566</v>
       </c>
       <c r="O5" t="n">
         <v>0.0184783632886566</v>
@@ -8226,7 +8226,7 @@
         <v>38.260849250634</v>
       </c>
       <c r="N6" t="n">
-        <v>1.720196596302732</v>
+        <v>10.07219149979295</v>
       </c>
       <c r="O6" t="n">
         <v>10.07224802993171</v>
@@ -8314,7 +8314,7 @@
         <v>0.03085366006550095</v>
       </c>
       <c r="N7" t="n">
-        <v>1.720196596302732</v>
+        <v>0.03085366006550095</v>
       </c>
       <c r="O7" t="n">
         <v>0.03085324739326422</v>
@@ -8402,7 +8402,7 @@
         <v>0.05978691632757768</v>
       </c>
       <c r="N8" t="n">
-        <v>1.720196596302732</v>
+        <v>0.04598603262155618</v>
       </c>
       <c r="O8" t="n">
         <v>0.04977863528403149</v>
@@ -8490,7 +8490,7 @@
         <v>0.09119592743927439</v>
       </c>
       <c r="N9" t="n">
-        <v>1.720196596302732</v>
+        <v>0.09119592743927439</v>
       </c>
       <c r="O9" t="n">
         <v>0.096740816613649</v>
@@ -9174,7 +9174,7 @@
         <v>0.03281073826739213</v>
       </c>
       <c r="N5" t="n">
-        <v>1.772052089876932</v>
+        <v>0.03281073826739225</v>
       </c>
       <c r="O5" t="n">
         <v>0.03281073826739225</v>
@@ -9262,7 +9262,7 @@
         <v>10.83707193612635</v>
       </c>
       <c r="N6" t="n">
-        <v>1.772052089876932</v>
+        <v>10.83595110388321</v>
       </c>
       <c r="O6" t="n">
         <v>41.09667498000858</v>
@@ -9350,7 +9350,7 @@
         <v>0.05287732246338821</v>
       </c>
       <c r="N7" t="n">
-        <v>1.772052089876932</v>
+        <v>0.05287732246338821</v>
       </c>
       <c r="O7" t="n">
         <v>0.05287647522355231</v>
@@ -9438,7 +9438,7 @@
         <v>0.09552298473077889</v>
       </c>
       <c r="N8" t="n">
-        <v>1.772052089876932</v>
+        <v>0.0746098048947158</v>
       </c>
       <c r="O8" t="n">
         <v>0.08035692827882238</v>
@@ -9526,7 +9526,7 @@
         <v>0.177509670863542</v>
       </c>
       <c r="N9" t="n">
-        <v>1.772052089876932</v>
+        <v>0.177509670863542</v>
       </c>
       <c r="O9" t="n">
         <v>0.1883813399774208</v>
@@ -10210,7 +10210,7 @@
         <v>0.0254832744769106</v>
       </c>
       <c r="N5" t="n">
-        <v>2.101418623317722</v>
+        <v>0.02548327447691059</v>
       </c>
       <c r="O5" t="n">
         <v>0.02548327447691059</v>
@@ -10298,7 +10298,7 @@
         <v>10.08692252837952</v>
       </c>
       <c r="N6" t="n">
-        <v>2.101418623317722</v>
+        <v>10.08649767005621</v>
       </c>
       <c r="O6" t="n">
         <v>38.28033377667391</v>
@@ -10386,7 +10386,7 @@
         <v>0.04215039844632647</v>
       </c>
       <c r="N7" t="n">
-        <v>2.101418623317722</v>
+        <v>0.04215039844632647</v>
       </c>
       <c r="O7" t="n">
         <v>0.04214981324856029</v>
@@ -10474,7 +10474,7 @@
         <v>0.07995750126248222</v>
       </c>
       <c r="N8" t="n">
-        <v>2.101418623317722</v>
+        <v>0.06187581613636207</v>
       </c>
       <c r="O8" t="n">
         <v>0.0668448201943577</v>
@@ -10562,7 +10562,7 @@
         <v>0.124865031171229</v>
       </c>
       <c r="N9" t="n">
-        <v>2.101418623317722</v>
+        <v>0.124865031171229</v>
       </c>
       <c r="O9" t="n">
         <v>0.1323994868497436</v>

--- a/Results/Phase 2/Hydrogen/hydrogen ionising radiation results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen ionising radiation results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6190237330813848</v>
+        <v>0.619023733081385</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6201452376342307</v>
+        <v>0.6201452376342311</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6208721357553862</v>
+        <v>0.6208721357553869</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06665164118109217</v>
+        <v>0.06665164118109204</v>
       </c>
       <c r="F2" t="n">
         <v>0.6226728230788066</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6228097143631918</v>
+        <v>0.6228097143631919</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6281079384447403</v>
+        <v>0.6281079384447408</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6216052943285858</v>
+        <v>0.6216052943285862</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6291126877444578</v>
+        <v>0.6291126877444582</v>
       </c>
       <c r="K2" t="n">
         <v>0.6260274876072774</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6194666704500981</v>
+        <v>0.6194666704500982</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6265818832968123</v>
+        <v>0.6265818832968124</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6240005402539633</v>
+        <v>0.6240005402539631</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6283507633000243</v>
+        <v>0.6283507633000247</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6385078314453982</v>
+        <v>0.6385078314453985</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6237148537826651</v>
+        <v>0.623714853782665</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6243092097589937</v>
+        <v>0.6243092097589938</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6191285444155668</v>
+        <v>0.6191285444155671</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6320063581335019</v>
+        <v>0.632006358133502</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6299509606275673</v>
+        <v>0.6299509606275678</v>
       </c>
       <c r="V2" t="n">
-        <v>1.107521435207248</v>
+        <v>1.107521435207249</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6474404852920725</v>
+        <v>0.6474404852920727</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6190843425537842</v>
+        <v>0.6190843425537849</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6453472591201894</v>
+        <v>0.6453472591201896</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.6359410767636379</v>
+        <v>0.6359410767636378</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.6210418303799582</v>
+        <v>0.621041830379958</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.6207178448767354</v>
+        <v>0.620717844876736</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6280540461686428</v>
+        <v>0.6280540461686424</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6280540461686428</v>
+        <v>0.6280540461686424</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6280540461686428</v>
+        <v>0.6280540461686424</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04041976556607732</v>
+        <v>0.0404197655660773</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6280540461686428</v>
+        <v>0.6280540461686424</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6280540461686428</v>
+        <v>0.6280540461686424</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6280540461686428</v>
+        <v>0.6280540461686424</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6280540461686428</v>
+        <v>0.6280540461686424</v>
       </c>
       <c r="J3" t="n">
-        <v>0.628402857582946</v>
+        <v>0.6284028575829452</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6280540461686428</v>
+        <v>0.6280540461686424</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6280540461686428</v>
+        <v>0.6280540461686424</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6280540461686428</v>
+        <v>0.6280540461686424</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6280540461686428</v>
+        <v>0.6280540461686424</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6280540461686428</v>
+        <v>0.6280540461686424</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6280540461686428</v>
+        <v>0.6280540461686424</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6280540461686428</v>
+        <v>0.6280540461686424</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6280540461686428</v>
+        <v>0.6280540461686424</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6280540461686428</v>
+        <v>0.6280540461686424</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6280540461686428</v>
+        <v>0.6280540461686424</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6280540461686428</v>
+        <v>0.6280540461686424</v>
       </c>
       <c r="V3" t="n">
         <v>1.108833561498898</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6280540461686428</v>
+        <v>0.6280540461686424</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6280540461686428</v>
+        <v>0.6280540461686424</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.6280540461686428</v>
+        <v>0.6280540461686424</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.6280540461686428</v>
+        <v>0.6280540461686424</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.6280540461686428</v>
+        <v>0.6280540461686424</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.6280540461686428</v>
+        <v>0.6280540461686424</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2045031211356236</v>
+        <v>0.2045031211356241</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5574383472332596</v>
+        <v>0.5574383472332597</v>
       </c>
       <c r="D4" t="n">
-        <v>0.785529512552136</v>
+        <v>0.785529512552137</v>
       </c>
       <c r="E4" t="n">
         <v>7.745500536062027</v>
       </c>
       <c r="F4" t="n">
-        <v>1.360663856906198</v>
+        <v>1.360663856906196</v>
       </c>
       <c r="G4" t="n">
-        <v>1.25641519020731</v>
+        <v>1.256415190207309</v>
       </c>
       <c r="H4" t="n">
-        <v>3.102025991195749</v>
+        <v>3.102025991195744</v>
       </c>
       <c r="I4" t="n">
-        <v>1.019244882889582</v>
+        <v>1.019244882889581</v>
       </c>
       <c r="J4" t="n">
-        <v>2.956873463719255</v>
+        <v>2.956873463719254</v>
       </c>
       <c r="K4" t="n">
-        <v>2.336714182312305</v>
+        <v>2.3367141823123</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3410196735634082</v>
+        <v>0.3410196735634068</v>
       </c>
       <c r="M4" t="n">
-        <v>2.546947464253627</v>
+        <v>2.54694746425363</v>
       </c>
       <c r="N4" t="n">
-        <v>1.690083873104206</v>
+        <v>1.690083873104208</v>
       </c>
       <c r="O4" t="n">
-        <v>2.645290330853781</v>
+        <v>2.645290330853778</v>
       </c>
       <c r="P4" t="n">
-        <v>5.554556911980186</v>
+        <v>5.554556911980175</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.617071487205126</v>
+        <v>1.617071487205122</v>
       </c>
       <c r="R4" t="n">
-        <v>1.873165529822438</v>
+        <v>1.873165529822436</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2372088842013577</v>
+        <v>0.2372088842013574</v>
       </c>
       <c r="T4" t="n">
-        <v>4.188632632181438</v>
+        <v>4.188632632181452</v>
       </c>
       <c r="U4" t="n">
         <v>3.302014827495948</v>
       </c>
       <c r="V4" t="n">
-        <v>4.332175611717314</v>
+        <v>4.332175611717301</v>
       </c>
       <c r="W4" t="n">
-        <v>8.479549506216076</v>
+        <v>8.47954950621607</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2395000435043372</v>
+        <v>0.239500043504336</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.859291086056022</v>
+        <v>7.859291086056027</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.893129990735116</v>
+        <v>4.893129990735122</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.8067110756627919</v>
+        <v>0.8067110756627905</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.7738219022051973</v>
+        <v>0.7738219022051964</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06938909584553594</v>
+        <v>0.06938909584553606</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09788884719353574</v>
+        <v>0.09788884719353513</v>
       </c>
       <c r="D5" t="n">
-        <v>0.09788884719353574</v>
+        <v>0.09788884719353513</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08271357030041032</v>
+        <v>0.08271357030041052</v>
       </c>
       <c r="F5" t="n">
-        <v>0.07382902401629321</v>
+        <v>0.07382902401629285</v>
       </c>
       <c r="G5" t="n">
-        <v>0.103798456290757</v>
+        <v>0.1037984562907567</v>
       </c>
       <c r="H5" t="n">
-        <v>0.09788884719353574</v>
+        <v>0.09788884719353513</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09788884719353574</v>
+        <v>0.09788884719353513</v>
       </c>
       <c r="J5" t="n">
-        <v>0.09850487977958061</v>
+        <v>0.09850487977958017</v>
       </c>
       <c r="K5" t="n">
-        <v>0.09788884719353574</v>
+        <v>0.09788884719353513</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09788884719353574</v>
+        <v>0.09788884719353513</v>
       </c>
       <c r="M5" t="n">
-        <v>0.09788884719354403</v>
+        <v>0.0978888471935435</v>
       </c>
       <c r="N5" t="n">
-        <v>1.690083873104206</v>
+        <v>0.07579677198205081</v>
       </c>
       <c r="O5" t="n">
-        <v>0.08186786604775689</v>
+        <v>0.08186786604775663</v>
       </c>
       <c r="P5" t="n">
         <v>0.08037969419668635</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.06378824424331689</v>
+        <v>0.06378824424331626</v>
       </c>
       <c r="R5" t="n">
-        <v>0.09788884719353574</v>
+        <v>0.09788884719353513</v>
       </c>
       <c r="S5" t="n">
-        <v>0.09788884719353574</v>
+        <v>0.09788884719353513</v>
       </c>
       <c r="T5" t="n">
-        <v>0.09788884719353574</v>
+        <v>0.09788884719353515</v>
       </c>
       <c r="U5" t="n">
-        <v>0.08405041402893494</v>
+        <v>0.08405041402893455</v>
       </c>
       <c r="V5" t="n">
-        <v>0.09426571138837878</v>
+        <v>0.09426571138837869</v>
       </c>
       <c r="W5" t="n">
-        <v>0.09789444816359753</v>
+        <v>0.09789444816359709</v>
       </c>
       <c r="X5" t="n">
-        <v>0.06640030305499245</v>
+        <v>0.06640030305499209</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.126348527087758</v>
+        <v>0.1263485270877577</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.06885969833646749</v>
+        <v>0.06885969833646766</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.09788884719353574</v>
+        <v>0.09788884719353513</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.127659220542682</v>
+        <v>0.1276592205426818</v>
       </c>
     </row>
     <row r="6">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1590221580004643</v>
+        <v>0.1590221580004641</v>
       </c>
       <c r="C6" t="n">
         <v>0.1962151960505101</v>
@@ -947,13 +947,13 @@
         <v>0.1962151960505101</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1876312395608019</v>
+        <v>0.1876312395608014</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1104750160670043</v>
+        <v>0.1104750160670039</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1962152545325186</v>
+        <v>0.196215254532518</v>
       </c>
       <c r="H6" t="n">
         <v>0.1962151960505101</v>
@@ -962,7 +962,7 @@
         <v>0.1962151960505101</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1968312286365549</v>
+        <v>0.1968312286365543</v>
       </c>
       <c r="K6" t="n">
         <v>0.1962151960505101</v>
@@ -974,16 +974,16 @@
         <v>0.1962151960505101</v>
       </c>
       <c r="N6" t="n">
-        <v>1.690083873104206</v>
+        <v>0.1962151960505101</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2085409980230431</v>
+        <v>0.2085409980230425</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2112216357580884</v>
+        <v>0.2112216357580875</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1962152545325186</v>
+        <v>0.196215254532518</v>
       </c>
       <c r="R6" t="n">
         <v>0.1962151960505101</v>
@@ -998,7 +998,7 @@
         <v>0.1962151960505101</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2432221801154853</v>
+        <v>0.243222180115485</v>
       </c>
       <c r="W6" t="n">
         <v>0.1962151960505101</v>
@@ -1010,7 +1010,7 @@
         <v>0.1962151960505101</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.1737911246628796</v>
+        <v>0.1737911246628789</v>
       </c>
       <c r="AA6" t="n">
         <v>0.1962151960505101</v>
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6243098486686671</v>
+        <v>0.6243098486686669</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6177865531154363</v>
+        <v>0.6177865531154361</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6135406308894882</v>
+        <v>0.6135406308894877</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1173772272855795</v>
+        <v>-0.1173772272855797</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6031153980029065</v>
+        <v>0.6031153980029061</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6018009993051308</v>
+        <v>0.6018009993051304</v>
       </c>
       <c r="H7" t="n">
-        <v>0.571540462696996</v>
+        <v>0.5715404626969959</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6092813605070537</v>
+        <v>0.6092813605070529</v>
       </c>
       <c r="J7" t="n">
         <v>0.566988409576605</v>
       </c>
       <c r="K7" t="n">
-        <v>0.583279589807011</v>
+        <v>0.5832795898070113</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6217148454752919</v>
+        <v>0.6217148454752913</v>
       </c>
       <c r="M7" t="n">
-        <v>0.580277648768341</v>
+        <v>0.5802776487683403</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5950769254802428</v>
+        <v>0.595076925480243</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5687572175513422</v>
+        <v>0.5687572175513425</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5081588337983295</v>
+        <v>0.5081588337983297</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5968096016717037</v>
+        <v>0.5968096016717035</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5935444242481883</v>
+        <v>0.5935444242481884</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6236998296759726</v>
+        <v>0.6236998296759727</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5483722038418172</v>
+        <v>0.5483722038418167</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5596651909234818</v>
+        <v>0.5596651909234822</v>
       </c>
       <c r="V7" t="n">
-        <v>1.014654908223936</v>
+        <v>1.014654908223937</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4566246831092225</v>
+        <v>0.4566246831092222</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6240087848554894</v>
+        <v>0.6240087848554891</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4692357510316545</v>
+        <v>0.4692357510316542</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.5237812877545994</v>
+        <v>0.5237812877545985</v>
       </c>
       <c r="AA7" t="n">
         <v>0.6124415969556577</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.6144475017148912</v>
+        <v>0.6144475017148908</v>
       </c>
     </row>
     <row r="8">
@@ -1114,61 +1114,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6173201112868458</v>
+        <v>0.6173201112868457</v>
       </c>
       <c r="C8" t="n">
         <v>0.615473495574463</v>
       </c>
       <c r="D8" t="n">
-        <v>0.614268485551861</v>
+        <v>0.6142684855518611</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.005146493435590674</v>
+        <v>-0.005146493435590977</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6113256586886404</v>
+        <v>0.6113256586886406</v>
       </c>
       <c r="G8" t="n">
         <v>0.6108644943767971</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6023940778670362</v>
+        <v>0.6023940778670366</v>
       </c>
       <c r="I8" t="n">
         <v>0.6130636625275634</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6011689181853395</v>
+        <v>0.601168918185339</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6056549672750088</v>
+        <v>0.6056549672750078</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6165823139327888</v>
+        <v>0.6165823139327897</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6048434702253299</v>
+        <v>0.6048434702253302</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6089958452488926</v>
+        <v>0.6089958452488924</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6013705173113718</v>
+        <v>0.6013705173113714</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5839551277335339</v>
+        <v>0.5839551277335345</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.6094985319664208</v>
+        <v>0.6094985319664212</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6086072218095467</v>
+        <v>0.6086072218095464</v>
       </c>
       <c r="S8" t="n">
-        <v>0.617147362035337</v>
+        <v>0.6171473620353375</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5957508659438313</v>
+        <v>0.5957508659438315</v>
       </c>
       <c r="U8" t="n">
         <v>0.5988338135486686</v>
@@ -1177,10 +1177,10 @@
         <v>1.064669847837581</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5694395787870707</v>
+        <v>0.5694395787870712</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6172437357648164</v>
+        <v>0.6172437357648161</v>
       </c>
       <c r="Y8" t="n">
         <v>0.5730844287089835</v>
@@ -1189,10 +1189,10 @@
         <v>0.5884966393876833</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.6139381162341266</v>
+        <v>0.613938116234127</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.6145268237887938</v>
+        <v>0.614526823788794</v>
       </c>
     </row>
   </sheetData>
@@ -1358,85 +1358,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6100563695617582</v>
+        <v>0.6100563695617585</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6111913660364788</v>
+        <v>0.6111913660364785</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6110423691761209</v>
+        <v>0.6110423691761215</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03243583548390607</v>
+        <v>0.03243583548390597</v>
       </c>
       <c r="F2" t="n">
-        <v>0.63862204052444</v>
+        <v>0.6386220405244403</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6221691023482797</v>
+        <v>0.6221691023482798</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6170756833126446</v>
+        <v>0.6170756833126442</v>
       </c>
       <c r="I2" t="n">
         <v>0.6143766766741418</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6218645385562023</v>
+        <v>0.6218645385562025</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6268734465811776</v>
+        <v>0.6268734465811771</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6221054334484705</v>
+        <v>0.6221054334484701</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6302891629324157</v>
+        <v>0.6302891629324162</v>
       </c>
       <c r="N2" t="n">
         <v>0.6195370638940413</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6540292144377353</v>
+        <v>0.6540292144377358</v>
       </c>
       <c r="P2" t="n">
-        <v>0.638400744800137</v>
+        <v>0.6384007448001369</v>
       </c>
       <c r="Q2" t="n">
         <v>0.6171331014190834</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6145355069209489</v>
+        <v>0.6145355069209484</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6250906467893209</v>
+        <v>0.6250906467893217</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6304177745329782</v>
+        <v>0.6304177745329783</v>
       </c>
       <c r="U2" t="n">
-        <v>0.624613127250066</v>
+        <v>0.6246131272500661</v>
       </c>
       <c r="V2" t="n">
-        <v>1.081464232285959</v>
+        <v>1.08146423228596</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6257088239903853</v>
+        <v>0.6257088239903857</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6239842616209673</v>
+        <v>0.6239842616209678</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6213209563456854</v>
+        <v>0.621320956345685</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.6128038111564013</v>
+        <v>0.6128038111564015</v>
       </c>
       <c r="AA2" t="n">
         <v>0.6134842596360327</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.6187153464995552</v>
+        <v>0.6187153464995553</v>
       </c>
     </row>
     <row r="3">
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6194608424928479</v>
+        <v>0.6194608424928485</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6194608424928479</v>
+        <v>0.6194608424928485</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6194608424928479</v>
+        <v>0.6194608424928485</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02747306287693057</v>
+        <v>0.0274730628769305</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6194608424928479</v>
+        <v>0.6194608424928485</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6194608424928479</v>
+        <v>0.6194608424928485</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6194608424928479</v>
+        <v>0.6194608424928485</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6194608424928479</v>
+        <v>0.6194608424928485</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6191841992766526</v>
+        <v>0.619184199276653</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6194608424928479</v>
+        <v>0.6194608424928485</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6194608424928479</v>
+        <v>0.6194608424928485</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6194608424928479</v>
+        <v>0.6194608424928485</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6194608424928479</v>
+        <v>0.6194608424928485</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6194608424928479</v>
+        <v>0.6194608424928485</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6194608424928479</v>
+        <v>0.6194608424928485</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6194608424928479</v>
+        <v>0.6194608424928485</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6194608424928479</v>
+        <v>0.6194608424928485</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6194608424928479</v>
+        <v>0.6194608424928485</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6194608424928479</v>
+        <v>0.6194608424928485</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6194608424928479</v>
+        <v>0.6194608424928485</v>
       </c>
       <c r="V3" t="n">
-        <v>1.094287595349625</v>
+        <v>1.094287595349626</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6194608424928479</v>
+        <v>0.6194608424928485</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6194608424928479</v>
+        <v>0.6194608424928485</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.6194608424928479</v>
+        <v>0.6194608424928485</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.6194608424928479</v>
+        <v>0.6194608424928485</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.6194608424928479</v>
+        <v>0.6194608424928485</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.6194608424928479</v>
+        <v>0.6194608424928485</v>
       </c>
     </row>
     <row r="4">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.06319798017479797</v>
+        <v>0.06319798017479768</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3454424620551907</v>
+        <v>0.3454424620551906</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3132998282719043</v>
+        <v>0.3132998282719042</v>
       </c>
       <c r="E4" t="n">
-        <v>1.243840096191484</v>
+        <v>1.243840096191482</v>
       </c>
       <c r="F4" t="n">
-        <v>7.331310732859155</v>
+        <v>7.331310732859144</v>
       </c>
       <c r="G4" t="n">
-        <v>2.746370816605705</v>
+        <v>2.7463708166057</v>
       </c>
       <c r="H4" t="n">
         <v>1.953907445742732</v>
       </c>
       <c r="I4" t="n">
-        <v>1.184946618461338</v>
+        <v>1.18494661846134</v>
       </c>
       <c r="J4" t="n">
-        <v>2.931294257345576</v>
+        <v>2.931294257345574</v>
       </c>
       <c r="K4" t="n">
         <v>3.884285592775543</v>
       </c>
       <c r="L4" t="n">
-        <v>2.801425666462207</v>
+        <v>2.801425666462211</v>
       </c>
       <c r="M4" t="n">
-        <v>5.142221424373609</v>
+        <v>5.142221424373603</v>
       </c>
       <c r="N4" t="n">
-        <v>2.518621175655708</v>
+        <v>2.51862117565571</v>
       </c>
       <c r="O4" t="n">
-        <v>9.836137781511711</v>
+        <v>9.83613778151172</v>
       </c>
       <c r="P4" t="n">
-        <v>6.443284393088909</v>
+        <v>6.443284393088911</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.763064754657412</v>
+        <v>1.763064754657411</v>
       </c>
       <c r="R4" t="n">
-        <v>1.262868437776268</v>
+        <v>1.262868437776267</v>
       </c>
       <c r="S4" t="n">
-        <v>3.448020298484969</v>
+        <v>3.448020298484971</v>
       </c>
       <c r="T4" t="n">
-        <v>5.403254342090206</v>
+        <v>5.403254342090208</v>
       </c>
       <c r="U4" t="n">
-        <v>3.302257002143889</v>
+        <v>3.302257002143884</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9716768580491877</v>
+        <v>0.9716768580491878</v>
       </c>
       <c r="W4" t="n">
         <v>4.00090533997373</v>
       </c>
       <c r="X4" t="n">
-        <v>3.462701139192252</v>
+        <v>3.462701139192259</v>
       </c>
       <c r="Y4" t="n">
         <v>2.951913384765791</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.6551300786440025</v>
+        <v>0.6551300786440035</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.9380779905962849</v>
+        <v>0.938077990596287</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.409620597626953</v>
+        <v>2.409620597626954</v>
       </c>
     </row>
     <row r="5">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04912039480225511</v>
+        <v>0.04912039480225498</v>
       </c>
       <c r="C5" t="n">
-        <v>0.07215522950234567</v>
+        <v>0.07215522950234525</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07215522950234567</v>
+        <v>0.07215522950234525</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05988985951536913</v>
+        <v>0.05988985951536922</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05270895283147985</v>
+        <v>0.0527089528314797</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07693165253328541</v>
+        <v>0.07693165253328513</v>
       </c>
       <c r="H5" t="n">
-        <v>0.07215522950234567</v>
+        <v>0.07215522950234525</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07215522950234567</v>
+        <v>0.07215522950234525</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07264294404680388</v>
+        <v>0.07264294404680376</v>
       </c>
       <c r="K5" t="n">
-        <v>0.07215522950234567</v>
+        <v>0.07215522950234525</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07215522950234567</v>
+        <v>0.07215522950234525</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07215522950243131</v>
+        <v>0.07215522950243096</v>
       </c>
       <c r="N5" t="n">
-        <v>2.518621175655708</v>
+        <v>0.05429937895859575</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05920632171323274</v>
+        <v>0.05920632171323259</v>
       </c>
       <c r="P5" t="n">
-        <v>0.05800351147723583</v>
+        <v>0.05800351147723566</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.04459352404688217</v>
+        <v>0.04459352404688206</v>
       </c>
       <c r="R5" t="n">
-        <v>0.07215522950234567</v>
+        <v>0.07215522950234525</v>
       </c>
       <c r="S5" t="n">
-        <v>0.07215522950234567</v>
+        <v>0.07215522950234525</v>
       </c>
       <c r="T5" t="n">
-        <v>0.07215522950234567</v>
+        <v>0.07215522950234525</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06073834190770906</v>
+        <v>0.06073834190770876</v>
       </c>
       <c r="V5" t="n">
-        <v>0.06893437405821488</v>
+        <v>0.06893437405821479</v>
       </c>
       <c r="W5" t="n">
-        <v>0.07215975647909181</v>
+        <v>0.07215975647909142</v>
       </c>
       <c r="X5" t="n">
-        <v>0.04670471240068013</v>
+        <v>0.04670471240068005</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.09476076236380757</v>
+        <v>0.09476076236380732</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.04869251092403561</v>
+        <v>0.0486925109240355</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.07215522950234567</v>
+        <v>0.07215522950234525</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.09621704046188141</v>
+        <v>0.09621704046188105</v>
       </c>
     </row>
     <row r="6">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0949495887022913</v>
+        <v>0.09494958870229125</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1176499001337208</v>
+        <v>0.1176499001337206</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1176499001337208</v>
+        <v>0.1176499001337206</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1124107443452181</v>
+        <v>0.112410744345218</v>
       </c>
       <c r="F6" t="n">
-        <v>0.06531951478567159</v>
+        <v>0.06531951478567165</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1176498786790575</v>
+        <v>0.1176498786790573</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1176499001337208</v>
+        <v>0.1176499001337206</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1176499001337208</v>
+        <v>0.1176499001337206</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1181376146781793</v>
+        <v>0.1181376146781792</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1176499001337208</v>
+        <v>0.1176499001337206</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1176499001337208</v>
+        <v>0.1176499001337206</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1176499001337208</v>
+        <v>0.1176499001337206</v>
       </c>
       <c r="N6" t="n">
-        <v>2.518621175655708</v>
+        <v>0.1176499001337206</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1251727250538676</v>
+        <v>0.1251727250538675</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1268088150700817</v>
+        <v>0.1268088150700816</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1176498786790575</v>
+        <v>0.1176498786790573</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1176499001337208</v>
+        <v>0.1176499001337206</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1176499001337208</v>
+        <v>0.1176499001337206</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1176499001337208</v>
+        <v>0.1176499001337206</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1176499001337208</v>
+        <v>0.1176499001337206</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1471121796465729</v>
+        <v>0.1471121796465728</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1176499001337208</v>
+        <v>0.1176499001337206</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1176499001337208</v>
+        <v>0.1176499001337206</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1176499001337208</v>
+        <v>0.1176499001337206</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.1039636224116133</v>
+        <v>0.1039636224116132</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.1176499001337208</v>
+        <v>0.1176499001337206</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1176499001337208</v>
+        <v>0.1176499001337206</v>
       </c>
     </row>
     <row r="7">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.618454590818592</v>
+        <v>0.6184545908185919</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6118131451644692</v>
+        <v>0.6118131451644694</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6126947721514571</v>
+        <v>0.6126947721514572</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.003701819438737461</v>
+        <v>-0.003701819438737605</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4519673728154727</v>
+        <v>0.4519673728154736</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5464344698517498</v>
+        <v>0.5464344698517503</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5776384851729565</v>
+        <v>0.5776384851729567</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5932132113593304</v>
+        <v>0.5932132113593306</v>
       </c>
       <c r="J7" t="n">
-        <v>0.546903342340607</v>
+        <v>0.5469033423406074</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5198226574437536</v>
+        <v>0.5198226574437547</v>
       </c>
       <c r="L7" t="n">
-        <v>0.547228862453883</v>
+        <v>0.5472288624538835</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5004096341571274</v>
+        <v>0.5004096341571284</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5626976393827801</v>
+        <v>0.5626976393827808</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3565665452265623</v>
+        <v>0.3565665452265627</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4494933909757432</v>
+        <v>0.4494933909757435</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5769095559520521</v>
+        <v>0.5769095559520526</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5923409433051685</v>
+        <v>0.5923409433051682</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5292923629993046</v>
+        <v>0.5292923629993049</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4992790875034965</v>
+        <v>0.4992790875034971</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5323168551640257</v>
+        <v>0.5323168551640267</v>
       </c>
       <c r="V7" t="n">
-        <v>1.069365607336716</v>
+        <v>1.069365607336717</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5260822822412948</v>
+        <v>0.5260822822412944</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5368077685575929</v>
+        <v>0.5368077685575935</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.552088360638513</v>
+        <v>0.5520883606385136</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.6021288206598934</v>
+        <v>0.6021288206598935</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5982486225978366</v>
+        <v>0.5982486225978371</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.5677618812368807</v>
+        <v>0.5677618812368816</v>
       </c>
     </row>
     <row r="8">
@@ -1889,52 +1889,52 @@
         <v>0.6095985218432384</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6077116393803013</v>
+        <v>0.6077116393803007</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6079637856086012</v>
+        <v>0.6079637856086013</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01825116468182187</v>
+        <v>0.01825116468182177</v>
       </c>
       <c r="F8" t="n">
-        <v>0.562411978051217</v>
+        <v>0.5624119780512169</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5889418700753387</v>
+        <v>0.5889418700753393</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5980463774521494</v>
+        <v>0.5980463774521492</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6024339208621539</v>
+        <v>0.6024339208621546</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5889765183048772</v>
+        <v>0.5889765183048778</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5815377548557846</v>
+        <v>0.5815377548557845</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5892396523410799</v>
+        <v>0.5892396523410798</v>
       </c>
       <c r="M8" t="n">
-        <v>0.576120483745973</v>
+        <v>0.5761204837459734</v>
       </c>
       <c r="N8" t="n">
-        <v>0.593709625585365</v>
+        <v>0.5937096255853654</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5344114713871605</v>
+        <v>0.5344114713871607</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5610650127057245</v>
+        <v>0.5610650127057251</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.597772130440117</v>
+        <v>0.5977721304401173</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6021958663645645</v>
+        <v>0.6021958663645642</v>
       </c>
       <c r="S8" t="n">
         <v>0.5840637012698653</v>
@@ -1943,28 +1943,28 @@
         <v>0.575734693016295</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5849623353040421</v>
+        <v>0.5849623353040424</v>
       </c>
       <c r="V8" t="n">
-        <v>1.070124648318421</v>
+        <v>1.070124648318422</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5832212814961142</v>
+        <v>0.5832212814961144</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5863768495807088</v>
+        <v>0.5863768495807095</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5906662623986033</v>
+        <v>0.5906662623986034</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.6049176859885308</v>
+        <v>0.6049176859885307</v>
       </c>
       <c r="AA8" t="n">
         <v>0.6038326319844688</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.5951921543732764</v>
+        <v>0.595192154373277</v>
       </c>
     </row>
   </sheetData>
@@ -2133,76 +2133,76 @@
         <v>0.6186229466745858</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6207130355224142</v>
+        <v>0.6207130355224143</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6190744669942393</v>
+        <v>0.6190744669942392</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0625151801798199</v>
+        <v>0.06251518017982037</v>
       </c>
       <c r="F2" t="n">
         <v>0.62244871937655</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6217495798419997</v>
+        <v>0.6217495798419995</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6279702948000886</v>
+        <v>0.6279702948000884</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6223396161056115</v>
+        <v>0.6223396161056119</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6278835323498115</v>
+        <v>0.6278835323498119</v>
       </c>
       <c r="K2" t="n">
         <v>0.6242767067126992</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6188267639995062</v>
+        <v>0.618826763999506</v>
       </c>
       <c r="M2" t="n">
-        <v>0.623644550830978</v>
+        <v>0.6236445508309783</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6224228022557777</v>
+        <v>0.6224228022557774</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6442766918555211</v>
+        <v>0.6442766918555209</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6365969068208674</v>
+        <v>0.6365969068208671</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6280642117627755</v>
+        <v>0.6280642117627754</v>
       </c>
       <c r="R2" t="n">
         <v>0.6258813738846792</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6188436971502715</v>
+        <v>0.6188436971502714</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6303975373231484</v>
+        <v>0.6303975373231482</v>
       </c>
       <c r="U2" t="n">
         <v>0.6289036805578556</v>
       </c>
       <c r="V2" t="n">
-        <v>1.11009909968877</v>
+        <v>1.110099099688769</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6450407822552271</v>
+        <v>0.6450407822552268</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6189907170332305</v>
+        <v>0.6189907170332309</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6456029046670544</v>
+        <v>0.6456029046670539</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.6352107513427564</v>
+        <v>0.6352107513427568</v>
       </c>
       <c r="AA2" t="n">
         <v>0.621876446298424</v>
@@ -2218,85 +2218,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.627892727383803</v>
+        <v>0.6278927273838032</v>
       </c>
       <c r="C3" t="n">
-        <v>0.627892727383803</v>
+        <v>0.6278927273838032</v>
       </c>
       <c r="D3" t="n">
-        <v>0.627892727383803</v>
+        <v>0.6278927273838032</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03875211242065369</v>
+        <v>0.03875211242065395</v>
       </c>
       <c r="F3" t="n">
-        <v>0.627892727383803</v>
+        <v>0.6278927273838032</v>
       </c>
       <c r="G3" t="n">
-        <v>0.627892727383803</v>
+        <v>0.6278927273838032</v>
       </c>
       <c r="H3" t="n">
-        <v>0.627892727383803</v>
+        <v>0.6278927273838032</v>
       </c>
       <c r="I3" t="n">
-        <v>0.627892727383803</v>
+        <v>0.6278927273838032</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6283555760686611</v>
+        <v>0.628355576068661</v>
       </c>
       <c r="K3" t="n">
-        <v>0.627892727383803</v>
+        <v>0.6278927273838032</v>
       </c>
       <c r="L3" t="n">
-        <v>0.627892727383803</v>
+        <v>0.6278927273838032</v>
       </c>
       <c r="M3" t="n">
-        <v>0.627892727383803</v>
+        <v>0.6278927273838032</v>
       </c>
       <c r="N3" t="n">
-        <v>0.627892727383803</v>
+        <v>0.6278927273838032</v>
       </c>
       <c r="O3" t="n">
-        <v>0.627892727383803</v>
+        <v>0.6278927273838032</v>
       </c>
       <c r="P3" t="n">
-        <v>0.627892727383803</v>
+        <v>0.6278927273838032</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.627892727383803</v>
+        <v>0.6278927273838032</v>
       </c>
       <c r="R3" t="n">
-        <v>0.627892727383803</v>
+        <v>0.6278927273838032</v>
       </c>
       <c r="S3" t="n">
-        <v>0.627892727383803</v>
+        <v>0.6278927273838032</v>
       </c>
       <c r="T3" t="n">
-        <v>0.627892727383803</v>
+        <v>0.6278927273838032</v>
       </c>
       <c r="U3" t="n">
-        <v>0.627892727383803</v>
+        <v>0.6278927273838032</v>
       </c>
       <c r="V3" t="n">
-        <v>1.109590098296652</v>
+        <v>1.109590098296653</v>
       </c>
       <c r="W3" t="n">
-        <v>0.627892727383803</v>
+        <v>0.6278927273838032</v>
       </c>
       <c r="X3" t="n">
-        <v>0.627892727383803</v>
+        <v>0.6278927273838032</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.627892727383803</v>
+        <v>0.6278927273838032</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.627892727383803</v>
+        <v>0.6278927273838032</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.627892727383803</v>
+        <v>0.6278927273838032</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.627892727383803</v>
+        <v>0.6278927273838032</v>
       </c>
     </row>
     <row r="4">
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1323309375753721</v>
+        <v>0.1323309375753639</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7111051628941547</v>
+        <v>0.7111051628941545</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2705734919371209</v>
+        <v>0.2705734919371128</v>
       </c>
       <c r="E4" t="n">
-        <v>6.551182509724817</v>
+        <v>6.551182509724836</v>
       </c>
       <c r="F4" t="n">
-        <v>1.228982641734292</v>
+        <v>1.228982641734297</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9356932132179813</v>
+        <v>0.9356932132179819</v>
       </c>
       <c r="H4" t="n">
-        <v>2.897961747864563</v>
+        <v>2.897961747864567</v>
       </c>
       <c r="I4" t="n">
-        <v>1.212913800819836</v>
+        <v>1.212913800819838</v>
       </c>
       <c r="J4" t="n">
-        <v>2.424670296411477</v>
+        <v>2.424670296411473</v>
       </c>
       <c r="K4" t="n">
-        <v>1.622695282527984</v>
+        <v>1.622695282527985</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1912692174438224</v>
+        <v>0.1912692174438578</v>
       </c>
       <c r="M4" t="n">
-        <v>1.578876263987177</v>
+        <v>1.578876263987173</v>
       </c>
       <c r="N4" t="n">
-        <v>1.190567840093182</v>
+        <v>1.190567840093183</v>
       </c>
       <c r="O4" t="n">
-        <v>6.352978392501984</v>
+        <v>6.352978392501988</v>
       </c>
       <c r="P4" t="n">
-        <v>4.735832984619916</v>
+        <v>4.735832984619897</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.755792141505128</v>
+        <v>2.755792141505136</v>
       </c>
       <c r="R4" t="n">
-        <v>2.259167134761242</v>
+        <v>2.25916713476124</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1904874532933104</v>
+        <v>0.1904874532933157</v>
       </c>
       <c r="T4" t="n">
-        <v>3.486549711560108</v>
+        <v>3.48654971156011</v>
       </c>
       <c r="U4" t="n">
-        <v>2.849887366345699</v>
+        <v>2.849887366345689</v>
       </c>
       <c r="V4" t="n">
-        <v>4.339710278288837</v>
+        <v>4.339710278288835</v>
       </c>
       <c r="W4" t="n">
-        <v>7.327481575125621</v>
+        <v>7.32748157512562</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2438132716388398</v>
+        <v>0.2438132716388487</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.380877648838456</v>
+        <v>7.380877648838449</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.396511217211907</v>
+        <v>4.396511217211913</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.021080210850735</v>
+        <v>1.02108021085074</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.6912678885826997</v>
+        <v>0.6912678885827026</v>
       </c>
     </row>
     <row r="5">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0654070245988134</v>
+        <v>0.06540702459881338</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09067485091212728</v>
+        <v>0.0906748509121275</v>
       </c>
       <c r="D5" t="n">
-        <v>0.09067485091212728</v>
+        <v>0.0906748509121275</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07722047876285464</v>
+        <v>0.07722047876285487</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06934345662220051</v>
+        <v>0.06934345662220059</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0959142992995736</v>
+        <v>0.09591429929957361</v>
       </c>
       <c r="H5" t="n">
-        <v>0.09067485091212728</v>
+        <v>0.0906748509121275</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09067485091212728</v>
+        <v>0.0906748509121275</v>
       </c>
       <c r="J5" t="n">
-        <v>0.09131395654961083</v>
+        <v>0.09131395654961071</v>
       </c>
       <c r="K5" t="n">
-        <v>0.09067485091212728</v>
+        <v>0.0906748509121275</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09067485091212728</v>
+        <v>0.0906748509121275</v>
       </c>
       <c r="M5" t="n">
-        <v>0.09067485091213795</v>
+        <v>0.09067485091213809</v>
       </c>
       <c r="N5" t="n">
-        <v>1.190567840093182</v>
+        <v>0.07108805829329932</v>
       </c>
       <c r="O5" t="n">
-        <v>0.07647067895287567</v>
+        <v>0.07647067895287572</v>
       </c>
       <c r="P5" t="n">
-        <v>0.07515126856914116</v>
+        <v>0.07515126856914128</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.06044132002930736</v>
+        <v>0.06044132002930721</v>
       </c>
       <c r="R5" t="n">
-        <v>0.09067485091212728</v>
+        <v>0.09067485091212751</v>
       </c>
       <c r="S5" t="n">
-        <v>0.09067485091212728</v>
+        <v>0.0906748509121275</v>
       </c>
       <c r="T5" t="n">
-        <v>0.09067485091212728</v>
+        <v>0.09067485091212751</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07844006852645037</v>
+        <v>0.07844006852645051</v>
       </c>
       <c r="V5" t="n">
-        <v>0.08811117900676629</v>
+        <v>0.0881111790067662</v>
       </c>
       <c r="W5" t="n">
         <v>0.09067981672257272</v>
       </c>
       <c r="X5" t="n">
-        <v>0.06275716649343595</v>
+        <v>0.06275716649343591</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1159659070066386</v>
+        <v>0.1159659070066387</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.06493766175599387</v>
+        <v>0.06493766175599415</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.09067485091212728</v>
+        <v>0.0906748509121275</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1170692083192326</v>
+        <v>0.117069208319233</v>
       </c>
     </row>
     <row r="6">
@@ -2482,46 +2482,46 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1367825442709194</v>
+        <v>0.136782544270919</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1675196610758572</v>
+        <v>0.1675196610758571</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1675196610758572</v>
+        <v>0.1675196610758571</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1604257035805421</v>
+        <v>0.160425703580542</v>
       </c>
       <c r="F6" t="n">
-        <v>0.09666214374918629</v>
+        <v>0.09666214374918611</v>
       </c>
       <c r="G6" t="n">
         <v>0.1675197178733266</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1675196610758572</v>
+        <v>0.1675196610758571</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1675196610758572</v>
+        <v>0.1675196610758571</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1681587667133405</v>
+        <v>0.1681587667133404</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1675196610758572</v>
+        <v>0.1675196610758571</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1675196610758572</v>
+        <v>0.1675196610758571</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1675196610758572</v>
+        <v>0.1675196610758571</v>
       </c>
       <c r="N6" t="n">
-        <v>1.190567840093182</v>
+        <v>0.1675196610758571</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1777059769582758</v>
+        <v>0.1777059769582759</v>
       </c>
       <c r="P6" t="n">
         <v>0.1799213135424786</v>
@@ -2530,37 +2530,37 @@
         <v>0.1675197178733266</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1675196610758572</v>
+        <v>0.1675196610758571</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1675196610758572</v>
+        <v>0.1675196610758571</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1675196610758572</v>
+        <v>0.1675196610758571</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1675196610758572</v>
+        <v>0.1675196610758571</v>
       </c>
       <c r="V6" t="n">
         <v>0.2072239060478044</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1675196610758572</v>
+        <v>0.1675196610758571</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1675196610758572</v>
+        <v>0.1675196610758571</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1675196610758572</v>
+        <v>0.1675196610758571</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.1489879354471987</v>
+        <v>0.1489879354471988</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.1675196610758572</v>
+        <v>0.1675196610758571</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1675196610758572</v>
+        <v>0.1675196610758571</v>
       </c>
     </row>
     <row r="7">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6255939859719352</v>
+        <v>0.6255939859719355</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6133699759150345</v>
+        <v>0.6133699759150349</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6229847778641462</v>
+        <v>0.6229847778641463</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.104291596108868</v>
+        <v>-0.1042915961088681</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6033404413057543</v>
+        <v>0.6033404413057545</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6070047284890544</v>
+        <v>0.6070047284890545</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5712617541325413</v>
+        <v>0.5712617541325419</v>
       </c>
       <c r="I7" t="n">
         <v>0.6039040744945381</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5739660215027242</v>
+        <v>0.5739660215027246</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5924623190002891</v>
+        <v>0.5924623190002895</v>
       </c>
       <c r="L7" t="n">
-        <v>0.624403548233441</v>
+        <v>0.6244035482334401</v>
       </c>
       <c r="M7" t="n">
-        <v>0.596335624553586</v>
+        <v>0.5963356245535866</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6032680104322717</v>
+        <v>0.6032680104322721</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4728067066553588</v>
+        <v>0.4728067066553593</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5184476780772621</v>
+        <v>0.5184476780772629</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5701798400872155</v>
+        <v>0.5701798400872156</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5832895956970341</v>
+        <v>0.5832895956970342</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6242918903569785</v>
+        <v>0.6242918903569786</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5567047713820668</v>
+        <v>0.556704771382067</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5647674709737328</v>
+        <v>0.5647674709737329</v>
       </c>
       <c r="V7" t="n">
         <v>1.004562928992908</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4696949055065236</v>
+        <v>0.4696949055065234</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6234710835577552</v>
+        <v>0.6234710835577557</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4666381121266543</v>
+        <v>0.4666381121266546</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.5270221363673151</v>
+        <v>0.5270221363673154</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.6064277092448258</v>
+        <v>0.606427709244826</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.6149855426878883</v>
+        <v>0.6149855426878887</v>
       </c>
     </row>
     <row r="8">
@@ -2658,49 +2658,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6175770120065317</v>
+        <v>0.6175770120065315</v>
       </c>
       <c r="C8" t="n">
-        <v>0.614105137322862</v>
+        <v>0.6141051373228618</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6168413343220885</v>
+        <v>0.616841334322088</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.002570163054363881</v>
+        <v>-0.002570163054363605</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6112773509675445</v>
+        <v>0.611277350967545</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6122454737787865</v>
+        <v>0.6122454737787862</v>
       </c>
       <c r="H8" t="n">
         <v>0.6022030214985609</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6114247025936954</v>
+        <v>0.6114247025936959</v>
       </c>
       <c r="J8" t="n">
         <v>0.6031361116930842</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6081557579881882</v>
+        <v>0.6081557579881888</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6172391763667371</v>
+        <v>0.6172391763667369</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6092859684767093</v>
+        <v>0.6092859684767098</v>
       </c>
       <c r="N8" t="n">
         <v>0.6112184775685141</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5737120581942551</v>
+        <v>0.5737120581942553</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5867990606057135</v>
+        <v>0.5867990606057137</v>
       </c>
       <c r="Q8" t="n">
         <v>0.6018046641227686</v>
@@ -2709,7 +2709,7 @@
         <v>0.6055868068254523</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6172053048278796</v>
+        <v>0.6172053048278797</v>
       </c>
       <c r="T8" t="n">
         <v>0.5980067904798032</v>
@@ -2724,16 +2724,16 @@
         <v>0.5730602691545198</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6169788550014358</v>
+        <v>0.616978855001436</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5722315408370837</v>
+        <v>0.5722315408370836</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5893143109747542</v>
+        <v>0.5893143109747544</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.6121097946402353</v>
+        <v>0.612109794640236</v>
       </c>
       <c r="AB8" t="n">
         <v>0.6145677924684183</v>
@@ -2902,64 +2902,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6139131954078554</v>
+        <v>0.6139131954078556</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6150305269156654</v>
+        <v>0.6150305269156648</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6141048205510161</v>
+        <v>0.6141048205510163</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04458525885673915</v>
+        <v>0.04458525885673931</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6287359130599495</v>
+        <v>0.628735913059949</v>
       </c>
       <c r="G2" t="n">
         <v>0.6158839443661771</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6222762765088625</v>
+        <v>0.6222762765088622</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6157815831882278</v>
+        <v>0.6157815831882277</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6205717994891196</v>
+        <v>0.6205717994891202</v>
       </c>
       <c r="K2" t="n">
         <v>0.6139974290123011</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6133704357534874</v>
+        <v>0.6133704357534873</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6176126459210581</v>
+        <v>0.617612645921058</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6166128689888211</v>
+        <v>0.6166128689888206</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6485050823805832</v>
+        <v>0.6485050823805824</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6297154763149293</v>
+        <v>0.6297154763149287</v>
       </c>
       <c r="Q2" t="n">
         <v>0.6317087891732649</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6199337828083232</v>
+        <v>0.619933782808323</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6135495564386002</v>
+        <v>0.6135495564386003</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6293424784115144</v>
+        <v>0.6293424784115143</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6217780014977583</v>
+        <v>0.6217780014977586</v>
       </c>
       <c r="V2" t="n">
         <v>1.099174784330459</v>
@@ -2968,19 +2968,19 @@
         <v>0.6350334960119569</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6142412985856612</v>
+        <v>0.6142412985856611</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6329126846044213</v>
+        <v>0.6329126846044211</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.6233371534839084</v>
+        <v>0.6233371534839083</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.616576689262387</v>
+        <v>0.6165766892623868</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.6148135026153314</v>
+        <v>0.6148135026153311</v>
       </c>
     </row>
     <row r="3">
@@ -2999,7 +2999,7 @@
         <v>0.6226704638604474</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03146319608230246</v>
+        <v>0.03146319608230243</v>
       </c>
       <c r="F3" t="n">
         <v>0.6226704638604474</v>
@@ -3078,85 +3078,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2290085433646394</v>
+        <v>0.2290085433646364</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5145455625192161</v>
+        <v>0.5145455625192165</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3004126052152479</v>
+        <v>0.3004126052152599</v>
       </c>
       <c r="E4" t="n">
-        <v>3.42103903467685</v>
+        <v>3.421039034676842</v>
       </c>
       <c r="F4" t="n">
-        <v>4.102795586709942</v>
+        <v>4.102795586709945</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6917097051182316</v>
+        <v>0.691709705118233</v>
       </c>
       <c r="H4" t="n">
-        <v>2.571790917072595</v>
+        <v>2.571790917072598</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7521449869066037</v>
+        <v>0.7521449869066021</v>
       </c>
       <c r="J4" t="n">
-        <v>1.761528782217697</v>
+        <v>1.761528782217698</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2535523161397036</v>
+        <v>0.2535523161397016</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1032772940590639</v>
+        <v>0.1032772940590753</v>
       </c>
       <c r="M4" t="n">
-        <v>1.240592638436751</v>
+        <v>1.24059263843675</v>
       </c>
       <c r="N4" t="n">
-        <v>0.943198373599446</v>
+        <v>0.94319837359945</v>
       </c>
       <c r="O4" t="n">
-        <v>7.952925581011517</v>
+        <v>7.952925581011515</v>
       </c>
       <c r="P4" t="n">
-        <v>3.948447423021959</v>
+        <v>3.948447423021964</v>
       </c>
       <c r="Q4" t="n">
         <v>4.731161956349373</v>
       </c>
       <c r="R4" t="n">
-        <v>1.891125419689491</v>
+        <v>1.891125419689489</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1437178695645814</v>
+        <v>0.1437178695645843</v>
       </c>
       <c r="T4" t="n">
-        <v>4.345580171063597</v>
+        <v>4.345580171063609</v>
       </c>
       <c r="U4" t="n">
         <v>2.14405579389997</v>
       </c>
       <c r="V4" t="n">
-        <v>2.996072061761154</v>
+        <v>2.99607206176116</v>
       </c>
       <c r="W4" t="n">
-        <v>5.600272391225811</v>
+        <v>5.600272391225795</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3321606322732706</v>
+        <v>0.3321606322732835</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.008890293894733</v>
+        <v>5.008890293894753</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.329033274973258</v>
+        <v>2.329033274973263</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.9179143603802314</v>
+        <v>0.9179143603802365</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.5155480056349011</v>
+        <v>0.5155480056349021</v>
       </c>
     </row>
     <row r="5">
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05186491565937193</v>
+        <v>0.05186491565937229</v>
       </c>
       <c r="C5" t="n">
-        <v>0.07166501452779557</v>
+        <v>0.07166501452779608</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07166501452779557</v>
+        <v>0.07166501452779608</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06112204595326765</v>
+        <v>0.0611220459532678</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05494953965064063</v>
+        <v>0.05494953965064068</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07577069401130694</v>
+        <v>0.07577069401130758</v>
       </c>
       <c r="H5" t="n">
-        <v>0.07166501452779557</v>
+        <v>0.07166501452779608</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07166501452779557</v>
+        <v>0.07166501452779608</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07227643388520007</v>
+        <v>0.07227643388520001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.07166501452779557</v>
+        <v>0.07166501452779608</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07166501452779558</v>
+        <v>0.07166501452779611</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07166501452782634</v>
+        <v>0.07166501452782677</v>
       </c>
       <c r="N5" t="n">
-        <v>0.943198373599446</v>
+        <v>0.05631662541199913</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06053449599216057</v>
+        <v>0.06053449599216108</v>
       </c>
       <c r="P5" t="n">
         <v>0.05950059399665741</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.04797374432522811</v>
+        <v>0.04797374432522907</v>
       </c>
       <c r="R5" t="n">
-        <v>0.07166501452779557</v>
+        <v>0.07166501452779608</v>
       </c>
       <c r="S5" t="n">
-        <v>0.07166501452779557</v>
+        <v>0.07166501452779608</v>
       </c>
       <c r="T5" t="n">
-        <v>0.07166501452779557</v>
+        <v>0.07166501452779608</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06201320827632535</v>
+        <v>0.0620132082763258</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0703242468640235</v>
+        <v>0.07032424686402372</v>
       </c>
       <c r="W5" t="n">
-        <v>0.07166890578213311</v>
+        <v>0.07166890578213335</v>
       </c>
       <c r="X5" t="n">
-        <v>0.04978846270999883</v>
+        <v>0.04978846270999857</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.09137294267061451</v>
+        <v>0.09137294267061549</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.05149711866028164</v>
+        <v>0.05149711866028205</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.07166501452779557</v>
+        <v>0.07166501452779608</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.09234787342306253</v>
+        <v>0.09234787342306269</v>
       </c>
     </row>
     <row r="6">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1008331767477547</v>
+        <v>0.1008331767477549</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1229936262506961</v>
+        <v>0.1229936262506965</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1229936262506961</v>
+        <v>0.1229936262506965</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1178791119437494</v>
+        <v>0.1178791119437495</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07190769608864213</v>
+        <v>0.07190769608864239</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1229936614136696</v>
+        <v>0.1229936614136694</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1229936262506961</v>
+        <v>0.1229936262506965</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1229936262506961</v>
+        <v>0.1229936262506965</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1236050456081002</v>
+        <v>0.1236050456081004</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1229936262506961</v>
+        <v>0.1229936262506965</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1229936262506961</v>
+        <v>0.1229936262506966</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1229936262506961</v>
+        <v>0.1229936262506965</v>
       </c>
       <c r="N6" t="n">
-        <v>0.943198373599446</v>
+        <v>0.1229936262506965</v>
       </c>
       <c r="O6" t="n">
         <v>0.1303376170152793</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1319348013575704</v>
+        <v>0.1319348013575709</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1229936614136696</v>
+        <v>0.1229936614136694</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1229936262506961</v>
+        <v>0.1229936262506965</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1229936262506961</v>
+        <v>0.1229936262506965</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1229936262506961</v>
+        <v>0.1229936262506965</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1229936262506961</v>
+        <v>0.1229936262506965</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1526236187106022</v>
+        <v>0.1526236187106025</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1229936262506961</v>
+        <v>0.1229936262506965</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1229936262506961</v>
+        <v>0.1229936262506966</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1229936262506961</v>
+        <v>0.1229936262506965</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.1096328597473078</v>
+        <v>0.1096328597473083</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.1229936262506961</v>
+        <v>0.1229936262506965</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1229936262506961</v>
+        <v>0.1229936262506965</v>
       </c>
     </row>
     <row r="7">
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6176183535645511</v>
+        <v>0.6176183535645512</v>
       </c>
       <c r="C7" t="n">
         <v>0.6111381675983886</v>
@@ -3351,76 +3351,76 @@
         <v>0.6165738921204922</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0481988029886166</v>
+        <v>-0.04819880298861646</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5313198115129678</v>
+        <v>0.5313198115129679</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6059033591016963</v>
+        <v>0.6059033591016965</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5690732968100928</v>
+        <v>0.5690732968100922</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6067820198988556</v>
+        <v>0.6067820198988547</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5805353070573165</v>
+        <v>0.5805353070573163</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6171951753335123</v>
+        <v>0.6171951753335121</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6208588332713245</v>
+        <v>0.6208588332713243</v>
       </c>
       <c r="M7" t="n">
         <v>0.5961278464626095</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6017949289267043</v>
+        <v>0.6017949289267045</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4115956203251659</v>
+        <v>0.4115956203251656</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5234118546961136</v>
+        <v>0.5234118546961137</v>
       </c>
       <c r="Q7" t="n">
         <v>0.5131788084773165</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5825891609396</v>
+        <v>0.5825891609395997</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6197906568583805</v>
+        <v>0.6197906568583809</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5273793785705708</v>
+        <v>0.5273793785705707</v>
       </c>
       <c r="U7" t="n">
         <v>0.5711032172836462</v>
       </c>
       <c r="V7" t="n">
-        <v>1.024170475905396</v>
+        <v>1.024170475905395</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4930070311750315</v>
+        <v>0.493007031175032</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6157678213854227</v>
+        <v>0.6157678213854223</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.505713196695794</v>
+        <v>0.5057131966957938</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.5616213075561517</v>
+        <v>0.5616213075561518</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.6019555040285589</v>
+        <v>0.6019555040285586</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.6124251036564301</v>
+        <v>0.6124251036564298</v>
       </c>
     </row>
     <row r="8">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6116144691231028</v>
+        <v>0.6116144691231027</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6097832953651811</v>
+        <v>0.6097832953651808</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6113308609807161</v>
+        <v>0.611330860980716</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008338795411743007</v>
+        <v>0.00833879541174316</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5871710751245899</v>
+        <v>0.5871710751245897</v>
       </c>
       <c r="G8" t="n">
         <v>0.6082548582673534</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5978893946969144</v>
+        <v>0.597889394696914</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6085522905522366</v>
+        <v>0.6085522905522369</v>
       </c>
       <c r="J8" t="n">
         <v>0.6012520456439628</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6115061552838366</v>
+        <v>0.6115061552838365</v>
       </c>
       <c r="L8" t="n">
         <v>0.6125461380621122</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6055356704187387</v>
+        <v>0.6055356704187389</v>
       </c>
       <c r="N8" t="n">
-        <v>0.607114434067585</v>
+        <v>0.6071144340675853</v>
       </c>
       <c r="O8" t="n">
-        <v>0.552465355916415</v>
+        <v>0.5524653559164149</v>
       </c>
       <c r="P8" t="n">
         <v>0.5845524928267385</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5818897370447382</v>
+        <v>0.581889737044738</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6016966622478038</v>
+        <v>0.6016966622478042</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6122392350752601</v>
+        <v>0.6122392350752593</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5859847309299493</v>
+        <v>0.58598473092995</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5983147399702499</v>
+        <v>0.5983147399702495</v>
       </c>
       <c r="V8" t="n">
-        <v>1.063302337034826</v>
+        <v>1.063302337034825</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5760362209272513</v>
+        <v>0.5760362209272512</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6111005742621082</v>
+        <v>0.6111005742621084</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5796967553238084</v>
+        <v>0.5796967553238087</v>
       </c>
       <c r="Z8" t="n">
         <v>0.5955595928133365</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.6071513165242173</v>
+        <v>0.6071513165242175</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.6101518310724769</v>
+        <v>0.6101518310724773</v>
       </c>
     </row>
   </sheetData>
@@ -3674,85 +3674,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6072734707937221</v>
+        <v>0.6072734707937216</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6073967099973063</v>
+        <v>0.6073967099973067</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6097197867435891</v>
+        <v>0.6097197867435894</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02893577687835905</v>
+        <v>0.02893577687835892</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6286297781684117</v>
+        <v>0.6286297781684119</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6091745379062568</v>
+        <v>0.6091745379062566</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6148911154108471</v>
+        <v>0.614891115410847</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6175542645752684</v>
+        <v>0.6175542645752681</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6128364515282415</v>
+        <v>0.6128364515282411</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6150359594881872</v>
+        <v>0.6150359594881876</v>
       </c>
       <c r="L2" t="n">
         <v>0.6139657198463361</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6160078760023571</v>
+        <v>0.6160078760023565</v>
       </c>
       <c r="N2" t="n">
-        <v>0.60880277658263</v>
+        <v>0.6088027765826309</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6315609731139259</v>
+        <v>0.6315609731139264</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6184319629366954</v>
+        <v>0.6184319629366959</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6282312757335149</v>
+        <v>0.6282312757335152</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6154559746487759</v>
+        <v>0.6154559746487756</v>
       </c>
       <c r="S2" t="n">
-        <v>0.613498747480104</v>
+        <v>0.6134987474801045</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6242030225071084</v>
+        <v>0.6242030225071088</v>
       </c>
       <c r="U2" t="n">
         <v>0.6102020805832373</v>
       </c>
       <c r="V2" t="n">
-        <v>1.07902351386043</v>
+        <v>1.079023513860429</v>
       </c>
       <c r="W2" t="n">
-        <v>0.622516533238067</v>
+        <v>0.6225165332380674</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6093584009270008</v>
+        <v>0.6093584009270006</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.611095637823272</v>
+        <v>0.6110956378232719</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.6091497500696097</v>
+        <v>0.6091497500696096</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.6097921741063586</v>
+        <v>0.6097921741063589</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.6074093073916422</v>
+        <v>0.6074093073916425</v>
       </c>
     </row>
     <row r="3">
@@ -3771,7 +3771,7 @@
         <v>0.6155009164550048</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02487285453008149</v>
+        <v>0.02487285453008171</v>
       </c>
       <c r="F3" t="n">
         <v>0.6155009164550048</v>
@@ -3786,7 +3786,7 @@
         <v>0.6155009164550048</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6154637104971816</v>
+        <v>0.6154637104971815</v>
       </c>
       <c r="K3" t="n">
         <v>0.6155009164550048</v>
@@ -3822,7 +3822,7 @@
         <v>0.6155009164550048</v>
       </c>
       <c r="V3" t="n">
-        <v>1.091997435066517</v>
+        <v>1.091997435066518</v>
       </c>
       <c r="W3" t="n">
         <v>0.6155009164550048</v>
@@ -3850,25 +3850,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3209240444825587</v>
+        <v>0.3209240444825605</v>
       </c>
       <c r="C4" t="n">
-        <v>0.372126097289929</v>
+        <v>0.3721260972899309</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9638139947146914</v>
+        <v>0.9638139947146966</v>
       </c>
       <c r="E4" t="n">
-        <v>1.046302645188633</v>
+        <v>1.046302645188632</v>
       </c>
       <c r="F4" t="n">
-        <v>5.859307011424294</v>
+        <v>5.859307011424304</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7495353114246509</v>
+        <v>0.7495353114246504</v>
       </c>
       <c r="H4" t="n">
-        <v>2.494201730570357</v>
+        <v>2.494201730570365</v>
       </c>
       <c r="I4" t="n">
         <v>3.052946793298602</v>
@@ -3877,58 +3877,58 @@
         <v>1.711933049846842</v>
       </c>
       <c r="K4" t="n">
-        <v>2.132980982803458</v>
+        <v>2.132980982803459</v>
       </c>
       <c r="L4" t="n">
-        <v>1.940042735320847</v>
+        <v>1.940042735320844</v>
       </c>
       <c r="M4" t="n">
-        <v>2.579546982262467</v>
+        <v>2.57954698226247</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7543655786914203</v>
+        <v>0.75436557869142</v>
       </c>
       <c r="O4" t="n">
-        <v>5.757952145492958</v>
+        <v>5.75795214549297</v>
       </c>
       <c r="P4" t="n">
-        <v>2.847048646605197</v>
+        <v>2.847048646605193</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.484323893963904</v>
+        <v>5.484323893963902</v>
       </c>
       <c r="R4" t="n">
         <v>2.595387256870612</v>
       </c>
       <c r="S4" t="n">
-        <v>1.779907064986803</v>
+        <v>1.779907064986804</v>
       </c>
       <c r="T4" t="n">
-        <v>4.86475307574426</v>
+        <v>4.864753075744259</v>
       </c>
       <c r="U4" t="n">
-        <v>1.011833936509766</v>
+        <v>1.011833936509768</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9158066116376814</v>
+        <v>0.9158066116376832</v>
       </c>
       <c r="W4" t="n">
-        <v>4.225957864500323</v>
+        <v>4.225957864500328</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8704982774137107</v>
+        <v>0.8704982774137099</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.334526208606014</v>
+        <v>1.334526208606018</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.6953220882970561</v>
+        <v>0.6953220882970528</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.9959056184409195</v>
+        <v>0.995905618440919</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.4174277730304105</v>
+        <v>0.4174277730304091</v>
       </c>
     </row>
     <row r="5">
@@ -3938,85 +3938,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03796104621691407</v>
+        <v>0.03796104621691339</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05471927071997189</v>
+        <v>0.05471927071997197</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05471927071997189</v>
+        <v>0.05471927071997197</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04579601051439637</v>
+        <v>0.04579601051439655</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04057178173373049</v>
+        <v>0.04057178173373075</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05819419773820571</v>
+        <v>0.05819419773820618</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05471927071997189</v>
+        <v>0.05471927071997197</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05471927071997189</v>
+        <v>0.05471927071997197</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0552567971450745</v>
+        <v>0.05525679714507505</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05471927071997189</v>
+        <v>0.05471927071997197</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0547192707199718</v>
+        <v>0.05471927071997199</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05471927072003944</v>
+        <v>0.05471927072003922</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7543655786914203</v>
+        <v>0.04172884313298843</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04529872541347696</v>
+        <v>0.0452987254134773</v>
       </c>
       <c r="P5" t="n">
-        <v>0.04442366100754954</v>
+        <v>0.0444236610075496</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0346676726217565</v>
+        <v>0.03466767262175665</v>
       </c>
       <c r="R5" t="n">
-        <v>0.05471927071997189</v>
+        <v>0.05471927071997197</v>
       </c>
       <c r="S5" t="n">
-        <v>0.05471927071997189</v>
+        <v>0.05471927071997197</v>
       </c>
       <c r="T5" t="n">
-        <v>0.05471927071997189</v>
+        <v>0.05471927071997197</v>
       </c>
       <c r="U5" t="n">
-        <v>0.04636184543262854</v>
+        <v>0.04636184543262891</v>
       </c>
       <c r="V5" t="n">
-        <v>0.05352773641597888</v>
+        <v>0.05352773641597886</v>
       </c>
       <c r="W5" t="n">
-        <v>0.05472256416330485</v>
+        <v>0.05472256416330538</v>
       </c>
       <c r="X5" t="n">
-        <v>0.03620359717936508</v>
+        <v>0.03620359717936564</v>
       </c>
       <c r="Y5" t="n">
         <v>0.07107715486305566</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03764975359546456</v>
+        <v>0.03764975359546421</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.05471927071997189</v>
+        <v>0.05471927071997197</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.07222463748742759</v>
+        <v>0.07222463748742704</v>
       </c>
     </row>
     <row r="6">
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.06728317363328512</v>
+        <v>0.0672831736332847</v>
       </c>
       <c r="C6" t="n">
-        <v>0.08268643138082735</v>
+        <v>0.08268643138082687</v>
       </c>
       <c r="D6" t="n">
-        <v>0.08268643138082735</v>
+        <v>0.08268643138082687</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07913142407182305</v>
+        <v>0.07913142407182271</v>
       </c>
       <c r="F6" t="n">
         <v>0.04717771535459845</v>
       </c>
       <c r="G6" t="n">
-        <v>0.08268643365640389</v>
+        <v>0.08268643365640342</v>
       </c>
       <c r="H6" t="n">
-        <v>0.08268643138082735</v>
+        <v>0.08268643138082687</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08268643138082735</v>
+        <v>0.08268643138082687</v>
       </c>
       <c r="J6" t="n">
-        <v>0.08322395780593085</v>
+        <v>0.08322395780593055</v>
       </c>
       <c r="K6" t="n">
-        <v>0.08268643138082735</v>
+        <v>0.08268643138082687</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08268643138082722</v>
+        <v>0.08268643138082694</v>
       </c>
       <c r="M6" t="n">
-        <v>0.08268643138082735</v>
+        <v>0.08268643138082687</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7543655786914203</v>
+        <v>0.08268643138082687</v>
       </c>
       <c r="O6" t="n">
-        <v>0.08779105385922037</v>
+        <v>0.08779105385922022</v>
       </c>
       <c r="P6" t="n">
-        <v>0.08890122117279975</v>
+        <v>0.08890122117279908</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.08268643365640389</v>
+        <v>0.08268643365640342</v>
       </c>
       <c r="R6" t="n">
-        <v>0.08268643138082735</v>
+        <v>0.08268643138082687</v>
       </c>
       <c r="S6" t="n">
-        <v>0.08268643138082735</v>
+        <v>0.08268643138082687</v>
       </c>
       <c r="T6" t="n">
-        <v>0.08268643138082735</v>
+        <v>0.08268643138082687</v>
       </c>
       <c r="U6" t="n">
-        <v>0.08268643138082735</v>
+        <v>0.08268643138082687</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1040464495056219</v>
+        <v>0.104046449505622</v>
       </c>
       <c r="W6" t="n">
-        <v>0.08268643138082735</v>
+        <v>0.08268643138082687</v>
       </c>
       <c r="X6" t="n">
-        <v>0.08268643138082722</v>
+        <v>0.08268643138082694</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.08268643138082735</v>
+        <v>0.08268643138082687</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0733996375737886</v>
+        <v>0.07339963757378785</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.08268643138082735</v>
+        <v>0.08268643138082687</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.08268643138082735</v>
+        <v>0.08268643138082689</v>
       </c>
     </row>
     <row r="7">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.607668513765962</v>
+        <v>0.6076685137659631</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6070576531059739</v>
+        <v>0.6070576531059749</v>
       </c>
       <c r="D7" t="n">
         <v>0.5934599493361232</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0009268441098602864</v>
+        <v>-0.000926844109860165</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4833421888338437</v>
+        <v>0.4833421888338444</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5963693834430898</v>
+        <v>0.5963693834430902</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5635217053302807</v>
+        <v>0.5635217053302809</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5476964300805709</v>
+        <v>0.547696430080571</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5747374170547193</v>
+        <v>0.574737417054719</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5622448893536235</v>
+        <v>0.5622448893536228</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5681542308930454</v>
+        <v>0.5681542308930457</v>
       </c>
       <c r="M7" t="n">
-        <v>0.556850728445288</v>
+        <v>0.5568507284452874</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5987607990273466</v>
+        <v>0.5987607990273469</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4630120764802508</v>
+        <v>0.4630120764802501</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5411378724192728</v>
+        <v>0.5411378724192721</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4846946758152787</v>
+        <v>0.4846946758152801</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5600793286259047</v>
+        <v>0.5600793286259045</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5707718214813284</v>
+        <v>0.570771821481329</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5086918042312885</v>
+        <v>0.5086918042312883</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5903791956063646</v>
+        <v>0.5903791956063645</v>
       </c>
       <c r="V7" t="n">
-        <v>1.068058296596599</v>
+        <v>1.068058296596601</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5177665579353734</v>
+        <v>0.5177665579353741</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5955575975898288</v>
+        <v>0.5955575975898285</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5852213902211969</v>
+        <v>0.585221390221197</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.596527256175621</v>
+        <v>0.5965272561756216</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.592883814299757</v>
+        <v>0.5928838142997567</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.6069955963260756</v>
+        <v>0.6069955963260754</v>
       </c>
     </row>
     <row r="8">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6037097026098206</v>
+        <v>0.603709702609821</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6035549982664136</v>
+        <v>0.6035549982664137</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5996910764641041</v>
+        <v>0.5996910764641035</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01719683177842436</v>
+        <v>0.01719683177842422</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5684971359359089</v>
+        <v>0.5684971359359091</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6004696294172571</v>
+        <v>0.6004696294172569</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5912404087011813</v>
+        <v>0.5912404087011803</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5867030071948238</v>
+        <v>0.5867030071948242</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5943058582249243</v>
+        <v>0.5943058582249241</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5908042974401712</v>
+        <v>0.5908042974401707</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5924228270307108</v>
+        <v>0.5924228270307107</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5893218535508771</v>
+        <v>0.5893218535508765</v>
       </c>
       <c r="N8" t="n">
-        <v>0.601185969805458</v>
+        <v>0.6011859698054575</v>
       </c>
       <c r="O8" t="n">
         <v>0.5621780649723149</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5845965409194782</v>
+        <v>0.5845965409194787</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5687140193876851</v>
+        <v>0.568714019387685</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5902389755684143</v>
+        <v>0.5902389755684148</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5931468667239143</v>
+        <v>0.5931468667239145</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5756045360648732</v>
+        <v>0.5756045360648738</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5987716175389323</v>
+        <v>0.598771617538932</v>
       </c>
       <c r="V8" t="n">
         <v>1.06813112956711</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5780470886507152</v>
+        <v>0.5780470886507161</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6002841272877599</v>
+        <v>0.6002841272877597</v>
       </c>
       <c r="Y8" t="n">
         <v>0.5973183568917648</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.6005166741770226</v>
+        <v>0.6005166741770234</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.5995013205492927</v>
+        <v>0.5995013205492929</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.6035393596281324</v>
+        <v>0.6035393596281328</v>
       </c>
     </row>
   </sheetData>
@@ -4446,58 +4446,58 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6248928412135076</v>
+        <v>0.6248928412135075</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6262495639490644</v>
+        <v>0.6262495639490642</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6261737018087398</v>
+        <v>0.6261737018087394</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06926089032518809</v>
+        <v>0.0692608903251882</v>
       </c>
       <c r="F2" t="n">
-        <v>0.630606436036627</v>
+        <v>0.6306064360366267</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6348791552309978</v>
+        <v>0.6348791552309977</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6287698833672642</v>
+        <v>0.6287698833672646</v>
       </c>
       <c r="I2" t="n">
         <v>0.6272151132641021</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6410387912986474</v>
+        <v>0.641038791298647</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6278157051738913</v>
+        <v>0.627815705173891</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6253514304604549</v>
+        <v>0.6253514304604548</v>
       </c>
       <c r="M2" t="n">
-        <v>0.646590696240981</v>
+        <v>0.6465906962409805</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6396973378876245</v>
+        <v>0.6396973378876244</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6796478544425263</v>
+        <v>0.6796478544425264</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6607398876016972</v>
+        <v>0.660739887601697</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.645633311502914</v>
+        <v>0.6456333115029139</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6277396791268779</v>
+        <v>0.6277396791268778</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6256592800083188</v>
+        <v>0.6256592800083186</v>
       </c>
       <c r="T2" t="n">
         <v>0.6477386423516965</v>
@@ -4506,22 +4506,22 @@
         <v>0.6410948664514285</v>
       </c>
       <c r="V2" t="n">
-        <v>1.115493101181715</v>
+        <v>1.115493101181714</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6633391481921347</v>
+        <v>0.6633391481921348</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6254148176346928</v>
+        <v>0.6254148176346926</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6581715364931635</v>
+        <v>0.6581715364931638</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.6448949688286567</v>
+        <v>0.6448949688286566</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.6281031223297122</v>
+        <v>0.6281031223297118</v>
       </c>
       <c r="AB2" t="n">
         <v>0.6401999256976842</v>
@@ -4534,85 +4534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6341352621592844</v>
+        <v>0.6341352621592843</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6341352621592844</v>
+        <v>0.6341352621592843</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6341352621592844</v>
+        <v>0.6341352621592843</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04266144101051928</v>
+        <v>0.0426614410105195</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6341352621592844</v>
+        <v>0.6341352621592843</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6341352621592844</v>
+        <v>0.6341352621592843</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6341352621592844</v>
+        <v>0.6341352621592843</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6341352621592844</v>
+        <v>0.6341352621592843</v>
       </c>
       <c r="J3" t="n">
         <v>0.6344184193497909</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6341352621592844</v>
+        <v>0.6341352621592843</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6341352621592844</v>
+        <v>0.6341352621592843</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6341352621592844</v>
+        <v>0.6341352621592843</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6341352621592844</v>
+        <v>0.6341352621592843</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6341352621592844</v>
+        <v>0.6341352621592843</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6341352621592844</v>
+        <v>0.6341352621592843</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6341352621592844</v>
+        <v>0.6341352621592843</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6341352621592844</v>
+        <v>0.6341352621592843</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6341352621592844</v>
+        <v>0.6341352621592843</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6341352621592844</v>
+        <v>0.6341352621592843</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6341352621592844</v>
+        <v>0.6341352621592843</v>
       </c>
       <c r="V3" t="n">
-        <v>1.113809797737461</v>
+        <v>1.11380979773746</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6341352621592844</v>
+        <v>0.6341352621592843</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6341352621592844</v>
+        <v>0.6341352621592843</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.6341352621592844</v>
+        <v>0.6341352621592843</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.6341352621592844</v>
+        <v>0.6341352621592843</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.6341352621592844</v>
+        <v>0.6341352621592843</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.6341352621592844</v>
+        <v>0.6341352621592843</v>
       </c>
     </row>
     <row r="4">
@@ -4622,85 +4622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1614993986024457</v>
+        <v>0.1614993986024462</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5406455338033913</v>
+        <v>0.540645533803391</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5316531097652082</v>
+        <v>0.5316531097652092</v>
       </c>
       <c r="E4" t="n">
-        <v>7.322527389405479</v>
+        <v>7.322527389405483</v>
       </c>
       <c r="F4" t="n">
-        <v>1.757229786842162</v>
+        <v>1.757229786842163</v>
       </c>
       <c r="G4" t="n">
-        <v>2.46741007310989</v>
+        <v>2.467410073109889</v>
       </c>
       <c r="H4" t="n">
         <v>1.315654898281978</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8338015392582957</v>
+        <v>0.8338015392582954</v>
       </c>
       <c r="J4" t="n">
-        <v>4.104787027542683</v>
+        <v>4.104787027542684</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9136405146832799</v>
+        <v>0.9136405146832808</v>
       </c>
       <c r="L4" t="n">
-        <v>0.279634811573289</v>
+        <v>0.2796348115732891</v>
       </c>
       <c r="M4" t="n">
         <v>5.714398216058377</v>
       </c>
       <c r="N4" t="n">
-        <v>4.124552008383039</v>
+        <v>4.12455200838304</v>
       </c>
       <c r="O4" t="n">
-        <v>13.18827106667263</v>
+        <v>13.18827106667262</v>
       </c>
       <c r="P4" t="n">
-        <v>9.236545386445625</v>
+        <v>9.236545386445648</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.615883475877532</v>
+        <v>5.615883475877526</v>
       </c>
       <c r="R4" t="n">
         <v>1.005168116808654</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3319902769283261</v>
+        <v>0.3319902769283259</v>
       </c>
       <c r="T4" t="n">
-        <v>6.290825479939781</v>
+        <v>6.290825479939775</v>
       </c>
       <c r="U4" t="n">
-        <v>4.314470193286525</v>
+        <v>4.314470193286533</v>
       </c>
       <c r="V4" t="n">
-        <v>4.617823137064295</v>
+        <v>4.617823137064299</v>
       </c>
       <c r="W4" t="n">
-        <v>10.62554196065834</v>
+        <v>10.62554196065836</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3156844672986247</v>
+        <v>0.3156844672986255</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.077293637341487</v>
+        <v>9.077293637341489</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.950307155223204</v>
+        <v>4.950307155223209</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.037917352602534</v>
+        <v>1.037917352602533</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.551768036240587</v>
+        <v>4.551768036240583</v>
       </c>
     </row>
     <row r="5">
@@ -4710,85 +4710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07967869292288712</v>
+        <v>0.07967869292288737</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1129635024998233</v>
+        <v>0.1129635024998237</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1129635024998233</v>
+        <v>0.1129635024998237</v>
       </c>
       <c r="E5" t="n">
-        <v>0.09524032324834543</v>
+        <v>0.0952403232483454</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08486407724253796</v>
+        <v>0.08486407724253815</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1198653245929766</v>
+        <v>0.1198653245929765</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1129635024998233</v>
+        <v>0.1129635024998237</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1129635024998233</v>
+        <v>0.1129635024998237</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1135656703128762</v>
+        <v>0.1135656703128763</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1129635024998233</v>
+        <v>0.1129635024998237</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1129635024998233</v>
+        <v>0.1129635024998237</v>
       </c>
       <c r="M5" t="n">
-        <v>0.112963502499853</v>
+        <v>0.1129635024998533</v>
       </c>
       <c r="N5" t="n">
-        <v>4.124552008383039</v>
+        <v>0.08716220664020065</v>
       </c>
       <c r="O5" t="n">
-        <v>0.09425262675129872</v>
+        <v>0.09425262675129897</v>
       </c>
       <c r="P5" t="n">
-        <v>0.09251459345565073</v>
+        <v>0.09251459345565084</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.07313746816263561</v>
+        <v>0.0731374681626358</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1129635024998233</v>
+        <v>0.1129635024998237</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1129635024998233</v>
+        <v>0.1129635024998237</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1129635024998233</v>
+        <v>0.1129635024998237</v>
       </c>
       <c r="U5" t="n">
-        <v>0.09668533717932914</v>
+        <v>0.09668533717932939</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1078301728066675</v>
+        <v>0.1078301728066674</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1129700438796225</v>
+        <v>0.1129700438796229</v>
       </c>
       <c r="X5" t="n">
-        <v>0.07618808707436626</v>
+        <v>0.07618808707436625</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1460025854192452</v>
+        <v>0.1460025854192453</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.07906041049975732</v>
+        <v>0.07906041049975712</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1129635024998233</v>
+        <v>0.1129635024998237</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1477322692974128</v>
+        <v>0.1477322692974127</v>
       </c>
     </row>
     <row r="6">
@@ -4798,16 +4798,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1732807342482308</v>
+        <v>0.1732807342482307</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2136541640041345</v>
+        <v>0.2136541640041344</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2136541640041345</v>
+        <v>0.2136541640041344</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2043361578129919</v>
+        <v>0.204336157812992</v>
       </c>
       <c r="F6" t="n">
         <v>0.1205823610962472</v>
@@ -4816,67 +4816,67 @@
         <v>0.2136541857360717</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2136541640041345</v>
+        <v>0.2136541640041344</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2136541640041345</v>
+        <v>0.2136541640041344</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2142563318171866</v>
+        <v>0.2142563318171868</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2136541640041345</v>
+        <v>0.2136541640041344</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2136541640041345</v>
+        <v>0.2136541640041344</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2136541640041345</v>
+        <v>0.2136541640041344</v>
       </c>
       <c r="N6" t="n">
-        <v>4.124552008383039</v>
+        <v>0.2136541640041344</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2270338946946262</v>
+        <v>0.2270338946946266</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2299437518359658</v>
+        <v>0.2299437518359662</v>
       </c>
       <c r="Q6" t="n">
         <v>0.2136541857360717</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2136541640041345</v>
+        <v>0.2136541640041344</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2136541640041345</v>
+        <v>0.2136541640041344</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2136541640041345</v>
+        <v>0.2136541640041344</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2136541640041345</v>
+        <v>0.2136541640041344</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2642437318383993</v>
+        <v>0.2642437318383994</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2136541640041345</v>
+        <v>0.2136541640041344</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2136541640041345</v>
+        <v>0.2136541640041344</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.2136541640041345</v>
+        <v>0.2136541640041344</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.1893125846362908</v>
+        <v>0.1893125846362911</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.2136541640041345</v>
+        <v>0.2136541640041344</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.2136541640041345</v>
+        <v>0.2136541640041344</v>
       </c>
     </row>
     <row r="7">
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6312810468156707</v>
+        <v>0.6312810468156709</v>
       </c>
       <c r="C7" t="n">
         <v>0.6233657094088997</v>
       </c>
       <c r="D7" t="n">
-        <v>0.623822565784974</v>
+        <v>0.6238225657849742</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1173302024903278</v>
+        <v>-0.1173302024903277</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5980347853188404</v>
+        <v>0.5980347853188397</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5719053558231268</v>
+        <v>0.5719053558231271</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6087875528848532</v>
+        <v>0.6087875528848533</v>
       </c>
       <c r="I7" t="n">
         <v>0.6177532171143097</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5376957256948887</v>
+        <v>0.5376957256948888</v>
       </c>
       <c r="K7" t="n">
         <v>0.6141762019634006</v>
       </c>
       <c r="L7" t="n">
-        <v>0.628587947654404</v>
+        <v>0.6285879476544038</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5047224190690481</v>
+        <v>0.5047224190690479</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5442286140044881</v>
+        <v>0.544228614004488</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3051761509024653</v>
+        <v>0.3051761509024649</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4175931983516432</v>
+        <v>0.4175931983516438</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5095194208779288</v>
+        <v>0.5095194208779285</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6147266425839458</v>
+        <v>0.614726642583946</v>
       </c>
       <c r="S7" t="n">
         <v>0.6267443063278774</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4975920058267355</v>
+        <v>0.4975920058267361</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5354168174254028</v>
+        <v>0.5354168174254027</v>
       </c>
       <c r="V7" t="n">
         <v>1.001552865974134</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4043946638469333</v>
+        <v>0.4043946638469332</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6282620922080346</v>
+        <v>0.6282620922080344</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4352155457642916</v>
+        <v>0.4352155457642914</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.5124199186744399</v>
+        <v>0.5124199186744397</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.6123745248864259</v>
+        <v>0.6123745248864254</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.5416846491132318</v>
+        <v>0.541684649113232</v>
       </c>
     </row>
     <row r="8">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6235941641363183</v>
+        <v>0.6235941641363186</v>
       </c>
       <c r="C8" t="n">
         <v>0.6213493831271111</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6214813920938151</v>
+        <v>0.621481392093815</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.003535817330812994</v>
+        <v>-0.003535817330812849</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6141806040288312</v>
+        <v>0.6141806040288315</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6065643495331011</v>
+        <v>0.6065643495331013</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6172365948690413</v>
+        <v>0.6172365948690415</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6197612305621593</v>
+        <v>0.6197612305621591</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5970296574487314</v>
+        <v>0.5970296574487316</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6187342691790126</v>
+        <v>0.6187342691790121</v>
       </c>
       <c r="L8" t="n">
         <v>0.6228273846824922</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5877074402206626</v>
+        <v>0.5877074402206623</v>
       </c>
       <c r="N8" t="n">
-        <v>0.598789526461705</v>
+        <v>0.5987895264617047</v>
       </c>
       <c r="O8" t="n">
-        <v>0.529970410490188</v>
+        <v>0.5299704104901878</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5622125584906077</v>
+        <v>0.5622125584906075</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5889327065927736</v>
+        <v>0.5889327065927741</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6189086953684981</v>
+        <v>0.6189086953684978</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6222963715514495</v>
+        <v>0.6222963715514497</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5856110255828476</v>
+        <v>0.5856110255828472</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5961776595004952</v>
+        <v>0.5961776595004953</v>
       </c>
       <c r="V8" t="n">
-        <v>1.064415839487785</v>
+        <v>1.064415839487786</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5588064438201688</v>
+        <v>0.5588064438201686</v>
       </c>
       <c r="X8" t="n">
         <v>0.6227425065901921</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5676624316139187</v>
+        <v>0.5676624316139189</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5895140996592673</v>
+        <v>0.589514099659267</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.6182019175232065</v>
+        <v>0.6182019175232062</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.5981346021391081</v>
+        <v>0.5981346021391079</v>
       </c>
     </row>
   </sheetData>
@@ -5218,61 +5218,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6149367872367304</v>
+        <v>0.61493678723673</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6165122044295557</v>
+        <v>0.6165122044295553</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6153407796162819</v>
+        <v>0.6153407796162809</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03902585650695675</v>
+        <v>0.03902585650695667</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6298294345790049</v>
+        <v>0.6298294345790044</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6248297930358981</v>
+        <v>0.6248297930358977</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6175534671672298</v>
+        <v>0.6175534671672296</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6165165277292347</v>
+        <v>0.616516527729234</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6270428674156491</v>
+        <v>0.6270428674156489</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6158759975796971</v>
+        <v>0.6158759975796969</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6152553038653297</v>
+        <v>0.6152553038653298</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6332124583279222</v>
+        <v>0.6332124583279218</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6271963346972474</v>
+        <v>0.6271963346972478</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6707000382419552</v>
+        <v>0.6707000382419548</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6500805022850056</v>
+        <v>0.6500805022850055</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6257746384184155</v>
+        <v>0.6257746384184153</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6156257632197136</v>
+        <v>0.6156257632197132</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6159673420400605</v>
+        <v>0.615967342040061</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6323266499932203</v>
+        <v>0.6323266499932195</v>
       </c>
       <c r="U2" t="n">
         <v>0.6301703552335445</v>
@@ -5281,22 +5281,22 @@
         <v>1.09956870504045</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6386756094534419</v>
+        <v>0.638675609453442</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6315193219475266</v>
+        <v>0.6315193219475261</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6391994799280913</v>
+        <v>0.6391994799280909</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.6218148832581957</v>
+        <v>0.6218148832581953</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.6176547743371654</v>
+        <v>0.6176547743371652</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.6320417428837847</v>
+        <v>0.6320417428837842</v>
       </c>
     </row>
     <row r="3">
@@ -5306,85 +5306,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6242610785249179</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6242610785249179</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6242610785249179</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03030757540724198</v>
+        <v>0.03030757540724221</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6242610785249179</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6242610785249179</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6242610785249179</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6242610785249179</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6244226532489505</v>
+        <v>0.6244226532489496</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6242610785249179</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6242610785249179</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6242610785249179</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6242610785249179</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6242610785249179</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6242610785249179</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6242610785249179</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6242610785249179</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6242610785249179</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6242610785249179</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6242610785249179</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="V3" t="n">
-        <v>1.103687899720697</v>
+        <v>1.103687899720696</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6242610785249179</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6242610785249179</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.6242610785249179</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.6242610785249179</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.6242610785249179</v>
+        <v>0.6242610785249173</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.6242610785249179</v>
+        <v>0.6242610785249173</v>
       </c>
     </row>
     <row r="4">
@@ -5394,85 +5394,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09914276234670467</v>
+        <v>0.0991427623467047</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4912099720264004</v>
+        <v>0.4912099720264002</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2073354258649338</v>
+        <v>0.2073354258649334</v>
       </c>
       <c r="E4" t="n">
-        <v>2.280213330506894</v>
+        <v>2.280213330506895</v>
       </c>
       <c r="F4" t="n">
-        <v>3.8400050340763</v>
+        <v>3.840005034076301</v>
       </c>
       <c r="G4" t="n">
-        <v>2.156972550144503</v>
+        <v>2.156972550144505</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8136336731659866</v>
+        <v>0.813633673165986</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5123710282307952</v>
+        <v>0.5123710282307937</v>
       </c>
       <c r="J4" t="n">
-        <v>2.780419812118912</v>
+        <v>2.780419812118911</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3252650280762225</v>
+        <v>0.3252650280762221</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1743618758322498</v>
+        <v>0.1743618758322491</v>
       </c>
       <c r="M4" t="n">
-        <v>4.137859763199255</v>
+        <v>4.13785976319925</v>
       </c>
       <c r="N4" t="n">
-        <v>3.087696440115826</v>
+        <v>3.087696440115822</v>
       </c>
       <c r="O4" t="n">
-        <v>12.40663003039554</v>
+        <v>12.40663003039555</v>
       </c>
       <c r="P4" t="n">
-        <v>8.235140912167232</v>
+        <v>8.235140912167239</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.512106171586905</v>
+        <v>2.512106171586901</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2891705255123168</v>
+        <v>0.2891705255123158</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3167263317870105</v>
+        <v>0.3167263317870109</v>
       </c>
       <c r="T4" t="n">
-        <v>4.320970770153848</v>
+        <v>4.320970770153842</v>
       </c>
       <c r="U4" t="n">
-        <v>3.289367292705477</v>
+        <v>3.289367292705474</v>
       </c>
       <c r="V4" t="n">
-        <v>2.884413063910267</v>
+        <v>2.884413063910265</v>
       </c>
       <c r="W4" t="n">
-        <v>5.728856802196074</v>
+        <v>5.728856802196068</v>
       </c>
       <c r="X4" t="n">
-        <v>4.10321883045724</v>
+        <v>4.103218830457244</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.236385489652559</v>
+        <v>6.236385489652561</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.612683154712455</v>
+        <v>1.612683154712452</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.7885442389833811</v>
+        <v>0.788544238983382</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.451171542900286</v>
+        <v>4.451171542900287</v>
       </c>
     </row>
     <row r="5">
@@ -5482,85 +5482,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05873873656429751</v>
+        <v>0.05873873656429735</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08290647494121282</v>
+        <v>0.08290647494121221</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08290647494121282</v>
+        <v>0.08290647494121221</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07003786716468111</v>
+        <v>0.07003786716468102</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06250378774587233</v>
+        <v>0.06250378774587242</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08791781292976088</v>
+        <v>0.0879178129297605</v>
       </c>
       <c r="H5" t="n">
-        <v>0.08290647494121282</v>
+        <v>0.08290647494121221</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08290647494121282</v>
+        <v>0.08290647494121221</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08348460266161505</v>
+        <v>0.08348460266161445</v>
       </c>
       <c r="K5" t="n">
-        <v>0.08290647494121282</v>
+        <v>0.08290647494121221</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08290647494121282</v>
+        <v>0.08290647494121221</v>
       </c>
       <c r="M5" t="n">
-        <v>0.08290647494121897</v>
+        <v>0.08290647494121833</v>
       </c>
       <c r="N5" t="n">
-        <v>3.087696440115826</v>
+        <v>0.06417243451744852</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06932071147679042</v>
+        <v>0.06932071147678999</v>
       </c>
       <c r="P5" t="n">
-        <v>0.06805874439575461</v>
+        <v>0.06805874439575432</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.05398922437886831</v>
+        <v>0.05398922437886865</v>
       </c>
       <c r="R5" t="n">
-        <v>0.08290647494121282</v>
+        <v>0.08290647494121221</v>
       </c>
       <c r="S5" t="n">
-        <v>0.08290647494121282</v>
+        <v>0.08290647494121221</v>
       </c>
       <c r="T5" t="n">
-        <v>0.08290647494121282</v>
+        <v>0.08290647494121221</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07104259658231374</v>
+        <v>0.07104259658231375</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0800707969102058</v>
+        <v>0.08007079691020559</v>
       </c>
       <c r="W5" t="n">
-        <v>0.08291122456684448</v>
+        <v>0.08291122456684415</v>
       </c>
       <c r="X5" t="n">
-        <v>0.05620424560631008</v>
+        <v>0.05620424560630984</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1068197023994915</v>
+        <v>0.1068197023994913</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.05828980841850704</v>
+        <v>0.05828980841850675</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.08290647494121282</v>
+        <v>0.08290647494121221</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1081516985239817</v>
+        <v>0.1081516985239813</v>
       </c>
     </row>
     <row r="6">
@@ -5570,7 +5570,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1177245186623807</v>
+        <v>0.1177245186623802</v>
       </c>
       <c r="C6" t="n">
         <v>0.1445564523732748</v>
@@ -5579,10 +5579,10 @@
         <v>0.1445564523732748</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1383637345033775</v>
+        <v>0.1383637345033772</v>
       </c>
       <c r="F6" t="n">
-        <v>0.08270155091296175</v>
+        <v>0.08270155091296187</v>
       </c>
       <c r="G6" t="n">
         <v>0.1445564302531514</v>
@@ -5594,7 +5594,7 @@
         <v>0.1445564523732748</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1451345800936775</v>
+        <v>0.1451345800936769</v>
       </c>
       <c r="K6" t="n">
         <v>0.1445564523732748</v>
@@ -5606,13 +5606,13 @@
         <v>0.1445564523732748</v>
       </c>
       <c r="N6" t="n">
-        <v>3.087696440115826</v>
+        <v>0.1445564523732748</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1534484906209455</v>
+        <v>0.1534484906209453</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1553823611888783</v>
+        <v>0.155382361188878</v>
       </c>
       <c r="Q6" t="n">
         <v>0.1445564302531514</v>
@@ -5630,7 +5630,7 @@
         <v>0.1445564523732748</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1793645040216921</v>
+        <v>0.1793645040216918</v>
       </c>
       <c r="W6" t="n">
         <v>0.1445564523732748</v>
@@ -5642,7 +5642,7 @@
         <v>0.1445564523732748</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.1283791735505909</v>
+        <v>0.128379173550591</v>
       </c>
       <c r="AA6" t="n">
         <v>0.1445564523732748</v>
@@ -5658,85 +5658,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6225222660597252</v>
+        <v>0.6225222660597246</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6133084930733206</v>
+        <v>0.6133084930733198</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6201828519477562</v>
+        <v>0.6201828519477559</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.02313590818508266</v>
+        <v>-0.02313590818508277</v>
       </c>
       <c r="F7" t="n">
-        <v>0.53574919441392</v>
+        <v>0.5357491944139192</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5637007517980502</v>
+        <v>0.5637007517980493</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6073369607800403</v>
+        <v>0.6073369607800396</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6133164204619057</v>
+        <v>0.613316420461905</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5521040307690703</v>
+        <v>0.5521040307690694</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6170375517601061</v>
+        <v>0.6170375517601058</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6206502399086679</v>
+        <v>0.6206502399086669</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5159117247447125</v>
+        <v>0.5159117247447119</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5504274599348999</v>
+        <v>0.5504274599348996</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2904138745522102</v>
+        <v>0.2904138745522094</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4130291460120592</v>
+        <v>0.4130291460120596</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5588994590340723</v>
+        <v>0.558899459034072</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6185362497102472</v>
+        <v>0.6185362497102468</v>
       </c>
       <c r="S7" t="n">
         <v>0.6164156542224716</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5207533501500078</v>
+        <v>0.5207533501500077</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5323832107974938</v>
+        <v>0.5323832107974934</v>
       </c>
       <c r="V7" t="n">
         <v>1.026510018336417</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4824302251472075</v>
+        <v>0.4824302251472068</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5253214152926744</v>
+        <v>0.5253214152926738</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4795724016398821</v>
+        <v>0.4795724016398813</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.581650549374149</v>
+        <v>0.5816505493741487</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.6065091216863646</v>
+        <v>0.606509121686364</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.522379721859843</v>
+        <v>0.5223797218598432</v>
       </c>
     </row>
     <row r="8">
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6141456220238004</v>
+        <v>0.6141456220238001</v>
       </c>
       <c r="C8" t="n">
-        <v>0.61152874314526</v>
+        <v>0.6115287431452594</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6134851735271365</v>
+        <v>0.6134851735271362</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01470890115817215</v>
+        <v>0.01470890115817224</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5895562452378627</v>
+        <v>0.5895562452378628</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5972746513808631</v>
+        <v>0.597274651380863</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6098529396593472</v>
+        <v>0.6098529396593465</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6115366734320082</v>
+        <v>0.6115366734320077</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5941376637215282</v>
+        <v>0.5941376637215278</v>
       </c>
       <c r="K8" t="n">
-        <v>0.612589269881694</v>
+        <v>0.6125892698816935</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6136123607878758</v>
+        <v>0.6136123607878756</v>
       </c>
       <c r="M8" t="n">
-        <v>0.583913157069026</v>
+        <v>0.5839131570690258</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5936018029450083</v>
+        <v>0.593601802945008</v>
       </c>
       <c r="O8" t="n">
-        <v>0.51879849652646</v>
+        <v>0.5187984965264594</v>
       </c>
       <c r="P8" t="n">
-        <v>0.553969299835427</v>
+        <v>0.5539692998354273</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.596034893254958</v>
+        <v>0.5960348932549584</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6130209478650914</v>
+        <v>0.6130209478650906</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6123976489805641</v>
+        <v>0.6123976489805647</v>
       </c>
       <c r="T8" t="n">
-        <v>0.585230303723078</v>
+        <v>0.5852303037230774</v>
       </c>
       <c r="U8" t="n">
-        <v>0.588365632620175</v>
+        <v>0.5883656326201747</v>
       </c>
       <c r="V8" t="n">
         <v>1.064452523059288</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5741421191784721</v>
+        <v>0.5741421191784725</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5865014598748577</v>
+        <v>0.5865014598748569</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5733656708499454</v>
+        <v>0.5733656708499451</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.6024269567028965</v>
+        <v>0.6024269567028963</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.6095775774034941</v>
+        <v>0.6095775774034937</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.5856854009245566</v>
+        <v>0.5856854009245562</v>
       </c>
     </row>
   </sheetData>
@@ -5990,61 +5990,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6065717382821737</v>
+        <v>0.6065717382821735</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6074981079829119</v>
+        <v>0.6074981079829108</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6078038132933201</v>
+        <v>0.6078038132933196</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02397288850439039</v>
+        <v>0.02397288850439033</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6291275064817918</v>
+        <v>0.6291275064817907</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6110349932795751</v>
+        <v>0.6110349932795741</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6112149875670974</v>
+        <v>0.6112149875670966</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6094512268447517</v>
+        <v>0.6094512268447508</v>
       </c>
       <c r="J2" t="n">
         <v>0.614783411102084</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6104606143101106</v>
+        <v>0.61046061431011</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6088963814609191</v>
+        <v>0.608896381460919</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6222147863811013</v>
+        <v>0.6222147863811006</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6130688118085927</v>
+        <v>0.6130688118085914</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6481368185522939</v>
+        <v>0.6481368185522933</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6382712738150813</v>
+        <v>0.6382712738150809</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6113549543698348</v>
+        <v>0.6113549543698346</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6079138404630938</v>
+        <v>0.6079138404630932</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6179764089735919</v>
+        <v>0.617976408973591</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6211214832437016</v>
+        <v>0.621121483243701</v>
       </c>
       <c r="U2" t="n">
         <v>0.6202171922738676</v>
@@ -6053,22 +6053,22 @@
         <v>1.082750461040455</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6149237132531032</v>
+        <v>0.6149237132531034</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6241661544250123</v>
+        <v>0.6241661544250118</v>
       </c>
       <c r="Y2" t="n">
         <v>0.6231029892359028</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.6079752759587256</v>
+        <v>0.607975275958725</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.6105619003781426</v>
+        <v>0.6105619003781431</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.6196912202229711</v>
+        <v>0.6196912202229704</v>
       </c>
     </row>
     <row r="3">
@@ -6087,7 +6087,7 @@
         <v>0.6158008957331516</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02331221300059785</v>
+        <v>0.02331221300059762</v>
       </c>
       <c r="F3" t="n">
         <v>0.6158008957331516</v>
@@ -6138,7 +6138,7 @@
         <v>0.6158008957331516</v>
       </c>
       <c r="V3" t="n">
-        <v>1.093316237946809</v>
+        <v>1.093316237946808</v>
       </c>
       <c r="W3" t="n">
         <v>0.6158008957331516</v>
@@ -6166,28 +6166,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0932798510013973</v>
+        <v>0.09327985100139782</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3286503048426605</v>
+        <v>0.3286503048426606</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4077371021828683</v>
+        <v>0.4077371021828679</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2386586781342565</v>
+        <v>0.2386586781342569</v>
       </c>
       <c r="F4" t="n">
-        <v>5.9187086296056</v>
+        <v>5.91870862960561</v>
       </c>
       <c r="G4" t="n">
-        <v>1.077300233636952</v>
+        <v>1.077300233636955</v>
       </c>
       <c r="H4" t="n">
-        <v>1.339786329624907</v>
+        <v>1.339786329624908</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8488647411479768</v>
+        <v>0.8488647411479762</v>
       </c>
       <c r="J4" t="n">
         <v>2.028909102280565</v>
@@ -6196,55 +6196,55 @@
         <v>1.031269012234271</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5904658212885464</v>
+        <v>0.5904658212885463</v>
       </c>
       <c r="M4" t="n">
-        <v>3.917929619757217</v>
+        <v>3.917929619757216</v>
       </c>
       <c r="N4" t="n">
-        <v>1.720196596302732</v>
+        <v>1.720196596302733</v>
       </c>
       <c r="O4" t="n">
-        <v>9.331611449440727</v>
+        <v>9.331611449440716</v>
       </c>
       <c r="P4" t="n">
-        <v>7.212107787805941</v>
+        <v>7.212107787805933</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.233148289769103</v>
+        <v>1.233148289769105</v>
       </c>
       <c r="R4" t="n">
-        <v>0.459390945500068</v>
+        <v>0.4593909455000658</v>
       </c>
       <c r="S4" t="n">
-        <v>2.642724940737923</v>
+        <v>2.642724940737925</v>
       </c>
       <c r="T4" t="n">
-        <v>3.781067115510758</v>
+        <v>3.78106711551076</v>
       </c>
       <c r="U4" t="n">
         <v>3.078978922393057</v>
       </c>
       <c r="V4" t="n">
-        <v>1.478995618747045</v>
+        <v>1.478995618747049</v>
       </c>
       <c r="W4" t="n">
-        <v>2.118915491046212</v>
+        <v>2.118915491046215</v>
       </c>
       <c r="X4" t="n">
-        <v>4.271531659527792</v>
+        <v>4.271531659527784</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.337673728142357</v>
+        <v>4.337673728142369</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.3935031330274523</v>
+        <v>0.3935031330274514</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.109293543428933</v>
+        <v>1.109293543428935</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.590507781200544</v>
+        <v>3.590507781200541</v>
       </c>
     </row>
     <row r="5">
@@ -6254,85 +6254,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04198316768479093</v>
+        <v>0.04198316768479116</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05978691632756965</v>
+        <v>0.05978691632756954</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05978691632756965</v>
+        <v>0.05978691632756954</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05030694535728274</v>
+        <v>0.05030694535728276</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04475678364399902</v>
+        <v>0.04475678364399892</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06347863958764938</v>
+        <v>0.06347863958764949</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05978691632756965</v>
+        <v>0.05978691632756954</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05978691632756965</v>
+        <v>0.05978691632756954</v>
       </c>
       <c r="J5" t="n">
-        <v>0.06034246491272935</v>
+        <v>0.06034246491272942</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05978691632756965</v>
+        <v>0.05978691632756954</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05978691632756965</v>
+        <v>0.05978691632756954</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0597869163275778</v>
+        <v>0.05978691632757778</v>
       </c>
       <c r="N5" t="n">
-        <v>1.720196596302732</v>
+        <v>0.04598603262155702</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04977863528403158</v>
+        <v>0.04977863528403106</v>
       </c>
       <c r="P5" t="n">
-        <v>0.04884897673052114</v>
+        <v>0.04884897673052069</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03848432473146485</v>
+        <v>0.03848432473146526</v>
       </c>
       <c r="R5" t="n">
-        <v>0.05978691632756965</v>
+        <v>0.05978691632756954</v>
       </c>
       <c r="S5" t="n">
-        <v>0.05978691632756965</v>
+        <v>0.05978691632756954</v>
       </c>
       <c r="T5" t="n">
-        <v>0.05978691632756965</v>
+        <v>0.05978691632756954</v>
       </c>
       <c r="U5" t="n">
-        <v>0.05099018009642781</v>
+        <v>0.0509901800964277</v>
       </c>
       <c r="V5" t="n">
-        <v>0.05850250911731182</v>
+        <v>0.05850250911731185</v>
       </c>
       <c r="W5" t="n">
-        <v>0.05979041525280727</v>
+        <v>0.05979041525280707</v>
       </c>
       <c r="X5" t="n">
-        <v>0.04011607365798551</v>
+        <v>0.04011607365798513</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.07730579385271574</v>
+        <v>0.07730579385271587</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.04165245391505171</v>
+        <v>0.04165245391505181</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.05978691632756965</v>
+        <v>0.05978691632756954</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.07838442049047181</v>
+        <v>0.07838442049047153</v>
       </c>
     </row>
     <row r="6">
@@ -6342,85 +6342,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.07446400596694451</v>
+        <v>0.07446400596694519</v>
       </c>
       <c r="C6" t="n">
-        <v>0.09119592743927454</v>
+        <v>0.0911959274392744</v>
       </c>
       <c r="D6" t="n">
-        <v>0.09119592743927454</v>
+        <v>0.0911959274392744</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08733424065752252</v>
+        <v>0.08733424065752222</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05262432862803142</v>
+        <v>0.05262432862803137</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0911958916175664</v>
+        <v>0.09119589161756643</v>
       </c>
       <c r="H6" t="n">
-        <v>0.09119592743927454</v>
+        <v>0.0911959274392744</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09119592743927454</v>
+        <v>0.0911959274392744</v>
       </c>
       <c r="J6" t="n">
-        <v>0.09175147602443424</v>
+        <v>0.09175147602443397</v>
       </c>
       <c r="K6" t="n">
-        <v>0.09119592743927454</v>
+        <v>0.0911959274392744</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09119592743927454</v>
+        <v>0.0911959274392744</v>
       </c>
       <c r="M6" t="n">
-        <v>0.09119592743927454</v>
+        <v>0.0911959274392744</v>
       </c>
       <c r="N6" t="n">
-        <v>1.720196596302732</v>
+        <v>0.0911959274392744</v>
       </c>
       <c r="O6" t="n">
-        <v>0.09674081661364918</v>
+        <v>0.09674081661364903</v>
       </c>
       <c r="P6" t="n">
-        <v>0.09794674266540629</v>
+        <v>0.09794674266540579</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0911958916175664</v>
+        <v>0.09119589161756643</v>
       </c>
       <c r="R6" t="n">
-        <v>0.09119592743927454</v>
+        <v>0.0911959274392744</v>
       </c>
       <c r="S6" t="n">
-        <v>0.09119592743927454</v>
+        <v>0.0911959274392744</v>
       </c>
       <c r="T6" t="n">
-        <v>0.09119592743927454</v>
+        <v>0.0911959274392744</v>
       </c>
       <c r="U6" t="n">
-        <v>0.09119592743927454</v>
+        <v>0.0911959274392744</v>
       </c>
       <c r="V6" t="n">
         <v>0.1142037131199573</v>
       </c>
       <c r="W6" t="n">
-        <v>0.09119592743927454</v>
+        <v>0.0911959274392744</v>
       </c>
       <c r="X6" t="n">
-        <v>0.09119592743927454</v>
+        <v>0.0911959274392744</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.09119592743927454</v>
+        <v>0.0911959274392744</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0811080524275663</v>
+        <v>0.08110805242756632</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.09119592743927454</v>
+        <v>0.0911959274392744</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.09119592743927454</v>
+        <v>0.0911959274392744</v>
       </c>
     </row>
     <row r="7">
@@ -6430,85 +6430,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6139726767706863</v>
+        <v>0.613972676770686</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6085663722395963</v>
+        <v>0.6085663722395964</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6067840855605039</v>
+        <v>0.6067840855605041</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01783743533448069</v>
+        <v>0.01783743533448048</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4825334303777938</v>
+        <v>0.4825334303777937</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5874357826765628</v>
+        <v>0.5874357826765627</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5869986491761034</v>
+        <v>0.5869986491761037</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5971692710880929</v>
+        <v>0.5971692710880927</v>
       </c>
       <c r="J7" t="n">
-        <v>0.565956840391051</v>
+        <v>0.5659568403910508</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5911869283876967</v>
+        <v>0.5911869283876974</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6002413005204195</v>
+        <v>0.6002413005204196</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5227259559514149</v>
+        <v>0.522725955951415</v>
       </c>
       <c r="N7" t="n">
         <v>0.5757755249874114</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3664235457181489</v>
+        <v>0.3664235457181492</v>
       </c>
       <c r="P7" t="n">
         <v>0.4250099393194243</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5859068933371659</v>
+        <v>0.5859068933371654</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6061777086289444</v>
+        <v>0.6061777086289447</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5463394695173824</v>
+        <v>0.546339469517383</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5288306752428994</v>
+        <v>0.5288306752428992</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5332321295616307</v>
+        <v>0.5332321295616305</v>
       </c>
       <c r="V7" t="n">
         <v>1.055049361633008</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5646941169468278</v>
+        <v>0.5646941169468273</v>
       </c>
       <c r="X7" t="n">
         <v>0.5108402566093077</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5165807343356275</v>
+        <v>0.5165807343356277</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.6056340749780774</v>
+        <v>0.6056340749780778</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5904580510711493</v>
+        <v>0.5904580510711491</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.5371711981962334</v>
+        <v>0.5371711981962335</v>
       </c>
     </row>
     <row r="8">
@@ -6518,85 +6518,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6057398928280646</v>
+        <v>0.605739892828064</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6042063767382853</v>
+        <v>0.6042063767382858</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6037011359298966</v>
+        <v>0.6037011359298968</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02148184721922586</v>
+        <v>0.02148184721922579</v>
       </c>
       <c r="F8" t="n">
-        <v>0.568490385046891</v>
+        <v>0.56849038504689</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5981287764445753</v>
+        <v>0.5981287764445752</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5981098735963265</v>
+        <v>0.5981098735963264</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6009737782557847</v>
+        <v>0.6009737782557846</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5920808870362303</v>
+        <v>0.5920808870362305</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5992611807278687</v>
+        <v>0.5992611807278693</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6018167160536381</v>
+        <v>0.6018167160536376</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5798653921681768</v>
+        <v>0.5798653921681767</v>
       </c>
       <c r="N8" t="n">
         <v>0.5948571405659924</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5346693295770071</v>
+        <v>0.5346693295770066</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5514607806321327</v>
+        <v>0.551460780632133</v>
       </c>
       <c r="Q8" t="n">
         <v>0.5977530880131284</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6035352596634013</v>
+        <v>0.603535259663401</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5863712386849859</v>
+        <v>0.5863712386849855</v>
       </c>
       <c r="T8" t="n">
         <v>0.5815497557629892</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5826481405347812</v>
+        <v>0.5826481405347809</v>
       </c>
       <c r="V8" t="n">
         <v>1.065338910368378</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5916699660376862</v>
+        <v>0.5916699660376863</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5764087291339537</v>
+        <v>0.5764087291339534</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5779574996041361</v>
+        <v>0.5779574996041363</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.6033493401154316</v>
+        <v>0.6033493401154311</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.5990308252940785</v>
+        <v>0.5990308252940771</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.5839144572656951</v>
+        <v>0.5839144572656947</v>
       </c>
     </row>
   </sheetData>
@@ -6762,85 +6762,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6206030201027822</v>
+        <v>0.6206030201027823</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6221449946269573</v>
+        <v>0.6221449946269577</v>
       </c>
       <c r="D2" t="n">
         <v>0.621575632148342</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06563058812612417</v>
+        <v>0.06563058812612424</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6256429499712999</v>
+        <v>0.6256429499713004</v>
       </c>
       <c r="G2" t="n">
         <v>0.6244409411291167</v>
       </c>
       <c r="H2" t="n">
-        <v>0.628783033564026</v>
+        <v>0.6287830335640258</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6240828552625309</v>
+        <v>0.6240828552625316</v>
       </c>
       <c r="J2" t="n">
-        <v>0.631384281747014</v>
+        <v>0.6313842817470142</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6251561536130972</v>
+        <v>0.6251561536130974</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6207565142621642</v>
+        <v>0.6207565142621643</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6275987996954663</v>
+        <v>0.6275987996954664</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6264577959336669</v>
+        <v>0.626457795933667</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6505643990877852</v>
+        <v>0.6505643990877853</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6419066336607977</v>
+        <v>0.6419066336607983</v>
       </c>
       <c r="Q2" t="n">
         <v>0.6277141911023257</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6258351544427495</v>
+        <v>0.6258351544427502</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6208412699714992</v>
+        <v>0.6208412699714996</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6338499182728734</v>
+        <v>0.6338499182728738</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6326630650601993</v>
+        <v>0.6326630650602002</v>
       </c>
       <c r="V2" t="n">
         <v>1.112171858368071</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6555653303432379</v>
+        <v>0.6555653303432382</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6212783191847471</v>
+        <v>0.6212783191847476</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6490902915458787</v>
+        <v>0.6490902915458788</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.6388309760447054</v>
+        <v>0.638830976044706</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.6238206324385026</v>
+        <v>0.6238206324385029</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.623774630634139</v>
+        <v>0.6237746306341386</v>
       </c>
     </row>
     <row r="3">
@@ -6859,7 +6859,7 @@
         <v>0.6298468774191761</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04016784212414349</v>
+        <v>0.04016784212414356</v>
       </c>
       <c r="F3" t="n">
         <v>0.6298468774191761</v>
@@ -6874,7 +6874,7 @@
         <v>0.6298468774191761</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6302851944344778</v>
+        <v>0.6302851944344776</v>
       </c>
       <c r="K3" t="n">
         <v>0.6298468774191761</v>
@@ -6910,7 +6910,7 @@
         <v>0.6298468774191761</v>
       </c>
       <c r="V3" t="n">
-        <v>1.111182704518163</v>
+        <v>1.111182704518162</v>
       </c>
       <c r="W3" t="n">
         <v>0.6298468774191761</v>
@@ -6938,64 +6938,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1460444434207097</v>
+        <v>0.1460444434207118</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5752088863755287</v>
+        <v>0.5752088863755285</v>
       </c>
       <c r="D4" t="n">
         <v>0.4341103198063238</v>
       </c>
       <c r="E4" t="n">
-        <v>7.012172512360581</v>
+        <v>7.012172512360576</v>
       </c>
       <c r="F4" t="n">
-        <v>1.56827330389296</v>
+        <v>1.568273303892958</v>
       </c>
       <c r="G4" t="n">
-        <v>1.085755519241122</v>
+        <v>1.085755519241123</v>
       </c>
       <c r="H4" t="n">
-        <v>2.565917416776119</v>
+        <v>2.565917416776118</v>
       </c>
       <c r="I4" t="n">
-        <v>1.146924914816972</v>
+        <v>1.146924914816973</v>
       </c>
       <c r="J4" t="n">
-        <v>2.788882421732887</v>
+        <v>2.788882421732886</v>
       </c>
       <c r="K4" t="n">
-        <v>1.301619973996965</v>
+        <v>1.301619973996964</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1911518406471605</v>
+        <v>0.1911518406471653</v>
       </c>
       <c r="M4" t="n">
-        <v>1.987874832115085</v>
+        <v>1.987874832115089</v>
       </c>
       <c r="N4" t="n">
-        <v>1.772052089876938</v>
+        <v>1.772052089876935</v>
       </c>
       <c r="O4" t="n">
-        <v>7.34747521321423</v>
+        <v>7.347475213214215</v>
       </c>
       <c r="P4" t="n">
-        <v>5.595394996373465</v>
+        <v>5.595394996373463</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.070979747312408</v>
+        <v>2.070979747312406</v>
       </c>
       <c r="R4" t="n">
-        <v>1.684386864609268</v>
+        <v>1.684386864609265</v>
       </c>
       <c r="S4" t="n">
-        <v>0.203418541669414</v>
+        <v>0.2034185416694148</v>
       </c>
       <c r="T4" t="n">
-        <v>3.915446577867026</v>
+        <v>3.915446577867024</v>
       </c>
       <c r="U4" t="n">
-        <v>3.309779198621673</v>
+        <v>3.30977919862168</v>
       </c>
       <c r="V4" t="n">
         <v>4.442549645874949</v>
@@ -7004,16 +7004,16 @@
         <v>9.663751693847683</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3444660558370037</v>
+        <v>0.3444660558370074</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.772895191479739</v>
+        <v>7.772895191479748</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.703950449538483</v>
+        <v>4.703950449538476</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.024622634516208</v>
+        <v>1.024622634516209</v>
       </c>
       <c r="AB4" t="n">
         <v>1.107016269701407</v>
@@ -7026,82 +7026,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06854406040847273</v>
+        <v>0.06854406040847282</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09552298473077842</v>
+        <v>0.09552298473077843</v>
       </c>
       <c r="D5" t="n">
-        <v>0.09552298473077842</v>
+        <v>0.09552298473077843</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08115750336575026</v>
+        <v>0.08115750336575027</v>
       </c>
       <c r="F5" t="n">
-        <v>0.07274706150371804</v>
+        <v>0.07274706150371808</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1011172404371912</v>
+        <v>0.1011172404371913</v>
       </c>
       <c r="H5" t="n">
-        <v>0.09552298473077842</v>
+        <v>0.09552298473077843</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09552298473077842</v>
+        <v>0.09552298473077843</v>
       </c>
       <c r="J5" t="n">
-        <v>0.09615751941286467</v>
+        <v>0.0961575194128647</v>
       </c>
       <c r="K5" t="n">
-        <v>0.09552298473077842</v>
+        <v>0.09552298473077843</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09552298473077842</v>
+        <v>0.09552298473077843</v>
       </c>
       <c r="M5" t="n">
-        <v>0.09552298473077846</v>
+        <v>0.09552298473077851</v>
       </c>
       <c r="N5" t="n">
-        <v>1.772052089876938</v>
+        <v>0.0746098048947164</v>
       </c>
       <c r="O5" t="n">
-        <v>0.08035692827882253</v>
+        <v>0.08035692827882258</v>
       </c>
       <c r="P5" t="n">
-        <v>0.07894816946964117</v>
+        <v>0.07894816946964121</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.06324208602607137</v>
+        <v>0.06324208602607144</v>
       </c>
       <c r="R5" t="n">
-        <v>0.09552298473077842</v>
+        <v>0.09552298473077843</v>
       </c>
       <c r="S5" t="n">
-        <v>0.09552298473077842</v>
+        <v>0.09552298473077843</v>
       </c>
       <c r="T5" t="n">
-        <v>0.09552298473077842</v>
+        <v>0.09552298473077843</v>
       </c>
       <c r="U5" t="n">
-        <v>0.08241159768798491</v>
+        <v>0.08241159768798502</v>
       </c>
       <c r="V5" t="n">
-        <v>0.09241715053860028</v>
+        <v>0.09241715053860022</v>
       </c>
       <c r="W5" t="n">
-        <v>0.09552828682178532</v>
+        <v>0.09552828682178534</v>
       </c>
       <c r="X5" t="n">
-        <v>0.06571475802319068</v>
+        <v>0.06571475802319064</v>
       </c>
       <c r="Y5" t="n">
         <v>0.1224444538924045</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.06804291304157262</v>
+        <v>0.06804291304157271</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.09552298473077842</v>
+        <v>0.09552298473077843</v>
       </c>
       <c r="AB5" t="n">
         <v>0.1237047270887205</v>
@@ -7129,7 +7129,7 @@
         <v>0.1018847232581706</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1775097299734778</v>
+        <v>0.1775097299734777</v>
       </c>
       <c r="H6" t="n">
         <v>0.1775096708635419</v>
@@ -7138,7 +7138,7 @@
         <v>0.1775096708635419</v>
       </c>
       <c r="J6" t="n">
-        <v>0.178144205545628</v>
+        <v>0.1781442055456279</v>
       </c>
       <c r="K6" t="n">
         <v>0.1775096708635419</v>
@@ -7150,16 +7150,16 @@
         <v>0.1775096708635419</v>
       </c>
       <c r="N6" t="n">
-        <v>1.772052089876938</v>
+        <v>0.1775096708635419</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1883813399774215</v>
+        <v>0.1883813399774213</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1907457286278639</v>
+        <v>0.1907457286278638</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1775097299734778</v>
+        <v>0.1775097299734777</v>
       </c>
       <c r="R6" t="n">
         <v>0.1775096708635419</v>
@@ -7174,7 +7174,7 @@
         <v>0.1775096708635419</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2195716143224261</v>
+        <v>0.2195716143224262</v>
       </c>
       <c r="W6" t="n">
         <v>0.1775096708635419</v>
@@ -7202,85 +7202,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6272511623362205</v>
+        <v>0.6272511623362199</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6182457202789744</v>
+        <v>0.6182457202789738</v>
       </c>
       <c r="D7" t="n">
-        <v>0.62159423068254</v>
+        <v>0.6215942306825404</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1130160945437976</v>
+        <v>-0.1130160945437974</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5979263767912049</v>
+        <v>0.5979263767912045</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6044328480195507</v>
+        <v>0.6044328480195499</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5797170851688006</v>
+        <v>0.5797170851688005</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6069510547777226</v>
+        <v>0.6069510547777228</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5664461332965826</v>
+        <v>0.5664461332965824</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6005797620788328</v>
+        <v>0.6005797620788326</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6263600960190012</v>
+        <v>0.6263600960190004</v>
       </c>
       <c r="M7" t="n">
-        <v>0.586478590360563</v>
+        <v>0.5864785903605635</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5928408500747558</v>
+        <v>0.5928408500747562</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4488087934269432</v>
+        <v>0.4488087934269431</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5002563936898921</v>
+        <v>0.5002563936898931</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5855243531263704</v>
+        <v>0.5855243531263707</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5967748220957053</v>
+        <v>0.5967748220957056</v>
       </c>
       <c r="S7" t="n">
         <v>0.6258462007228353</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5497481094820151</v>
+        <v>0.5497481094820149</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5558967186889968</v>
+        <v>0.5558967186889974</v>
       </c>
       <c r="V7" t="n">
         <v>1.00318785540036</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4209251679389588</v>
+        <v>0.4209251679389581</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6233294730264611</v>
+        <v>0.6233294730264607</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4594163676388017</v>
+        <v>0.4594163676388013</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.5189329072832765</v>
+        <v>0.5189329072832768</v>
       </c>
       <c r="AA7" t="n">
         <v>0.6082991223166813</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.6087183544888479</v>
+        <v>0.6087183544888483</v>
       </c>
     </row>
     <row r="8">
@@ -7290,34 +7290,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6194219614679841</v>
+        <v>0.6194219614679837</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6168664311574714</v>
+        <v>0.6168664311574719</v>
       </c>
       <c r="D8" t="n">
         <v>0.6178206515835482</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.004068591226030216</v>
+        <v>-0.00406859122603013</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6111190204609739</v>
+        <v>0.6111190204609741</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6128774767625808</v>
+        <v>0.6128774767625809</v>
       </c>
       <c r="H8" t="n">
-        <v>0.605973818335936</v>
+        <v>0.6059738183359362</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6136651829960122</v>
+        <v>0.613665182996012</v>
       </c>
       <c r="J8" t="n">
         <v>0.6023373054862546</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6118395228644783</v>
+        <v>0.6118395228644785</v>
       </c>
       <c r="L8" t="n">
         <v>0.6191700176133712</v>
@@ -7326,49 +7326,49 @@
         <v>0.6078660908772672</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6096199355607436</v>
+        <v>0.6096199355607447</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5681914939371773</v>
+        <v>0.5681914939371775</v>
       </c>
       <c r="P8" t="n">
-        <v>0.582942550583606</v>
+        <v>0.5829425505836064</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.6075473013015961</v>
+        <v>0.6075473013015956</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6107872638761835</v>
+        <v>0.6107872638761839</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6190209493252642</v>
+        <v>0.6190209493252646</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5974047236018374</v>
+        <v>0.5974047236018373</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5990155071727958</v>
+        <v>0.5990155071727952</v>
       </c>
       <c r="V8" t="n">
-        <v>1.063033857860307</v>
+        <v>1.063033857860308</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5605052867357548</v>
+        <v>0.5605052867357552</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6183128794163276</v>
+        <v>0.6183128794163274</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5715438664659992</v>
+        <v>0.5715438664659994</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5883647661710204</v>
+        <v>0.5883647661710213</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.6140163351982469</v>
+        <v>0.6140163351982467</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.614161085368232</v>
+        <v>0.6141610853682319</v>
       </c>
     </row>
   </sheetData>
@@ -7534,61 +7534,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6145226157418897</v>
+        <v>0.6145226157418892</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6159456981172748</v>
+        <v>0.6159456981172747</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6148046899835331</v>
+        <v>0.6148046899835324</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04911163444940914</v>
+        <v>0.04911163444940892</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6313583246256266</v>
+        <v>0.6313583246256261</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6182391956457769</v>
+        <v>0.6182391956457757</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6207898583176469</v>
+        <v>0.6207898583176461</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6157235950279263</v>
+        <v>0.6157235950279257</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6265091167460384</v>
+        <v>0.6265091167460387</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6170558094212232</v>
+        <v>0.6170558094212231</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6148720291787705</v>
+        <v>0.6148720291787698</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6479508956077319</v>
+        <v>0.6479508956077307</v>
       </c>
       <c r="N2" t="n">
         <v>0.6223574822448215</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6639471159210174</v>
+        <v>0.6639471159210169</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6408055109650858</v>
+        <v>0.6408055109650863</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6271304812918888</v>
+        <v>0.6271304812918882</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6163898551525089</v>
+        <v>0.6163898551525083</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6153200651413849</v>
+        <v>0.615320065141384</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6306423162615488</v>
+        <v>0.6306423162615478</v>
       </c>
       <c r="U2" t="n">
         <v>0.6323870378503806</v>
@@ -7597,22 +7597,22 @@
         <v>1.097990134939607</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6395964859896088</v>
+        <v>0.6395964859896089</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6230781518056679</v>
+        <v>0.6230781518056677</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6363419198469902</v>
+        <v>0.6363419198469896</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.6236438439347523</v>
+        <v>0.6236438439347511</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.6173600729043487</v>
+        <v>0.6173600729043485</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.6235250521765003</v>
+        <v>0.6235250521764997</v>
       </c>
     </row>
     <row r="3">
@@ -7622,85 +7622,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6239440403019272</v>
+        <v>0.6239440403019264</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6239440403019272</v>
+        <v>0.6239440403019264</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6239440403019272</v>
+        <v>0.6239440403019264</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03347766029931067</v>
+        <v>0.03347766029931053</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6239440403019272</v>
+        <v>0.6239440403019264</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6239440403019272</v>
+        <v>0.6239440403019264</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6239440403019272</v>
+        <v>0.6239440403019264</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6239440403019272</v>
+        <v>0.6239440403019264</v>
       </c>
       <c r="J3" t="n">
-        <v>0.624200569420933</v>
+        <v>0.6242005694209324</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6239440403019272</v>
+        <v>0.6239440403019264</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6239440403019272</v>
+        <v>0.6239440403019264</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6239440403019272</v>
+        <v>0.6239440403019264</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6239440403019272</v>
+        <v>0.6239440403019264</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6239440403019272</v>
+        <v>0.6239440403019264</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6239440403019272</v>
+        <v>0.6239440403019264</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6239440403019272</v>
+        <v>0.6239440403019264</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6239440403019272</v>
+        <v>0.6239440403019264</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6239440403019272</v>
+        <v>0.6239440403019264</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6239440403019272</v>
+        <v>0.6239440403019264</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6239440403019272</v>
+        <v>0.6239440403019264</v>
       </c>
       <c r="V3" t="n">
         <v>1.102886815748017</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6239440403019272</v>
+        <v>0.6239440403019264</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6239440403019272</v>
+        <v>0.6239440403019264</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.6239440403019272</v>
+        <v>0.6239440403019264</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.6239440403019272</v>
+        <v>0.6239440403019264</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.6239440403019272</v>
+        <v>0.6239440403019264</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.6239440403019272</v>
+        <v>0.6239440403019264</v>
       </c>
     </row>
     <row r="4">
@@ -7710,43 +7710,43 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07643032559339098</v>
+        <v>0.07643032559339039</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4299844503409174</v>
+        <v>0.429984450340918</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1540688185006363</v>
+        <v>0.1540688185006372</v>
       </c>
       <c r="E4" t="n">
-        <v>4.047122327206966</v>
+        <v>4.047122327206967</v>
       </c>
       <c r="F4" t="n">
-        <v>4.35883180674439</v>
+        <v>4.358831806744393</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8894758345853959</v>
+        <v>0.8894758345854255</v>
       </c>
       <c r="H4" t="n">
-        <v>1.813012581656419</v>
+        <v>1.81301258165642</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3999685455454342</v>
+        <v>0.3999685455454352</v>
       </c>
       <c r="J4" t="n">
-        <v>2.839878679468912</v>
+        <v>2.839878679468927</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6614426468052473</v>
+        <v>0.6614426468052474</v>
       </c>
       <c r="L4" t="n">
         <v>0.161517880365629</v>
       </c>
       <c r="M4" t="n">
-        <v>8.028960181006513</v>
+        <v>8.028960181006514</v>
       </c>
       <c r="N4" t="n">
-        <v>2.101418623317719</v>
+        <v>2.10141862331772</v>
       </c>
       <c r="O4" t="n">
         <v>11.02328320786834</v>
@@ -7755,40 +7755,40 @@
         <v>6.165922364587868</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.006009530108046</v>
+        <v>3.006009530108045</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5857416283020932</v>
+        <v>0.5857416283020943</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2546073872789417</v>
+        <v>0.2546073872789413</v>
       </c>
       <c r="T4" t="n">
         <v>4.28240102104411</v>
       </c>
       <c r="U4" t="n">
-        <v>4.170642662884183</v>
+        <v>4.17064266288418</v>
       </c>
       <c r="V4" t="n">
-        <v>2.742351364217537</v>
+        <v>2.742351364217536</v>
       </c>
       <c r="W4" t="n">
-        <v>6.438305949648464</v>
+        <v>6.438305949648459</v>
       </c>
       <c r="X4" t="n">
-        <v>2.226286603757548</v>
+        <v>2.226286603757531</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.533489589525124</v>
+        <v>5.533489589525121</v>
       </c>
       <c r="Z4" t="n">
         <v>2.091280207082074</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.7973619596704338</v>
+        <v>0.7973619596704327</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.514498832025884</v>
+        <v>2.514498832025886</v>
       </c>
     </row>
     <row r="5">
@@ -7798,85 +7798,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05663132999157507</v>
+        <v>0.05663132999157468</v>
       </c>
       <c r="C5" t="n">
-        <v>0.07995750126240646</v>
+        <v>0.07995750126240607</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07995750126240646</v>
+        <v>0.07995750126240607</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06753700314569082</v>
+        <v>0.06753700314569068</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06026527485337488</v>
+        <v>0.06026527485337459</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08479433482898574</v>
+        <v>0.08479433482898513</v>
       </c>
       <c r="H5" t="n">
-        <v>0.07995750126240646</v>
+        <v>0.07995750126240607</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07995750126240646</v>
+        <v>0.07995750126240607</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08055411444508655</v>
+        <v>0.08055411444508537</v>
       </c>
       <c r="K5" t="n">
-        <v>0.07995750126240646</v>
+        <v>0.07995750126240607</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07995750126240642</v>
+        <v>0.079957501262406</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07995750126248173</v>
+        <v>0.07995750126248116</v>
       </c>
       <c r="N5" t="n">
-        <v>2.101418623317719</v>
+        <v>0.06187581613636214</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06684482019435793</v>
+        <v>0.06684482019435707</v>
       </c>
       <c r="P5" t="n">
-        <v>0.06562679723337667</v>
+        <v>0.06562679723337675</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.05204720495095499</v>
+        <v>0.05204720495095536</v>
       </c>
       <c r="R5" t="n">
-        <v>0.07995750126240646</v>
+        <v>0.07995750126240607</v>
       </c>
       <c r="S5" t="n">
-        <v>0.07995750126240646</v>
+        <v>0.07995750126240607</v>
       </c>
       <c r="T5" t="n">
-        <v>0.07995750126240646</v>
+        <v>0.07995750126240607</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06854876124611479</v>
+        <v>0.06854876124611399</v>
       </c>
       <c r="V5" t="n">
-        <v>0.07751917913491491</v>
+        <v>0.07751917913491424</v>
       </c>
       <c r="W5" t="n">
-        <v>0.07996208549365183</v>
+        <v>0.07996208549365127</v>
       </c>
       <c r="X5" t="n">
-        <v>0.05418509487946627</v>
+        <v>0.05418509487946613</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1031099001187799</v>
+        <v>0.1031099001187796</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.05619803438707646</v>
+        <v>0.05619803438707743</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.07995750126240646</v>
+        <v>0.07995750126240607</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1043236376299077</v>
+        <v>0.1043236376299085</v>
       </c>
     </row>
     <row r="6">
@@ -7886,85 +7886,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1021294318745331</v>
+        <v>0.1021294318745327</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1248650311712288</v>
+        <v>0.1248650311712256</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1248650311712288</v>
+        <v>0.1248650311712256</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1196176943464901</v>
+        <v>0.1196176943464889</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07245336000885308</v>
+        <v>0.07245336000885183</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1248649619517766</v>
+        <v>0.1248649619517764</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1248650311712288</v>
+        <v>0.1248650311712256</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1248650311712288</v>
+        <v>0.1248650311712256</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1254616443539087</v>
+        <v>0.125461644353904</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1248650311712288</v>
+        <v>0.1248650311712256</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1248650311712289</v>
+        <v>0.124865031171225</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1248650311712288</v>
+        <v>0.1248650311712256</v>
       </c>
       <c r="N6" t="n">
-        <v>2.101418623317719</v>
+        <v>0.1248650311712256</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1323994868497436</v>
+        <v>0.1323994868497457</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1340381167443744</v>
+        <v>0.1340381167443741</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1248649619517766</v>
+        <v>0.1248649619517764</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1248650311712288</v>
+        <v>0.1248650311712256</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1248650311712288</v>
+        <v>0.1248650311712256</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1248650311712288</v>
+        <v>0.1248650311712256</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1248650311712288</v>
+        <v>0.1248650311712256</v>
       </c>
       <c r="V6" t="n">
-        <v>0.155064282868513</v>
+        <v>0.1550642828685039</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1248650311712288</v>
+        <v>0.1248650311712256</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1248650311712288</v>
+        <v>0.1248650311712256</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1248650311712288</v>
+        <v>0.1248650311712256</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.1111574590374174</v>
+        <v>0.1111574590374169</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.1248650311712288</v>
+        <v>0.1248650311712256</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1248650311712288</v>
+        <v>0.1248650311712256</v>
       </c>
     </row>
     <row r="7">
@@ -7974,85 +7974,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6227425959550983</v>
+        <v>0.622742595955098</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6144144944617098</v>
+        <v>0.6144144944617096</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6211090378574993</v>
+        <v>0.6211090378574994</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.06120416198376368</v>
+        <v>-0.0612041619837639</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5246326518431002</v>
+        <v>0.5246326518430997</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6006449848175008</v>
+        <v>0.6006449848175001</v>
       </c>
       <c r="H7" t="n">
-        <v>0.586306350152618</v>
+        <v>0.5863063501526175</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6157419286070945</v>
+        <v>0.6157419286070933</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5538797544504717</v>
+        <v>0.5538797544504729</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6079003040652857</v>
+        <v>0.6079003040652856</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6206845382815008</v>
+        <v>0.6206845382815001</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4277017051759934</v>
+        <v>0.4277017051759935</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5766691042042434</v>
+        <v>0.5766691042042426</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3283861801708634</v>
+        <v>0.3283861801708625</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4660693746717062</v>
+        <v>0.4660693746717061</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5487184338553345</v>
+        <v>0.5487184338553339</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6118716895856655</v>
+        <v>0.6118716895856662</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6180168267302036</v>
+        <v>0.6180168267302037</v>
       </c>
       <c r="T7" t="n">
-        <v>0.528400352091643</v>
+        <v>0.5284003520916428</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5170319862254701</v>
+        <v>0.5170319862254691</v>
       </c>
       <c r="V7" t="n">
-        <v>1.030358320178957</v>
+        <v>1.030358320178956</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4747668686856568</v>
+        <v>0.4747668686856557</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5725976066413351</v>
+        <v>0.5725976066413343</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4941851353076248</v>
+        <v>0.4941851353076253</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.5685402840287551</v>
+        <v>0.568540284028755</v>
       </c>
       <c r="AA7" t="n">
         <v>0.6060202155616952</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.5700415610702004</v>
+        <v>0.5700415610701994</v>
       </c>
     </row>
     <row r="8">
@@ -8062,85 +8062,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6139759547353071</v>
+        <v>0.6139759547353069</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6116097243911157</v>
+        <v>0.6116097243911159</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6135147548367018</v>
+        <v>0.613514754836701</v>
       </c>
       <c r="E8" t="n">
-        <v>0.006031103577545685</v>
+        <v>0.006031103577545671</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5861713263902435</v>
+        <v>0.5861713263902429</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6076380511506786</v>
+        <v>0.6076380511506787</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6036645893555099</v>
+        <v>0.6036645893555097</v>
       </c>
       <c r="I8" t="n">
         <v>0.6119916080681985</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5945129218353388</v>
+        <v>0.5945129218353381</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6097558583051976</v>
+        <v>0.6097558583051971</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6133889453720607</v>
+        <v>0.6133889453720596</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5586600077382167</v>
+        <v>0.5586600077382166</v>
       </c>
       <c r="N8" t="n">
-        <v>0.600847235664094</v>
+        <v>0.6008472356640928</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5294673476743688</v>
+        <v>0.5294673476743684</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5689720349866295</v>
+        <v>0.5689720349866287</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5929025906289056</v>
+        <v>0.5929025906289057</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6108968971043116</v>
+        <v>0.6108968971043114</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6126231640773416</v>
+        <v>0.6126231640773414</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5871696336462017</v>
+        <v>0.5871696336462007</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5837417125370917</v>
+        <v>0.5837417125370908</v>
       </c>
       <c r="V8" t="n">
         <v>1.064989438321084</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5717203975047671</v>
+        <v>0.571720397504767</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5997153608587235</v>
+        <v>0.5997153608587227</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5773012045574898</v>
+        <v>0.5773012045574889</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5984349582691637</v>
+        <v>0.5984349582691627</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.6092046755277031</v>
+        <v>0.6092046755277025</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.5989992523490559</v>
+        <v>0.5989992523490553</v>
       </c>
     </row>
   </sheetData>
